--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD394712-8DB7-4A0F-9F40-2EA519D4B8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="10480" firstSheet="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -15,6 +21,7 @@
     <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
     <sheet name="DialogueEvents" sheetId="7" r:id="rId7"/>
     <sheet name="StreamEvents" sheetId="8" r:id="rId8"/>
+    <sheet name="PhaseEndingConditions" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
@@ -28,8 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="337">
   <si>
     <t>ID</t>
   </si>
@@ -162,60 +167,69 @@
     <t>参数+15</t>
   </si>
   <si>
+    <t>战术喝水</t>
+  </si>
+  <si>
+    <t>参数+5，神采+4</t>
+  </si>
+  <si>
+    <t>网络波动</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Buff</t>
+  </si>
+  <si>
+    <t>刷新</t>
+  </si>
+  <si>
+    <t>重抽其他手牌，抽牌次数+1</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>才八点</t>
+  </si>
+  <si>
+    <t>获得一个额外回合，神采+7，出牌次数+1</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>渐入佳境</t>
+  </si>
+  <si>
+    <t>体力消耗减少1点，神采+4</t>
+  </si>
+  <si>
+    <t>wink</t>
+  </si>
+  <si>
+    <t>亲和力+3，神采+2</t>
+  </si>
+  <si>
+    <t>集中</t>
+  </si>
+  <si>
+    <t>专注+2，神采+2</t>
+  </si>
+  <si>
+    <t>生气</t>
+  </si>
+  <si>
+    <t>红温+2，神采+2</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
-    <t>战术喝水</t>
-  </si>
-  <si>
-    <t>参数+5，神采+4</t>
-  </si>
-  <si>
-    <t>网络波动</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>刷新</t>
-  </si>
-  <si>
-    <t>重抽其他手牌，卡牌使用次数+1，体力消耗减少50%+2回合</t>
-  </si>
-  <si>
-    <t>才八点</t>
-  </si>
-  <si>
-    <t>获得一个额外回合，神采+7，出牌次数+1</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>wink</t>
-  </si>
-  <si>
-    <t>亲和力+3，神采+2</t>
-  </si>
-  <si>
-    <t>集中</t>
-  </si>
-  <si>
-    <t>专注+2，神采+2</t>
-  </si>
-  <si>
-    <t>生气</t>
-  </si>
-  <si>
-    <t>红温+2，神采+2</t>
-  </si>
-  <si>
     <t>二次推流</t>
   </si>
   <si>
@@ -225,15 +239,12 @@
     <t>加分动画显示需改进</t>
   </si>
   <si>
-    <t>才艺</t>
+    <t>计划</t>
   </si>
   <si>
     <t>参数+11，神采+7</t>
   </si>
   <si>
-    <t>Rare</t>
-  </si>
-  <si>
     <t>小花花</t>
   </si>
   <si>
@@ -258,6 +269,9 @@
     <t>舰长+1，神采+4，体力消耗减少+2回合</t>
   </si>
   <si>
+    <t>再一次</t>
+  </si>
+  <si>
     <t>攻击弹幕</t>
   </si>
   <si>
@@ -276,7 +290,7 @@
     <t>在有红温的状态下可使用，参数+24</t>
   </si>
   <si>
-    <t>激怒</t>
+    <t>红温</t>
   </si>
   <si>
     <t>体力消耗增加50%+2回合，参数+30，神采+5</t>
@@ -312,10 +326,10 @@
     <t>专注+3，神采+4</t>
   </si>
   <si>
-    <t>警告！</t>
-  </si>
-  <si>
-    <t>在红温的状态下可用，参数+12，红温大于10层时，参数+24，红温大于30层时，参数+36</t>
+    <t>状态火热</t>
+  </si>
+  <si>
+    <t>红温+5，下一回合开始时，参数+18，下下回合开始时，参数+24</t>
   </si>
   <si>
     <t>躺</t>
@@ -324,22 +338,28 @@
     <t>神采+6</t>
   </si>
   <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>流水+30，神采+3，体力消耗减少+2回合</t>
+    <t>惊喜</t>
+  </si>
+  <si>
+    <t>舰长+1，参数+4，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>祝福</t>
+  </si>
+  <si>
+    <t>流水+30，神采+3，体力消耗减少50%+2回合</t>
+  </si>
+  <si>
+    <t>宣传</t>
+  </si>
+  <si>
+    <t>同接+50，神采+2</t>
   </si>
   <si>
     <t>直播通知</t>
   </si>
   <si>
-    <t>同接+50，神采+2</t>
-  </si>
-  <si>
-    <t>YLG</t>
-  </si>
-  <si>
-    <t>同接+20，以后，每当打出A卡时，同接+10</t>
+    <t>同接+20，以后，每当打出A卡时，同接+10,</t>
   </si>
   <si>
     <t>爆米</t>
@@ -351,13 +371,13 @@
     <t>爆！</t>
   </si>
   <si>
-    <t>参数+38</t>
+    <t>参数+42</t>
   </si>
   <si>
     <t>越想越气</t>
   </si>
   <si>
-    <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
+    <t>有红温的状态下，专注+1，红温+3</t>
   </si>
   <si>
     <t>欢呼</t>
@@ -381,7 +401,7 @@
     <t>体力消耗减少50%+4回合，神采+3</t>
   </si>
   <si>
-    <t>补充营养</t>
+    <t>预知梦</t>
   </si>
   <si>
     <t>体力消耗减少1点，神采+5</t>
@@ -414,7 +434,7 @@
     <t>申请对线</t>
   </si>
   <si>
-    <t>红温+2，之后4回合内，回合结束时，参数+8</t>
+    <t>红温+2，之后4回合内，回合结束时，参数+4</t>
   </si>
   <si>
     <t>子弹时间</t>
@@ -438,7 +458,7 @@
     <t>参数+8，亲和力+3</t>
   </si>
   <si>
-    <t>玩梗</t>
+    <t>应援</t>
   </si>
   <si>
     <t>参数+7，幽默+2</t>
@@ -456,7 +476,7 @@
     <t>亲和力+1，以后，回合结束时，亲和力+3</t>
   </si>
   <si>
-    <t>拿个快递</t>
+    <t>摘花</t>
   </si>
   <si>
     <t>抽两张牌，体力消耗减少+2回合</t>
@@ -465,46 +485,7 @@
     <t>点炮仗</t>
   </si>
   <si>
-    <t>红温&gt;10层时可使用，获得红温300%的参数，红温减少50%</t>
-  </si>
-  <si>
-    <t>逼逼赖赖</t>
-  </si>
-  <si>
-    <t>红温+3，卡牌使用次数+1，如果红温大于10层，红温+3</t>
-  </si>
-  <si>
-    <t>雷区</t>
-  </si>
-  <si>
-    <t>红温+1，以后每当使用A卡的时候，红温+1</t>
-  </si>
-  <si>
-    <t>红温+2，幽默+1</t>
-  </si>
-  <si>
-    <t>自洽</t>
-  </si>
-  <si>
-    <t>幽默+3，参数+12，卡牌使用次数+1</t>
-  </si>
-  <si>
-    <t>早上好！</t>
-  </si>
-  <si>
-    <t>开局加入手牌，幽默+2，神采+2</t>
-  </si>
-  <si>
-    <t>拜拜！！！</t>
-  </si>
-  <si>
-    <t>最后一回合加入手牌，</t>
-  </si>
-  <si>
-    <t>封禁</t>
-  </si>
-  <si>
-    <t>神采+5两次，获得神采70%的参数</t>
+    <t>红温&gt;10层时可使用，获得红温200%的参数，红温减少50%</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -777,39 +758,6 @@
     <t>减少X%的红温</t>
   </si>
   <si>
-    <t>红温大于10层时，红温+X</t>
-  </si>
-  <si>
-    <t>红温大于10层时，参数获得量+X%</t>
-  </si>
-  <si>
-    <t>红温大于30层时，参数获得量+X%</t>
-  </si>
-  <si>
-    <t>红温大于50层时，参数获得量+X%</t>
-  </si>
-  <si>
-    <t>红温大于50层时，大于50层的部分每层红温会使参数获得量+5%</t>
-  </si>
-  <si>
-    <t>红温大于10层时，参数+X</t>
-  </si>
-  <si>
-    <t>参数+ {AttributeDelta}</t>
-  </si>
-  <si>
-    <t>红温大于30层时，参数+X</t>
-  </si>
-  <si>
-    <t>红温大于50层时，参数+X</t>
-  </si>
-  <si>
-    <t>每当使用A卡，红温+X</t>
-  </si>
-  <si>
-    <t>每当使用A卡，红温+1</t>
-  </si>
-  <si>
     <t>BuffType</t>
   </si>
   <si>
@@ -819,144 +767,210 @@
     <t>Latency</t>
   </si>
   <si>
+    <t>亲和力</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>专注</t>
+  </si>
+  <si>
+    <t>积极</t>
+  </si>
+  <si>
+    <t>Persistent</t>
+  </si>
+  <si>
+    <t>体力消耗减少X点</t>
+  </si>
+  <si>
+    <t>体力消耗减少50%</t>
+  </si>
+  <si>
+    <t>回合结束时，专注+2</t>
+  </si>
+  <si>
+    <t>体力消耗增加50%</t>
+  </si>
+  <si>
+    <t>回合结束时，参数+4</t>
+  </si>
+  <si>
+    <t>幽默</t>
+  </si>
+  <si>
+    <t>营业</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>OperatorType</t>
+  </si>
+  <si>
+    <t>NameOrID</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>TargetDelta</t>
+  </si>
+  <si>
+    <t>有红温时</t>
+  </si>
+  <si>
+    <t>VBuffLayerCondition</t>
+  </si>
+  <si>
+    <t>GreaterThan</t>
+  </si>
+  <si>
+    <t>使用M卡时</t>
+  </si>
+  <si>
+    <t>VCardTypeCondition</t>
+  </si>
+  <si>
+    <t>使用A卡时</t>
+  </si>
+  <si>
+    <t>当红温大于3层时</t>
+  </si>
+  <si>
+    <t>当专注大于4层时</t>
+  </si>
+  <si>
+    <t>当亲和力大于3层时</t>
+  </si>
+  <si>
+    <t>当红温大于10层时</t>
+  </si>
+  <si>
     <t>Effect5</t>
   </si>
   <si>
     <t>E5Param</t>
   </si>
   <si>
-    <t>亲和力</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>专注</t>
-  </si>
-  <si>
-    <t>盐</t>
-  </si>
-  <si>
-    <t>红温</t>
-  </si>
-  <si>
-    <t>Persistent</t>
-  </si>
-  <si>
-    <t>体力消耗减少X点</t>
-  </si>
-  <si>
-    <t>体力消耗减少50%</t>
-  </si>
-  <si>
-    <t>回合结束时，专注+2</t>
-  </si>
-  <si>
-    <t>体力消耗增加50%</t>
-  </si>
-  <si>
-    <t>回合结束时，参数+4</t>
-  </si>
-  <si>
-    <t>幽默</t>
-  </si>
-  <si>
-    <t>营业</t>
-  </si>
-  <si>
-    <t>盐应对</t>
-  </si>
-  <si>
-    <t>好娇娇</t>
-  </si>
-  <si>
-    <t>每当使用A卡时，红温+1</t>
-  </si>
-  <si>
-    <t>OperatorType</t>
-  </si>
-  <si>
-    <t>NameOrID</t>
-  </si>
-  <si>
-    <t>TargetValue</t>
-  </si>
-  <si>
-    <t>TargetDelta</t>
-  </si>
-  <si>
-    <t>有红温时</t>
-  </si>
-  <si>
-    <t>VBuffLayerCondition</t>
-  </si>
-  <si>
-    <t>GreaterThan</t>
-  </si>
-  <si>
-    <t>使用M卡时</t>
-  </si>
-  <si>
-    <t>VCardTypeCondition</t>
-  </si>
-  <si>
-    <t>使用A卡时</t>
-  </si>
-  <si>
-    <t>当红温大于3层时</t>
-  </si>
-  <si>
-    <t>当专注大于4层时</t>
-  </si>
-  <si>
-    <t>当亲和力大于3层时</t>
-  </si>
-  <si>
-    <t>当红温大于10层时</t>
-  </si>
-  <si>
-    <t>当红温大于30层时</t>
-  </si>
-  <si>
-    <t>当红温大于50层时</t>
-  </si>
-  <si>
     <t>Param</t>
   </si>
   <si>
+    <t>safdsafsadfasdf</t>
+  </si>
+  <si>
+    <t>VRaisingAddAbilityEffect</t>
+  </si>
+  <si>
+    <t>CASingingAbility</t>
+  </si>
+  <si>
+    <t>DialogueNode</t>
+  </si>
+  <si>
     <t>AddSinging</t>
   </si>
   <si>
-    <t>safdsafsadfasdf</t>
-  </si>
-  <si>
-    <t>VRaisingAddAbilityEffect</t>
-  </si>
-  <si>
-    <t>CASingingAbility</t>
-  </si>
-  <si>
     <t>AddGaming</t>
   </si>
   <si>
+    <t>AddChatting</t>
+  </si>
+  <si>
+    <t>AddStamina</t>
+  </si>
+  <si>
     <t>CAGamingAbility</t>
   </si>
   <si>
-    <t>AddChatting</t>
-  </si>
-  <si>
     <t>CAChattingAbility</t>
   </si>
   <si>
-    <t>AddStamina</t>
-  </si>
-  <si>
     <t>VRaisingAddAttributeEffect</t>
   </si>
   <si>
     <t>CAStamina</t>
   </si>
   <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>Recovery</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>Stream1</t>
+  </si>
+  <si>
+    <t>Stream2</t>
+  </si>
+  <si>
+    <t>Stream3</t>
+  </si>
+  <si>
+    <t>DayOff!</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>DayOff</t>
+  </si>
+  <si>
+    <t>Recover 10 Stamina</t>
+  </si>
+  <si>
+    <t>Recover 20 Stamina</t>
+  </si>
+  <si>
+    <t>Recover 30 Stamina</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>BackGroundColor</t>
+  </si>
+  <si>
+    <t>#FFB200</t>
+  </si>
+  <si>
+    <t>#FF2160</t>
+  </si>
+  <si>
+    <t>#4B58FF</t>
+  </si>
+  <si>
+    <t>#00B050</t>
+  </si>
+  <si>
+    <t>#AB0580</t>
+  </si>
+  <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>TurnCount</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>SuccessEvent</t>
+  </si>
+  <si>
+    <t>FailEvent</t>
+  </si>
+  <si>
+    <t>InitialViewers</t>
+  </si>
+  <si>
     <t>AddPressure</t>
   </si>
   <si>
@@ -966,13 +980,31 @@
     <t>CAPressure</t>
   </si>
   <si>
+    <t>Add Money</t>
+  </si>
+  <si>
+    <t>CAMoney</t>
+  </si>
+  <si>
+    <t>StreamSuccess</t>
+  </si>
+  <si>
+    <t>StreamFail</t>
+  </si>
+  <si>
+    <t>#00B051</t>
+  </si>
+  <si>
+    <t>#00B052</t>
+  </si>
+  <si>
     <t>AddMoney</t>
   </si>
   <si>
-    <t>Add Money</t>
-  </si>
-  <si>
-    <t>CAMoney</t>
+    <t>#00B053</t>
+  </si>
+  <si>
+    <t>NoStamina</t>
   </si>
   <si>
     <t>SkipEvent</t>
@@ -981,10 +1013,19 @@
     <t>VRaisingSkipEventEffect</t>
   </si>
   <si>
+    <t>VRaisingModifyScheduleEffect</t>
+  </si>
+  <si>
     <t>ModifySchedule</t>
   </si>
   <si>
-    <t>VRaisingModifyScheduleEffect</t>
+    <t>OuttaStamina</t>
+  </si>
+  <si>
+    <t>sadf</t>
+  </si>
+  <si>
+    <t>Type_M</t>
   </si>
   <si>
     <t>AddRandomM</t>
@@ -993,278 +1034,82 @@
     <t>VRaisingAddRandomCardEffect</t>
   </si>
   <si>
-    <t>Type_M</t>
-  </si>
-  <si>
-    <t>sadf</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>BackGroundColor</t>
-  </si>
-  <si>
-    <t>DialogueNode</t>
-  </si>
-  <si>
-    <t>Practice</t>
-  </si>
-  <si>
-    <t>#FF2160</t>
-  </si>
-  <si>
-    <t>#4B58FF</t>
-  </si>
-  <si>
-    <t>#FFB200</t>
-  </si>
-  <si>
-    <t>Nap</t>
-  </si>
-  <si>
-    <t>Recover 10 Stamina</t>
-  </si>
-  <si>
-    <t>Recovery</t>
-  </si>
-  <si>
-    <t>#00B050</t>
-  </si>
-  <si>
-    <t>Break</t>
-  </si>
-  <si>
-    <t>Recover 20 Stamina</t>
-  </si>
-  <si>
-    <t>DayOff!</t>
-  </si>
-  <si>
-    <t>Recover 30 Stamina</t>
-  </si>
-  <si>
-    <t>DayOff</t>
-  </si>
-  <si>
-    <t>StreamSuccess</t>
-  </si>
-  <si>
-    <t>#00B051</t>
-  </si>
-  <si>
-    <t>StreamFail</t>
-  </si>
-  <si>
-    <t>#00B052</t>
-  </si>
-  <si>
-    <t>NoStamina</t>
-  </si>
-  <si>
-    <t>#00B053</t>
-  </si>
-  <si>
-    <t>OuttaStamina</t>
-  </si>
-  <si>
-    <t>TurnCount</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>InitialViewers</t>
-  </si>
-  <si>
-    <t>SuccessEvent</t>
-  </si>
-  <si>
-    <t>FailEvent</t>
-  </si>
-  <si>
-    <t>Stream1</t>
-  </si>
-  <si>
-    <t>Stream</t>
-  </si>
-  <si>
-    <t>#AB0580</t>
-  </si>
-  <si>
-    <t>Stream2</t>
-  </si>
-  <si>
-    <t>Stream3</t>
+    <t>DeleteRandomRare</t>
+  </si>
+  <si>
+    <t>VCardRarityCondition</t>
+  </si>
+  <si>
+    <t>VRaisingDeleteCardEffect</t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>VPhaseEndingAttributeCondition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASingingAbility </t>
+  </si>
+  <si>
+    <t>StreamEnding</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1273,7 +1118,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAB0580"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1303,198 +1154,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFAB0580"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1520,338 +1185,51 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2109,43 +1487,45 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AE62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="38.2166666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.425" customWidth="1"/>
-    <col min="5" max="5" width="13.425" customWidth="1"/>
-    <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" customWidth="1"/>
-    <col min="8" max="8" width="7.14166666666667" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
-    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" customWidth="1"/>
-    <col min="13" max="13" width="9.70833333333333" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.7083333333333" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
-    <col min="18" max="18" width="17.1416666666667" customWidth="1"/>
-    <col min="21" max="21" width="17.7083333333333" customWidth="1"/>
-    <col min="22" max="22" width="10.7083333333333" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="9" style="2"/>
+    <col min="21" max="21" width="17.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" style="2" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" customWidth="1"/>
-    <col min="25" max="26" width="12.425" customWidth="1"/>
-    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
-    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="3" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="12.28515625" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:31">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2167,10 +1547,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2182,46 +1562,46 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
@@ -2237,7 +1617,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:31">
+    <row r="2" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2256,10 +1636,10 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="2">
         <v>4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="3">
         <v>3</v>
       </c>
       <c r="J2">
@@ -2268,22 +1648,21 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="2">
         <v>11</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="3">
         <v>7</v>
       </c>
-      <c r="P2"/>
-      <c r="AC2" s="13"/>
+      <c r="AC2" s="4"/>
       <c r="AE2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:31">
+    <row r="3" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2302,10 +1681,10 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
         <v>0</v>
       </c>
       <c r="J3">
@@ -2314,22 +1693,21 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="2">
         <v>2</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="3">
         <v>4</v>
       </c>
-      <c r="P3"/>
-      <c r="AC3" s="13"/>
+      <c r="AC3" s="4"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" customFormat="1" hidden="1" spans="1:31">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2348,10 +1726,10 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="2">
         <v>5</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="3">
         <v>5</v>
       </c>
       <c r="J4">
@@ -2360,30 +1738,29 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="2">
         <v>11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="3">
         <v>15</v>
       </c>
-      <c r="P4"/>
-      <c r="AC4" s="13"/>
+      <c r="AC4" s="4"/>
       <c r="AE4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -2394,10 +1771,10 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="2">
         <v>3</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="3">
         <v>3</v>
       </c>
       <c r="J5">
@@ -2406,56 +1783,55 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="2">
         <v>11</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="3">
         <v>5</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="2">
         <v>2</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
-      <c r="R5" s="12">
-        <v>2</v>
-      </c>
-      <c r="S5"/>
-      <c r="AC5" s="13"/>
+      <c r="R5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="4"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="1" hidden="1" spans="1:31">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2464,26 +1840,26 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13"/>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4"/>
       <c r="AE6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>49</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -2491,46 +1867,27 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="2">
         <v>5</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="3">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2">
         <v>4</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="M7" s="10">
-        <v>4</v>
-      </c>
-      <c r="P7" s="10">
-        <v>21</v>
-      </c>
-      <c r="Q7">
-        <v>2</v>
-      </c>
-      <c r="R7" s="12">
-        <v>2</v>
-      </c>
-      <c r="S7" s="10">
-        <v>14</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7" s="12">
-        <v>1</v>
-      </c>
-      <c r="V7"/>
-      <c r="AC7" s="13"/>
+      <c r="AC7" s="4"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="1" hidden="1" spans="1:31">
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2541,21 +1898,21 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2564,42 +1921,41 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="2">
         <v>2</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="3">
         <v>7</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="2">
         <v>3</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8" s="12">
-        <v>1</v>
-      </c>
-      <c r="S8" s="10">
+      <c r="R8" s="3">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2">
         <v>14</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="12">
-        <v>1</v>
-      </c>
-      <c r="V8"/>
-      <c r="AC8" s="13"/>
+      <c r="U8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="4"/>
       <c r="AE8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" customFormat="1" hidden="1" spans="1:31">
+    <row r="9" spans="1:31">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>53</v>
@@ -2616,45 +1972,44 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="10">
-        <v>2</v>
-      </c>
-      <c r="I9" s="12">
-        <v>2</v>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2">
+        <v>17</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3">
         <v>6</v>
       </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
-      <c r="O9" s="12">
-        <v>4</v>
-      </c>
-      <c r="P9" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <v>3</v>
-      </c>
-      <c r="R9" s="12">
-        <v>4</v>
-      </c>
-      <c r="S9"/>
-      <c r="AC9" s="13"/>
+      <c r="AC9" s="4"/>
       <c r="AE9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>55</v>
@@ -2671,10 +2026,10 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="10">
-        <v>2</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="3">
         <v>2</v>
       </c>
       <c r="J10">
@@ -2683,33 +2038,32 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="M10" s="10">
-        <v>7</v>
+      <c r="M10" s="2">
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>2</v>
-      </c>
-      <c r="O10" s="12">
         <v>3</v>
       </c>
-      <c r="P10" s="10">
+      <c r="O10" s="3">
+        <v>4</v>
+      </c>
+      <c r="P10" s="2">
         <v>2</v>
       </c>
       <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10" s="12">
         <v>3</v>
       </c>
-      <c r="S10"/>
-      <c r="AC10" s="13"/>
+      <c r="R10" s="3">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="4"/>
       <c r="AE10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>57</v>
@@ -2726,10 +2080,10 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="10">
-        <v>2</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2738,33 +2092,32 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="M11" s="10">
-        <v>15</v>
+      <c r="M11" s="2">
+        <v>7</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="3">
         <v>3</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="2">
         <v>2</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="3">
         <v>3</v>
       </c>
-      <c r="S11"/>
-      <c r="AC11" s="13"/>
+      <c r="AC11" s="4"/>
       <c r="AE11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
@@ -2776,53 +2129,49 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="10">
-        <v>6</v>
-      </c>
-      <c r="I12" s="12">
-        <v>6</v>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="2">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>3</v>
+      </c>
+      <c r="P12" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="4"/>
+      <c r="AE12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="A13">
         <v>11</v>
-      </c>
-      <c r="N12">
-        <v>9</v>
-      </c>
-      <c r="O12" s="12">
-        <v>13</v>
-      </c>
-      <c r="P12" s="10">
-        <v>11</v>
-      </c>
-      <c r="Q12">
-        <v>9</v>
-      </c>
-      <c r="R12" s="12">
-        <v>13</v>
-      </c>
-      <c r="S12"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:31">
-      <c r="A13">
-        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>62</v>
@@ -2831,7 +2180,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -2839,46 +2188,47 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="10">
-        <v>5</v>
-      </c>
-      <c r="I13" s="12">
-        <v>5</v>
+      <c r="H13" s="2">
+        <v>6</v>
+      </c>
+      <c r="I13" s="3">
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="2">
         <v>11</v>
       </c>
       <c r="N13">
+        <v>9</v>
+      </c>
+      <c r="O13" s="3">
+        <v>13</v>
+      </c>
+      <c r="P13" s="2">
         <v>11</v>
       </c>
-      <c r="O13" s="12">
-        <v>15</v>
-      </c>
-      <c r="P13" s="10">
-        <v>2</v>
-      </c>
       <c r="Q13">
-        <v>7</v>
-      </c>
-      <c r="R13" s="12">
         <v>9</v>
       </c>
-      <c r="S13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13"/>
+      <c r="R13" s="3">
+        <v>13</v>
+      </c>
+      <c r="AC13" s="4"/>
+      <c r="AD13" t="s">
+        <v>64</v>
+      </c>
       <c r="AE13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" customFormat="1" hidden="1" spans="1:31">
+    <row r="14" spans="1:31">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>65</v>
@@ -2887,19 +2237,19 @@
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="12">
-        <v>4</v>
+      <c r="I14" s="3">
+        <v>5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2907,27 +2257,32 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="M14" s="10">
-        <v>6</v>
+      <c r="M14" s="2">
+        <v>11</v>
       </c>
       <c r="N14">
-        <v>6</v>
-      </c>
-      <c r="O14" s="12">
-        <v>8</v>
-      </c>
-      <c r="P14"/>
-      <c r="Q14"/>
-      <c r="R14"/>
-      <c r="S14"/>
-      <c r="AC14" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="O14" s="3">
+        <v>15</v>
+      </c>
+      <c r="P14" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q14">
+        <v>7</v>
+      </c>
+      <c r="R14" s="3">
+        <v>9</v>
+      </c>
+      <c r="AC14" s="4"/>
       <c r="AE14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>67</v>
@@ -2936,44 +2291,43 @@
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="2">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3">
         <v>4</v>
       </c>
-      <c r="I15" s="12">
-        <v>4</v>
-      </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="M15" s="10">
-        <v>18</v>
+      <c r="M15" s="2">
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>1.4</v>
-      </c>
-      <c r="O15" s="12">
-        <v>1.8</v>
-      </c>
-      <c r="P15"/>
-      <c r="AC15" s="13"/>
+        <v>6</v>
+      </c>
+      <c r="O15" s="3">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="4"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="1" hidden="1" spans="1:31">
+    <row r="16" spans="1:31">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>69</v>
@@ -2982,7 +2336,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -2990,45 +2344,35 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="10">
-        <v>6</v>
-      </c>
-      <c r="I16" s="12">
-        <v>5</v>
+      <c r="H16" s="2">
+        <v>4</v>
+      </c>
+      <c r="I16" s="3">
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="M16" s="10">
-        <v>6</v>
+      <c r="M16" s="2">
+        <v>18</v>
       </c>
       <c r="N16">
-        <v>4</v>
-      </c>
-      <c r="O16" s="12">
-        <v>5</v>
-      </c>
-      <c r="P16" s="10">
-        <v>18</v>
-      </c>
-      <c r="Q16">
-        <v>0.8</v>
-      </c>
-      <c r="R16" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="S16"/>
-      <c r="AC16" s="13"/>
+        <v>1.4</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" s="4"/>
       <c r="AE16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:31">
+    <row r="17" spans="1:31">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
@@ -3037,62 +2381,52 @@
         <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="10">
-        <v>3</v>
-      </c>
-      <c r="I17" s="12">
-        <v>3</v>
+      <c r="H17" s="2">
+        <v>6</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="M17" s="10">
-        <v>19</v>
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17" s="12">
-        <v>1</v>
-      </c>
-      <c r="P17" s="10">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="O17" s="3">
+        <v>5</v>
+      </c>
+      <c r="P17" s="2">
+        <v>18</v>
       </c>
       <c r="Q17">
-        <v>4</v>
-      </c>
-      <c r="R17" s="12">
-        <v>6</v>
-      </c>
-      <c r="S17" s="10">
-        <v>21</v>
-      </c>
-      <c r="T17">
-        <v>2</v>
-      </c>
-      <c r="U17" s="12">
-        <v>3</v>
-      </c>
-      <c r="V17"/>
-      <c r="AC17" s="14"/>
+        <v>0.8</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AC17" s="4"/>
       <c r="AE17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31">
       <c r="A18">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>73</v>
@@ -3101,7 +2435,7 @@
         <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
@@ -3109,51 +2443,62 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="2">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2">
+        <v>19</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q18">
         <v>4</v>
       </c>
-      <c r="I18" s="12">
+      <c r="R18" s="3">
+        <v>6</v>
+      </c>
+      <c r="S18" s="2">
+        <v>21</v>
+      </c>
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18" s="3">
         <v>3</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="M18" s="10">
-        <v>15</v>
-      </c>
-      <c r="N18">
-        <v>5</v>
-      </c>
-      <c r="O18" s="12">
-        <v>7</v>
-      </c>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18"/>
-      <c r="S18"/>
-      <c r="T18"/>
-      <c r="U18"/>
-      <c r="V18"/>
-      <c r="AC18" s="13"/>
+      <c r="AC18" s="5"/>
       <c r="AE18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31">
       <c r="A19">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -3161,66 +2506,50 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="2">
+        <v>6</v>
+      </c>
+      <c r="I19" s="3">
         <v>5</v>
       </c>
-      <c r="I19" s="12">
-        <v>4</v>
-      </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="M19" s="10">
-        <v>23</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19" s="12">
-        <v>1</v>
-      </c>
-      <c r="P19" s="10">
-        <v>7</v>
-      </c>
-      <c r="Q19">
-        <v>1</v>
-      </c>
-      <c r="R19" s="12">
-        <v>2</v>
-      </c>
-      <c r="S19"/>
-      <c r="AC19" s="13"/>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="4"/>
       <c r="AE19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31">
       <c r="A20">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
         <v>77</v>
       </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="10">
-        <v>6</v>
-      </c>
-      <c r="I20" s="12">
-        <v>6</v>
+      <c r="H20" s="2">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>3</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -3228,268 +2557,248 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" s="10">
-        <v>11</v>
+      <c r="M20" s="2">
+        <v>15</v>
       </c>
       <c r="N20">
-        <v>24</v>
-      </c>
-      <c r="O20" s="12">
-        <v>30</v>
-      </c>
-      <c r="P20"/>
-      <c r="AC20" s="14"/>
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
+        <v>7</v>
+      </c>
+      <c r="AC20" s="4"/>
       <c r="AE20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="2">
         <v>5</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="3">
         <v>4</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="M21" s="10">
-        <v>26</v>
+      <c r="M21" s="2">
+        <v>23</v>
       </c>
       <c r="N21">
-        <v>2</v>
-      </c>
-      <c r="O21" s="12">
-        <v>2</v>
-      </c>
-      <c r="P21" s="10">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2">
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>30</v>
-      </c>
-      <c r="R21" s="12">
-        <v>42</v>
-      </c>
-      <c r="S21" s="10">
-        <v>2</v>
-      </c>
-      <c r="T21">
-        <v>5</v>
-      </c>
-      <c r="U21" s="12">
-        <v>7</v>
-      </c>
-      <c r="V21"/>
-      <c r="AC21" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="R21" s="3">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="4"/>
       <c r="AE21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31">
       <c r="A22">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
         <v>81</v>
       </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="10">
-        <v>4</v>
-      </c>
-      <c r="I22" s="12">
-        <v>4</v>
+      <c r="H22" s="2">
+        <v>6</v>
+      </c>
+      <c r="I22" s="3">
+        <v>6</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="M22" s="10">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>24</v>
       </c>
       <c r="N22">
-        <v>2</v>
-      </c>
-      <c r="O22" s="12">
-        <v>4</v>
-      </c>
-      <c r="P22" s="10">
-        <v>28</v>
-      </c>
-      <c r="Q22">
-        <v>1</v>
-      </c>
-      <c r="R22" s="12">
-        <v>1</v>
-      </c>
-      <c r="S22"/>
-      <c r="AC22" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="O22" s="3">
+        <v>30</v>
+      </c>
+      <c r="AC22" s="5"/>
       <c r="AE22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" hidden="1" spans="1:31">
-      <c r="A23">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" t="s">
-        <v>38</v>
       </c>
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="10">
-        <v>1</v>
-      </c>
-      <c r="I23" s="12">
-        <v>1</v>
+      <c r="H23" s="2">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="M23" s="10">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="M23" s="2">
+        <v>26</v>
       </c>
       <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" s="3">
+        <v>2</v>
+      </c>
+      <c r="P23" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q23">
+        <v>30</v>
+      </c>
+      <c r="R23" s="3">
+        <v>42</v>
+      </c>
+      <c r="S23" s="2">
+        <v>2</v>
+      </c>
+      <c r="T23">
         <v>5</v>
       </c>
-      <c r="O23" s="12">
+      <c r="U23" s="3">
         <v>7</v>
       </c>
-      <c r="P23" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q23">
-        <v>1</v>
-      </c>
-      <c r="R23" s="12">
-        <v>1</v>
-      </c>
-      <c r="S23"/>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23"/>
-      <c r="AC23" s="13"/>
+      <c r="AC23" s="4"/>
       <c r="AE23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31">
       <c r="A24">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
         <v>85</v>
       </c>
-      <c r="C24" t="s">
-        <v>86</v>
-      </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="2">
         <v>4</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="3">
         <v>4</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="M24" s="10">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="M24" s="2">
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>3</v>
-      </c>
-      <c r="O24" s="12">
+        <v>2</v>
+      </c>
+      <c r="O24" s="3">
         <v>4</v>
       </c>
-      <c r="P24" s="10">
-        <v>11</v>
+      <c r="P24" s="2">
+        <v>28</v>
       </c>
       <c r="Q24">
-        <v>8</v>
-      </c>
-      <c r="R24" s="12">
-        <v>11</v>
-      </c>
-      <c r="S24"/>
-      <c r="AC24" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="4"/>
       <c r="AE24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31">
       <c r="A25">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
-        <v>88</v>
-      </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
         <v>38</v>
@@ -3497,60 +2806,65 @@
       <c r="F25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="10">
-        <v>3</v>
-      </c>
-      <c r="I25" s="12">
-        <v>2</v>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="2">
+        <v>6</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25" s="3">
         <v>7</v>
       </c>
-      <c r="N25">
-        <v>3</v>
-      </c>
-      <c r="O25" s="12">
-        <v>5</v>
-      </c>
-      <c r="P25"/>
-      <c r="Q25"/>
-      <c r="R25"/>
-      <c r="S25"/>
-      <c r="AC25" s="13"/>
+      <c r="P25" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="4"/>
       <c r="AE25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31">
       <c r="A26">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
         <v>89</v>
       </c>
-      <c r="C26" t="s">
-        <v>90</v>
-      </c>
       <c r="D26" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="10">
-        <v>3</v>
-      </c>
-      <c r="I26" s="12">
-        <v>2</v>
+      <c r="H26" s="2">
+        <v>4</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3558,106 +2872,83 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="M26" s="10">
-        <v>7</v>
+      <c r="M26" s="2">
+        <v>15</v>
       </c>
       <c r="N26">
         <v>3</v>
       </c>
-      <c r="O26" s="12">
+      <c r="O26" s="3">
         <v>4</v>
       </c>
-      <c r="P26" s="10">
-        <v>2</v>
+      <c r="P26" s="2">
+        <v>11</v>
       </c>
       <c r="Q26">
-        <v>4</v>
-      </c>
-      <c r="R26" s="12">
-        <v>6</v>
-      </c>
-      <c r="S26"/>
-      <c r="AC26" s="13"/>
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
+        <v>11</v>
+      </c>
+      <c r="AC26" s="4"/>
       <c r="AE26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31">
       <c r="A27">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
         <v>91</v>
       </c>
-      <c r="C27" t="s">
-        <v>92</v>
-      </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="10">
-        <v>8</v>
-      </c>
-      <c r="I27" s="12">
-        <v>6</v>
+      <c r="H27" s="2">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" s="10">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>7</v>
       </c>
       <c r="N27">
-        <v>12</v>
-      </c>
-      <c r="O27" s="12">
-        <v>18</v>
-      </c>
-      <c r="P27" s="10">
-        <v>56</v>
-      </c>
-      <c r="Q27">
-        <v>24</v>
-      </c>
-      <c r="R27" s="12">
-        <v>30</v>
-      </c>
-      <c r="S27" s="10">
-        <v>57</v>
-      </c>
-      <c r="T27">
-        <v>36</v>
-      </c>
-      <c r="U27" s="12">
-        <v>44</v>
-      </c>
-      <c r="V27"/>
-      <c r="AC27" s="14"/>
+        <v>3</v>
+      </c>
+      <c r="O27" s="3">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="4"/>
       <c r="AE27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31">
       <c r="A28">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
         <v>93</v>
-      </c>
-      <c r="C28" t="s">
-        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -3668,112 +2959,116 @@
       <c r="F28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="10">
-        <v>1</v>
-      </c>
-      <c r="I28" s="12">
-        <v>0</v>
+      <c r="H28" s="2">
+        <v>3</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="M28" s="10">
-        <v>2</v>
+      <c r="M28" s="2">
+        <v>7</v>
       </c>
       <c r="N28">
+        <v>3</v>
+      </c>
+      <c r="O28" s="3">
+        <v>4</v>
+      </c>
+      <c r="P28" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>4</v>
+      </c>
+      <c r="R28" s="3">
         <v>6</v>
       </c>
-      <c r="O28" s="12">
-        <v>8</v>
-      </c>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="AC28" s="13"/>
+      <c r="AC28" s="4"/>
       <c r="AE28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31">
       <c r="A29">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
         <v>95</v>
       </c>
-      <c r="C29" t="s">
-        <v>96</v>
-      </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="2">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3">
+        <v>8</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="M29" s="2">
+        <v>15</v>
+      </c>
+      <c r="N29">
         <v>5</v>
       </c>
-      <c r="I29" s="12">
-        <v>5</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="M29" s="10">
+      <c r="O29" s="3">
+        <v>7</v>
+      </c>
+      <c r="P29" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1</v>
+      </c>
+      <c r="S29" s="2">
+        <v>31</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="5"/>
+      <c r="AE29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
         <v>32</v>
-      </c>
-      <c r="N29">
-        <v>30</v>
-      </c>
-      <c r="O29" s="12">
-        <v>30</v>
-      </c>
-      <c r="P29" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q29">
-        <v>3</v>
-      </c>
-      <c r="R29" s="12">
-        <v>5</v>
-      </c>
-      <c r="S29" s="10">
-        <v>21</v>
-      </c>
-      <c r="T29">
-        <v>2</v>
-      </c>
-      <c r="U29" s="12">
-        <v>3</v>
-      </c>
-      <c r="V29"/>
-      <c r="AC29" s="13"/>
-      <c r="AE29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:31">
-      <c r="A30">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>64</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
@@ -3781,112 +3076,107 @@
       <c r="F30" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="10">
-        <v>4</v>
-      </c>
-      <c r="I30" s="12">
-        <v>4</v>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="M30" s="10">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>2</v>
       </c>
       <c r="N30">
-        <v>50</v>
-      </c>
-      <c r="O30" s="12">
-        <v>70</v>
-      </c>
-      <c r="P30" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q30">
-        <v>2</v>
-      </c>
-      <c r="R30" s="12">
-        <v>4</v>
-      </c>
-      <c r="S30"/>
-      <c r="AC30" s="14"/>
+        <v>6</v>
+      </c>
+      <c r="O30" s="3">
+        <v>8</v>
+      </c>
+      <c r="AC30" s="4"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:31">
+    <row r="31" spans="1:31">
       <c r="A31">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" t="s">
         <v>99</v>
       </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="2">
+        <v>6</v>
+      </c>
+      <c r="I31" s="3">
+        <v>5</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="M31" s="2">
+        <v>19</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31" s="3">
+        <v>1</v>
+      </c>
+      <c r="P31" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q31">
         <v>4</v>
       </c>
-      <c r="I31" s="12">
-        <v>3</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="M31" s="10">
-        <v>33</v>
-      </c>
-      <c r="N31">
-        <v>20</v>
-      </c>
-      <c r="O31" s="12">
-        <v>30</v>
-      </c>
-      <c r="P31" s="10">
-        <v>35</v>
-      </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="R31" s="12">
-        <v>1</v>
-      </c>
-      <c r="S31"/>
-      <c r="T31"/>
-      <c r="U31"/>
-      <c r="V31"/>
-      <c r="AC31" s="14"/>
+      <c r="R31" s="3">
+        <v>7</v>
+      </c>
+      <c r="S31" s="2">
+        <v>14</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="5"/>
       <c r="AE31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:31">
+    <row r="32" spans="1:31">
       <c r="A32">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
         <v>101</v>
       </c>
-      <c r="C32" t="s">
-        <v>102</v>
-      </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
         <v>38</v>
@@ -3894,11 +3184,11 @@
       <c r="F32" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="10">
-        <v>7</v>
-      </c>
-      <c r="I32" s="12">
-        <v>6</v>
+      <c r="H32" s="2">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>5</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3906,34 +3196,62 @@
       <c r="K32">
         <v>1</v>
       </c>
+      <c r="M32" s="2">
+        <v>32</v>
+      </c>
+      <c r="N32">
+        <v>30</v>
+      </c>
+      <c r="O32" s="3">
+        <v>30</v>
+      </c>
+      <c r="P32" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q32">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
+        <v>5</v>
+      </c>
+      <c r="S32" s="2">
+        <v>21</v>
+      </c>
+      <c r="T32">
+        <v>2</v>
+      </c>
+      <c r="U32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="4"/>
       <c r="AE32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" customFormat="1" hidden="1" spans="1:31">
+    <row r="33" spans="1:31">
       <c r="A33">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
         <v>103</v>
       </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="10">
-        <v>8</v>
-      </c>
-      <c r="I33" s="12">
-        <v>7</v>
+      <c r="H33" s="2">
+        <v>4</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -3941,35 +3259,41 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" s="10">
-        <v>11</v>
+      <c r="M33" s="2">
+        <v>33</v>
       </c>
       <c r="N33">
-        <v>38</v>
-      </c>
-      <c r="O33" s="12">
-        <v>52</v>
-      </c>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
+        <v>50</v>
+      </c>
+      <c r="O33" s="3">
+        <v>70</v>
+      </c>
+      <c r="P33" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q33">
+        <v>2</v>
+      </c>
+      <c r="R33" s="3">
+        <v>4</v>
+      </c>
+      <c r="AC33" s="5"/>
       <c r="AE33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31">
       <c r="A34">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="s">
         <v>105</v>
       </c>
-      <c r="C34" t="s">
-        <v>106</v>
-      </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
@@ -3977,140 +3301,123 @@
       <c r="F34" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="2">
+        <v>4</v>
+      </c>
+      <c r="I34" s="3">
         <v>3</v>
       </c>
-      <c r="I34" s="12">
-        <v>3</v>
-      </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="10">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="M34" s="2">
+        <v>33</v>
       </c>
       <c r="N34">
-        <v>3</v>
-      </c>
-      <c r="O34" s="12">
-        <v>4</v>
-      </c>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
+        <v>20</v>
+      </c>
+      <c r="O34" s="3">
+        <v>30</v>
+      </c>
+      <c r="P34" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="5"/>
       <c r="AE34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31">
       <c r="A35">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
         <v>107</v>
       </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E35" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="10">
-        <v>3</v>
-      </c>
-      <c r="I35" s="12">
-        <v>3</v>
+      <c r="H35" s="2">
+        <v>7</v>
+      </c>
+      <c r="I35" s="3">
+        <v>6</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="M35" s="10">
-        <v>11</v>
-      </c>
-      <c r="N35">
-        <v>18</v>
-      </c>
-      <c r="O35" s="12">
-        <v>22</v>
-      </c>
-      <c r="P35"/>
+        <v>1</v>
+      </c>
       <c r="AE35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31">
       <c r="A36">
-        <v>37</v>
-      </c>
-      <c r="B36" s="11">
-        <v>144</v>
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
       </c>
       <c r="C36" t="s">
         <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="10">
-        <v>3</v>
-      </c>
-      <c r="I36" s="12">
-        <v>3</v>
+      <c r="H36" s="2">
+        <v>8</v>
+      </c>
+      <c r="I36" s="3">
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="M36" s="10">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="M36" s="2">
+        <v>11</v>
       </c>
       <c r="N36">
-        <v>3</v>
-      </c>
-      <c r="O36" s="12">
-        <v>4</v>
-      </c>
-      <c r="P36" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q36">
-        <v>6</v>
-      </c>
-      <c r="R36" s="12">
-        <v>8</v>
-      </c>
-      <c r="S36"/>
+        <v>42</v>
+      </c>
+      <c r="O36" s="3">
+        <v>54</v>
+      </c>
       <c r="AE36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31">
       <c r="A37">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>110</v>
@@ -4119,7 +3426,7 @@
         <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E37" t="s">
         <v>38</v>
@@ -4127,44 +3434,43 @@
       <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="2">
         <v>3</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="3">
         <v>3</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="M37" s="10">
-        <v>7</v>
+      <c r="M37" s="2">
+        <v>37</v>
       </c>
       <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" s="3">
+        <v>2</v>
+      </c>
+      <c r="P37" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q37">
         <v>3</v>
       </c>
-      <c r="O37" s="12">
+      <c r="R37" s="3">
         <v>4</v>
       </c>
-      <c r="P37" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q37">
-        <v>6</v>
-      </c>
-      <c r="R37" s="12">
-        <v>8</v>
-      </c>
-      <c r="S37"/>
       <c r="AE37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:31">
+    <row r="38" spans="1:31">
       <c r="A38">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>112</v>
@@ -4173,61 +3479,51 @@
         <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="10">
-        <v>1</v>
-      </c>
-      <c r="I38" s="12">
-        <v>1</v>
+      <c r="H38" s="2">
+        <v>3</v>
+      </c>
+      <c r="I38" s="3">
+        <v>3</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38">
-        <v>1</v>
-      </c>
-      <c r="M38" s="10">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>11</v>
       </c>
       <c r="N38">
-        <v>4</v>
-      </c>
-      <c r="O38" s="12">
-        <v>5</v>
-      </c>
-      <c r="P38" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q38">
-        <v>3</v>
-      </c>
-      <c r="R38" s="12">
-        <v>5</v>
-      </c>
-      <c r="S38"/>
+        <v>18</v>
+      </c>
+      <c r="O38" s="3">
+        <v>22</v>
+      </c>
       <c r="AE38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:31">
+    <row r="39" spans="1:31">
       <c r="A39">
-        <v>40</v>
-      </c>
-      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>144</v>
+      </c>
+      <c r="C39" t="s">
         <v>114</v>
       </c>
-      <c r="C39" t="s">
-        <v>115</v>
-      </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -4235,53 +3531,52 @@
       <c r="F39" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="10">
-        <v>1</v>
-      </c>
-      <c r="I39" s="12">
-        <v>1</v>
+      <c r="H39" s="2">
+        <v>3</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
-        <v>1</v>
-      </c>
-      <c r="M39" s="10">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>15</v>
       </c>
       <c r="N39">
-        <v>1</v>
-      </c>
-      <c r="O39" s="12">
-        <v>2</v>
-      </c>
-      <c r="P39" s="10">
+        <v>3</v>
+      </c>
+      <c r="O39" s="3">
+        <v>4</v>
+      </c>
+      <c r="P39" s="2">
         <v>2</v>
       </c>
       <c r="Q39">
         <v>6</v>
       </c>
-      <c r="R39" s="12">
-        <v>7</v>
-      </c>
-      <c r="S39"/>
+      <c r="R39" s="3">
+        <v>8</v>
+      </c>
       <c r="AE39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31">
       <c r="A40">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" t="s">
         <v>116</v>
       </c>
-      <c r="C40" t="s">
-        <v>117</v>
-      </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -4289,53 +3584,52 @@
       <c r="F40" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="2">
+        <v>3</v>
+      </c>
+      <c r="I40" s="3">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>7</v>
+      </c>
+      <c r="N40">
+        <v>3</v>
+      </c>
+      <c r="O40" s="3">
         <v>4</v>
       </c>
-      <c r="I40" s="12">
-        <v>3</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="M40" s="10">
-        <v>7</v>
-      </c>
-      <c r="N40">
-        <v>4</v>
-      </c>
-      <c r="O40" s="12">
-        <v>5</v>
-      </c>
-      <c r="P40" s="10">
-        <v>38</v>
+      <c r="P40" s="2">
+        <v>2</v>
       </c>
       <c r="Q40">
-        <v>4</v>
-      </c>
-      <c r="R40" s="12">
-        <v>5</v>
-      </c>
-      <c r="S40"/>
+        <v>6</v>
+      </c>
+      <c r="R40" s="3">
+        <v>8</v>
+      </c>
       <c r="AE40" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" customFormat="1" hidden="1" spans="1:31">
+    <row r="41" spans="1:31">
       <c r="A41">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" t="s">
         <v>118</v>
       </c>
-      <c r="C41" t="s">
-        <v>119</v>
-      </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
         <v>38</v>
@@ -4343,53 +3637,52 @@
       <c r="F41" t="s">
         <v>34</v>
       </c>
-      <c r="H41" s="10">
-        <v>2</v>
-      </c>
-      <c r="I41" s="12">
-        <v>2</v>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="M41" s="10">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="M41" s="2">
+        <v>21</v>
       </c>
       <c r="N41">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
+        <v>5</v>
+      </c>
+      <c r="P41" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q41">
         <v>3</v>
       </c>
-      <c r="O41" s="12">
-        <v>3</v>
-      </c>
-      <c r="P41" s="10">
-        <v>39</v>
-      </c>
-      <c r="Q41">
-        <v>2</v>
-      </c>
-      <c r="R41" s="12">
-        <v>3</v>
-      </c>
-      <c r="S41"/>
+      <c r="R41" s="3">
+        <v>5</v>
+      </c>
       <c r="AE41" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31">
       <c r="A42">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" t="s">
         <v>120</v>
       </c>
-      <c r="C42" t="s">
-        <v>121</v>
-      </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
@@ -4397,11 +3690,11 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="10">
-        <v>4</v>
-      </c>
-      <c r="I42" s="12">
-        <v>3</v>
+      <c r="H42" s="2">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -4409,158 +3702,146 @@
       <c r="K42">
         <v>1</v>
       </c>
-      <c r="M42" s="10">
+      <c r="M42" s="2">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42" s="3">
+        <v>2</v>
+      </c>
+      <c r="P42" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q42">
+        <v>6</v>
+      </c>
+      <c r="R42" s="3">
         <v>7</v>
       </c>
-      <c r="N42">
-        <v>1</v>
-      </c>
-      <c r="O42" s="12">
-        <v>3</v>
-      </c>
-      <c r="P42" s="10">
+      <c r="AE42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31">
+      <c r="A43">
         <v>41</v>
       </c>
-      <c r="Q42">
-        <v>1</v>
-      </c>
-      <c r="R42" s="12">
-        <v>1</v>
-      </c>
-      <c r="S42"/>
-      <c r="AE42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" hidden="1" spans="1:31">
-      <c r="A43">
-        <v>44</v>
-      </c>
       <c r="B43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" t="s">
         <v>122</v>
       </c>
-      <c r="C43" t="s">
-        <v>123</v>
-      </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="2">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="M43" s="2">
         <v>7</v>
       </c>
-      <c r="I43" s="12">
+      <c r="N43">
         <v>4</v>
       </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="M43" s="10">
-        <v>6</v>
-      </c>
-      <c r="N43">
+      <c r="O43" s="3">
         <v>5</v>
       </c>
-      <c r="O43" s="12">
+      <c r="P43" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q43">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>5</v>
       </c>
-      <c r="P43" s="10">
-        <v>14</v>
-      </c>
-      <c r="Q43">
-        <v>1</v>
-      </c>
-      <c r="R43" s="12">
-        <v>1</v>
-      </c>
-      <c r="S43" s="10">
-        <v>18</v>
-      </c>
-      <c r="T43">
-        <v>0.9</v>
-      </c>
-      <c r="U43" s="12">
-        <v>1.2</v>
-      </c>
-      <c r="V43"/>
       <c r="AE43" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31">
       <c r="A44">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" t="s">
         <v>124</v>
       </c>
-      <c r="C44" t="s">
-        <v>125</v>
-      </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="2">
+        <v>2</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2">
         <v>6</v>
       </c>
-      <c r="I44" s="12">
-        <v>4</v>
-      </c>
-      <c r="J44">
-        <v>1</v>
-      </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-      <c r="M44" s="10">
-        <v>15</v>
-      </c>
       <c r="N44">
-        <v>2</v>
-      </c>
-      <c r="O44" s="12">
-        <v>2</v>
-      </c>
-      <c r="P44" s="10">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="O44" s="3">
+        <v>3</v>
+      </c>
+      <c r="P44" s="2">
+        <v>39</v>
       </c>
       <c r="Q44">
-        <v>8</v>
-      </c>
-      <c r="R44" s="12">
-        <v>12</v>
-      </c>
-      <c r="S44"/>
+        <v>2</v>
+      </c>
+      <c r="R44" s="3">
+        <v>3</v>
+      </c>
       <c r="AE44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31">
       <c r="A45">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" t="s">
         <v>126</v>
       </c>
-      <c r="C45" t="s">
-        <v>127</v>
-      </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -4568,125 +3849,114 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" s="10">
-        <v>5</v>
-      </c>
-      <c r="I45" s="12">
+      <c r="H45" s="2">
         <v>4</v>
       </c>
+      <c r="I45" s="3">
+        <v>3</v>
+      </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="M45" s="10">
+      <c r="M45" s="2">
         <v>7</v>
       </c>
       <c r="N45">
-        <v>7</v>
-      </c>
-      <c r="O45" s="12">
-        <v>9</v>
-      </c>
-      <c r="P45" s="10">
-        <v>26</v>
+        <v>1</v>
+      </c>
+      <c r="O45" s="3">
+        <v>3</v>
+      </c>
+      <c r="P45" s="2">
+        <v>41</v>
       </c>
       <c r="Q45">
-        <v>2</v>
-      </c>
-      <c r="R45" s="12">
-        <v>2</v>
-      </c>
-      <c r="S45" s="10">
-        <v>2</v>
-      </c>
-      <c r="T45">
-        <v>7</v>
-      </c>
-      <c r="U45" s="12">
-        <v>8</v>
-      </c>
-      <c r="V45"/>
+        <v>1</v>
+      </c>
+      <c r="R45" s="3">
+        <v>1</v>
+      </c>
       <c r="AE45" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:31">
+    <row r="46" spans="1:31">
       <c r="A46">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" t="s">
         <v>128</v>
       </c>
-      <c r="C46" t="s">
-        <v>129</v>
-      </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="10">
-        <v>10</v>
-      </c>
-      <c r="I46" s="12">
+      <c r="H46" s="2">
+        <v>7</v>
+      </c>
+      <c r="I46" s="3">
+        <v>4</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2">
         <v>6</v>
       </c>
-      <c r="J46">
-        <v>1</v>
-      </c>
-      <c r="K46">
-        <v>1</v>
-      </c>
-      <c r="M46" s="10">
-        <v>32</v>
-      </c>
       <c r="N46">
-        <v>40</v>
-      </c>
-      <c r="O46" s="12">
-        <v>40</v>
-      </c>
-      <c r="P46" s="10">
+        <v>5</v>
+      </c>
+      <c r="O46" s="3">
+        <v>5</v>
+      </c>
+      <c r="P46" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46" s="3">
+        <v>1</v>
+      </c>
+      <c r="S46" s="2">
+        <v>18</v>
+      </c>
+      <c r="T46">
+        <v>0.9</v>
+      </c>
+      <c r="U46" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="AE46" t="s">
         <v>33</v>
       </c>
-      <c r="Q46">
-        <v>30</v>
-      </c>
-      <c r="R46" s="12">
-        <v>30</v>
-      </c>
-      <c r="S46" s="10">
-        <v>19</v>
-      </c>
-      <c r="T46">
-        <v>1</v>
-      </c>
-      <c r="U46" s="12">
-        <v>1</v>
-      </c>
-      <c r="V46"/>
-      <c r="AE46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" hidden="1" spans="1:31">
+    </row>
+    <row r="47" spans="1:31">
       <c r="A47">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" t="s">
         <v>130</v>
       </c>
-      <c r="C47" t="s">
-        <v>131</v>
-      </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E47" t="s">
         <v>33</v>
@@ -4694,93 +3964,105 @@
       <c r="F47" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="10">
-        <v>2</v>
-      </c>
-      <c r="I47" s="12">
-        <v>1</v>
+      <c r="H47" s="2">
+        <v>6</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="M47" s="10">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="M47" s="2">
+        <v>15</v>
       </c>
       <c r="N47">
-        <v>10</v>
-      </c>
-      <c r="O47" s="12">
-        <v>14</v>
-      </c>
-      <c r="P47"/>
-      <c r="Q47"/>
-      <c r="R47"/>
-      <c r="S47"/>
+        <v>2</v>
+      </c>
+      <c r="O47" s="3">
+        <v>2</v>
+      </c>
+      <c r="P47" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q47">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
+        <v>5</v>
+      </c>
       <c r="AE47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31">
       <c r="A48">
-        <v>49</v>
-      </c>
-      <c r="B48"/>
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
       <c r="C48" t="s">
         <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="2">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>4</v>
       </c>
-      <c r="I48" s="12">
-        <v>3</v>
-      </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="M48" s="10">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="M48" s="2">
+        <v>7</v>
       </c>
       <c r="N48">
+        <v>7</v>
+      </c>
+      <c r="O48" s="3">
+        <v>9</v>
+      </c>
+      <c r="P48" s="2">
+        <v>26</v>
+      </c>
+      <c r="Q48">
+        <v>2</v>
+      </c>
+      <c r="R48" s="3">
+        <v>2</v>
+      </c>
+      <c r="S48" s="2">
+        <v>2</v>
+      </c>
+      <c r="T48">
+        <v>7</v>
+      </c>
+      <c r="U48" s="3">
         <v>8</v>
       </c>
-      <c r="O48" s="12">
-        <v>11</v>
-      </c>
-      <c r="P48" s="10">
-        <v>6</v>
-      </c>
-      <c r="Q48">
-        <v>3</v>
-      </c>
-      <c r="R48" s="12">
-        <v>3</v>
-      </c>
-      <c r="S48"/>
-      <c r="T48"/>
-      <c r="U48"/>
-      <c r="V48"/>
       <c r="AE48" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" hidden="1" spans="1:31">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31">
       <c r="A49">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
         <v>133</v>
@@ -4789,55 +4071,60 @@
         <v>134</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="10">
-        <v>4</v>
-      </c>
-      <c r="I49" s="12">
-        <v>3</v>
+      <c r="H49" s="2">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3">
+        <v>6</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="M49" s="10">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="M49" s="2">
+        <v>32</v>
       </c>
       <c r="N49">
-        <v>7</v>
-      </c>
-      <c r="O49" s="12">
-        <v>11</v>
-      </c>
-      <c r="P49" s="10">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="O49" s="3">
+        <v>40</v>
+      </c>
+      <c r="P49" s="2">
+        <v>33</v>
       </c>
       <c r="Q49">
-        <v>2</v>
-      </c>
-      <c r="R49" s="12">
-        <v>3</v>
-      </c>
-      <c r="S49"/>
-      <c r="T49"/>
-      <c r="U49"/>
-      <c r="V49"/>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3">
+        <v>30</v>
+      </c>
+      <c r="S49" s="2">
+        <v>19</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3">
+        <v>1</v>
+      </c>
       <c r="AE49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" hidden="1" spans="1:31">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31">
       <c r="A50">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
         <v>135</v>
@@ -4846,7 +4133,7 @@
         <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -4854,161 +4141,146 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="10">
-        <v>5</v>
-      </c>
-      <c r="I50" s="12">
-        <v>4</v>
+      <c r="H50" s="2">
+        <v>2</v>
+      </c>
+      <c r="I50" s="3">
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>1</v>
-      </c>
-      <c r="M50" s="10">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M50" s="2">
+        <v>11</v>
       </c>
       <c r="N50">
-        <v>5</v>
-      </c>
-      <c r="O50" s="12">
-        <v>7</v>
-      </c>
-      <c r="P50" s="10">
-        <v>18</v>
-      </c>
-      <c r="Q50">
-        <v>1.1</v>
-      </c>
-      <c r="R50" s="12">
-        <v>1.7</v>
-      </c>
-      <c r="S50"/>
+        <v>10</v>
+      </c>
+      <c r="O50" s="3">
+        <v>14</v>
+      </c>
       <c r="AE50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="C51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" hidden="1" spans="1:31">
-      <c r="A51">
-        <v>52</v>
-      </c>
-      <c r="B51" t="s">
-        <v>137</v>
-      </c>
-      <c r="C51" t="s">
-        <v>138</v>
-      </c>
-      <c r="D51" t="s">
-        <v>46</v>
-      </c>
-      <c r="E51" t="s">
-        <v>38</v>
       </c>
       <c r="F51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="10">
-        <v>9</v>
-      </c>
-      <c r="I51" s="12">
+      <c r="H51" s="2">
+        <v>4</v>
+      </c>
+      <c r="I51" s="3">
+        <v>3</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2">
+        <v>11</v>
+      </c>
+      <c r="N51">
+        <v>8</v>
+      </c>
+      <c r="O51" s="3">
+        <v>11</v>
+      </c>
+      <c r="P51" s="2">
         <v>6</v>
       </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51">
-        <v>1</v>
-      </c>
-      <c r="M51" s="10">
-        <v>6</v>
-      </c>
-      <c r="N51">
-        <v>1</v>
-      </c>
-      <c r="O51" s="12">
+      <c r="Q51">
         <v>3</v>
       </c>
-      <c r="P51" s="10">
-        <v>49</v>
-      </c>
-      <c r="Q51">
-        <v>1</v>
-      </c>
-      <c r="R51" s="12">
-        <v>1</v>
-      </c>
-      <c r="S51"/>
+      <c r="R51" s="3">
+        <v>3</v>
+      </c>
       <c r="AE51" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:31">
+    <row r="52" spans="1:31">
       <c r="A52">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
         <v>139</v>
       </c>
-      <c r="C52" t="s">
-        <v>140</v>
-      </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E52" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" s="10">
-        <v>1</v>
-      </c>
-      <c r="I52" s="12">
-        <v>0</v>
+      <c r="H52" s="2">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="M52" s="10">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>11</v>
       </c>
       <c r="N52">
-        <v>2</v>
-      </c>
-      <c r="O52" s="12">
-        <v>2</v>
-      </c>
-      <c r="P52" s="10">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="O52" s="3">
+        <v>11</v>
+      </c>
+      <c r="P52" s="2">
+        <v>45</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="12">
-        <v>2</v>
-      </c>
-      <c r="S52"/>
+      <c r="R52" s="3">
+        <v>3</v>
+      </c>
       <c r="AE52" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" hidden="1" spans="1:31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31">
       <c r="A53">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
+        <v>140</v>
+      </c>
+      <c r="C53" t="s">
         <v>141</v>
       </c>
-      <c r="C53" t="s">
-        <v>142</v>
-      </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -5016,122 +4288,105 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="2">
         <v>5</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="3">
+        <v>4</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="M53" s="2">
+        <v>6</v>
+      </c>
+      <c r="N53">
         <v>5</v>
       </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53">
-        <v>6</v>
-      </c>
-      <c r="M53" s="10">
-        <v>50</v>
-      </c>
-      <c r="N53">
-        <v>3</v>
-      </c>
-      <c r="O53" s="12">
-        <v>4</v>
-      </c>
-      <c r="P53" s="10">
-        <v>51</v>
+      <c r="O53" s="3">
+        <v>7</v>
+      </c>
+      <c r="P53" s="2">
+        <v>18</v>
       </c>
       <c r="Q53">
-        <v>-0.5</v>
-      </c>
-      <c r="R53" s="12">
-        <v>-0.5</v>
-      </c>
-      <c r="S53"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R53" s="3">
+        <v>1.7</v>
+      </c>
       <c r="AE53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31">
       <c r="A54">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
         <v>143</v>
       </c>
-      <c r="C54" t="s">
-        <v>144</v>
-      </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
         <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
-      </c>
-      <c r="G54">
-        <v>14</v>
-      </c>
-      <c r="H54" s="10">
-        <v>2</v>
-      </c>
-      <c r="I54" s="12">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="H54" s="2">
+        <v>9</v>
+      </c>
+      <c r="I54" s="3">
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="M54" s="10">
-        <v>15</v>
+      <c r="M54" s="2">
+        <v>6</v>
       </c>
       <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54" s="3">
         <v>3</v>
       </c>
-      <c r="O54" s="12">
-        <v>4</v>
-      </c>
-      <c r="P54" s="10">
-        <v>14</v>
+      <c r="P54" s="2">
+        <v>49</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
-      <c r="R54" s="12">
-        <v>1</v>
-      </c>
-      <c r="S54" s="10">
-        <v>52</v>
-      </c>
-      <c r="T54">
-        <v>3</v>
-      </c>
-      <c r="U54" s="12">
-        <v>5</v>
-      </c>
-      <c r="V54"/>
+      <c r="R54" s="3">
+        <v>1</v>
+      </c>
       <c r="AE54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" hidden="1" spans="1:31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31">
       <c r="A55">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
         <v>145</v>
       </c>
-      <c r="C55" t="s">
-        <v>146</v>
-      </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E55" t="s">
         <v>38</v>
@@ -5139,11 +4394,11 @@
       <c r="F55" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="10">
-        <v>4</v>
-      </c>
-      <c r="I55" s="12">
-        <v>3</v>
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -5151,313 +4406,102 @@
       <c r="K55">
         <v>1</v>
       </c>
-      <c r="M55">
-        <v>15</v>
+      <c r="M55" s="2">
+        <v>9</v>
       </c>
       <c r="N55">
-        <v>1</v>
-      </c>
-      <c r="O55">
-        <v>3</v>
-      </c>
-      <c r="P55" s="10">
-        <v>60</v>
+        <v>2</v>
+      </c>
+      <c r="O55" s="3">
+        <v>2</v>
+      </c>
+      <c r="P55" s="2">
+        <v>21</v>
       </c>
       <c r="Q55">
-        <v>1</v>
-      </c>
-      <c r="R55" s="12">
-        <v>1</v>
-      </c>
-      <c r="S55"/>
-      <c r="AA55" s="12"/>
-      <c r="AE55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" hidden="1" spans="3:31">
+        <v>2</v>
+      </c>
+      <c r="R55" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>146</v>
+      </c>
       <c r="C56" t="s">
         <v>147</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" s="10">
-        <v>3</v>
-      </c>
-      <c r="I56" s="12">
-        <v>2</v>
+      <c r="H56" s="2">
+        <v>5</v>
+      </c>
+      <c r="I56" s="3">
+        <v>5</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56"/>
-      <c r="M56">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>6</v>
+      </c>
+      <c r="M56" s="2">
+        <v>50</v>
       </c>
       <c r="N56">
         <v>2</v>
       </c>
-      <c r="O56">
-        <v>2</v>
-      </c>
-      <c r="P56" s="10">
-        <v>45</v>
+      <c r="O56" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="P56" s="2">
+        <v>51</v>
       </c>
       <c r="Q56">
-        <v>1</v>
-      </c>
-      <c r="R56" s="12">
-        <v>2</v>
-      </c>
-      <c r="S56"/>
-      <c r="AA56" s="12"/>
-      <c r="AE56" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" hidden="1" spans="2:31">
-      <c r="B57" t="s">
-        <v>148</v>
-      </c>
-      <c r="C57" t="s">
-        <v>149</v>
-      </c>
-      <c r="D57" t="s">
-        <v>64</v>
-      </c>
-      <c r="E57" t="s">
-        <v>33</v>
-      </c>
-      <c r="F57" t="s">
-        <v>47</v>
-      </c>
-      <c r="G57">
-        <v>3</v>
-      </c>
-      <c r="H57" s="10">
-        <v>2</v>
-      </c>
-      <c r="I57" s="12">
-        <v>1</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>1</v>
-      </c>
-      <c r="M57">
-        <v>45</v>
-      </c>
-      <c r="N57">
-        <v>3</v>
-      </c>
-      <c r="O57">
-        <v>4</v>
-      </c>
-      <c r="P57" s="10">
-        <v>11</v>
-      </c>
-      <c r="Q57">
-        <v>12</v>
-      </c>
-      <c r="R57" s="12">
-        <v>18</v>
-      </c>
-      <c r="S57" s="10">
-        <v>14</v>
-      </c>
-      <c r="T57">
-        <v>1</v>
-      </c>
-      <c r="U57" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="12"/>
-      <c r="AE57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" hidden="1" spans="2:31">
-      <c r="B58" t="s">
-        <v>150</v>
-      </c>
-      <c r="C58" t="s">
-        <v>151</v>
-      </c>
-      <c r="D58" t="s">
-        <v>64</v>
-      </c>
-      <c r="E58" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58" t="s">
-        <v>34</v>
-      </c>
-      <c r="H58" s="10">
-        <v>3</v>
-      </c>
-      <c r="I58" s="12">
-        <v>3</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="M58" s="10">
-        <v>45</v>
-      </c>
-      <c r="N58">
-        <v>2</v>
-      </c>
-      <c r="O58" s="12">
-        <v>3</v>
-      </c>
-      <c r="P58" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q58">
-        <v>2</v>
-      </c>
-      <c r="R58" s="12">
-        <v>3</v>
-      </c>
-      <c r="AE58" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" hidden="1" spans="2:31">
-      <c r="B59" t="s">
-        <v>152</v>
-      </c>
-      <c r="C59" t="s">
-        <v>153</v>
-      </c>
-      <c r="D59" t="s">
-        <v>64</v>
-      </c>
-      <c r="E59" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59" t="s">
-        <v>34</v>
-      </c>
-      <c r="H59" s="10">
-        <v>3</v>
-      </c>
-      <c r="I59" s="12">
-        <v>3</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
-      </c>
-      <c r="K59">
-        <v>1</v>
-      </c>
-      <c r="AE59" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" hidden="1" spans="2:31">
-      <c r="B60" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" t="s">
-        <v>155</v>
-      </c>
-      <c r="D60" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" t="s">
-        <v>33</v>
-      </c>
-      <c r="F60" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60">
-        <v>3</v>
-      </c>
-      <c r="H60" s="10">
-        <v>2</v>
-      </c>
-      <c r="I60" s="12">
-        <v>1</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="M60" s="10">
-        <v>2</v>
-      </c>
-      <c r="N60">
-        <v>5</v>
-      </c>
-      <c r="O60" s="12">
-        <v>6</v>
-      </c>
-      <c r="P60" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q60">
-        <v>5</v>
-      </c>
-      <c r="R60" s="12">
-        <v>6</v>
-      </c>
-      <c r="AE60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" hidden="1"/>
-    <row r="62" hidden="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="R56" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="30">
-      <filters>
-        <filter val="F"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:AE62" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5471,151 +4515,150 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>157</v>
+        <v>148</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="G1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" customFormat="1" spans="1:9">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:9">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" t="s">
         <v>165</v>
-      </c>
-      <c r="E5" t="s">
-        <v>173</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:9">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:9">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:9">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5624,18 +4667,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:9">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5644,18 +4687,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:9">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5664,138 +4707,138 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:9">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:9">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:9">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:9">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:9">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:9">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:9">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5804,38 +4847,38 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:9">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5844,18 +4887,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:9">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5864,58 +4907,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:9">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:9">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:9">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5924,41 +4967,41 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:9">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:9">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5967,21 +5010,21 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:9">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5990,38 +5033,38 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:9">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:9">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -6030,24 +5073,24 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:9">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -6056,18 +5099,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="1:9">
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6076,133 +5119,133 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:9">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C31" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E31" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:9">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D32" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:9">
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:9">
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:9">
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:9">
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F36" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6211,18 +5254,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" customFormat="1" spans="1:9">
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -6231,38 +5274,38 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:9">
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I38">
         <v>-1</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:9">
+    <row r="39" spans="1:9">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -6274,38 +5317,38 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:9">
+    <row r="40" spans="1:9">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E40" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I40">
         <v>-1</v>
       </c>
     </row>
-    <row r="41" customFormat="1" spans="1:9">
+    <row r="41" spans="1:9">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6317,24 +5360,24 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:9">
+    <row r="42" spans="1:9">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -6343,18 +5386,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="43" customFormat="1" spans="1:9">
+    <row r="43" spans="1:9">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -6363,18 +5406,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="1:9">
+    <row r="44" spans="1:9">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -6383,61 +5426,61 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:9">
+    <row r="45" spans="1:9">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F45" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I45">
         <v>-1</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:9">
+    <row r="46" spans="1:9">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C46" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E46" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="1:9">
+    <row r="47" spans="1:9">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C47" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D47" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -6446,41 +5489,41 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" customFormat="1" spans="1:9">
+    <row r="48" spans="1:9">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I48">
         <v>-1</v>
       </c>
     </row>
-    <row r="49" customFormat="1" spans="1:9">
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6489,41 +5532,41 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:9">
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I50">
         <v>-1</v>
       </c>
     </row>
-    <row r="51" customFormat="1" spans="1:9">
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -6532,18 +5575,18 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:9">
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -6552,18 +5595,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customFormat="1" spans="1:9">
+    <row r="53" spans="1:9">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D53" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -6572,236 +5615,30 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:9">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" t="s">
-        <v>246</v>
-      </c>
-      <c r="C54" t="s">
-        <v>246</v>
-      </c>
-      <c r="D54" t="s">
-        <v>181</v>
-      </c>
-      <c r="E54">
-        <v>3</v>
-      </c>
-      <c r="G54">
-        <v>6</v>
-      </c>
-      <c r="I54">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:9">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55" t="s">
-        <v>247</v>
-      </c>
-      <c r="C55" t="s">
-        <v>247</v>
-      </c>
-      <c r="D55" t="s">
-        <v>194</v>
-      </c>
-      <c r="E55" t="s">
-        <v>166</v>
-      </c>
-      <c r="G55">
-        <v>6</v>
-      </c>
-      <c r="I55">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:9">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>248</v>
-      </c>
-      <c r="C56" t="s">
-        <v>248</v>
-      </c>
-      <c r="D56" t="s">
-        <v>194</v>
-      </c>
-      <c r="E56" t="s">
-        <v>166</v>
-      </c>
-      <c r="G56">
-        <v>7</v>
-      </c>
-      <c r="I56">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:9">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>249</v>
-      </c>
-      <c r="C57" t="s">
-        <v>250</v>
-      </c>
-      <c r="D57" t="s">
-        <v>194</v>
-      </c>
-      <c r="E57" t="s">
-        <v>166</v>
-      </c>
-      <c r="G57">
-        <v>8</v>
-      </c>
-      <c r="I57">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:9">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58" t="s">
-        <v>251</v>
-      </c>
-      <c r="C58" t="s">
-        <v>252</v>
-      </c>
-      <c r="D58" t="s">
-        <v>165</v>
-      </c>
-      <c r="E58" t="s">
-        <v>166</v>
-      </c>
-      <c r="G58">
-        <v>6</v>
-      </c>
-      <c r="I58">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:9">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59" t="s">
-        <v>253</v>
-      </c>
-      <c r="C59" t="s">
-        <v>252</v>
-      </c>
-      <c r="D59" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" t="s">
-        <v>166</v>
-      </c>
-      <c r="G59">
-        <v>7</v>
-      </c>
-      <c r="I59">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:9">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60" t="s">
-        <v>254</v>
-      </c>
-      <c r="C60" t="s">
-        <v>252</v>
-      </c>
-      <c r="D60" t="s">
-        <v>165</v>
-      </c>
-      <c r="E60" t="s">
-        <v>166</v>
-      </c>
-      <c r="G60">
-        <v>8</v>
-      </c>
-      <c r="I60">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:9">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61" t="s">
-        <v>255</v>
-      </c>
-      <c r="C61" t="s">
-        <v>255</v>
-      </c>
-      <c r="D61" t="s">
-        <v>181</v>
-      </c>
-      <c r="E61">
-        <v>3</v>
-      </c>
-      <c r="F61" t="s">
-        <v>214</v>
-      </c>
-      <c r="I61">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:9">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62" t="s">
-        <v>256</v>
-      </c>
-      <c r="C62" t="s">
-        <v>256</v>
-      </c>
-      <c r="D62" t="s">
-        <v>181</v>
-      </c>
-      <c r="E62">
-        <v>20</v>
-      </c>
-      <c r="I62">
-        <v>-1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:15">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6809,13 +5646,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="D1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -6842,21 +5679,21 @@
         <v>22</v>
       </c>
       <c r="N1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="O1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:9">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6877,15 +5714,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6900,15 +5737,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6916,16 +5753,22 @@
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:11">
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6939,28 +5782,16 @@
       <c r="G5">
         <v>0.5</v>
       </c>
-      <c r="H5">
-        <v>53</v>
-      </c>
-      <c r="I5">
-        <v>0.5</v>
-      </c>
-      <c r="J5">
-        <v>54</v>
-      </c>
-      <c r="K5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:7">
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6975,15 +5806,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6998,15 +5829,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -7021,15 +5852,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -7044,15 +5875,15 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -7067,15 +5898,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -7096,15 +5927,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -7125,15 +5956,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -7148,15 +5979,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -7171,15 +6002,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -7194,15 +6025,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7217,15 +6048,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7236,19 +6067,19 @@
       <c r="F17">
         <v>46</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -7263,15 +6094,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7280,86 +6111,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
         <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:5">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:7">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>277</v>
-      </c>
-      <c r="C22" t="s">
-        <v>263</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7370,30 +6159,30 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="G1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:6">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -7402,52 +6191,52 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="13" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="13" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7456,18 +6245,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -7476,18 +6265,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -7496,18 +6285,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -7516,65 +6305,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:6">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D9" t="s">
-        <v>284</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:6">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>293</v>
-      </c>
-      <c r="C10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" t="s">
-        <v>284</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>50</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94841436-4B03-4D46-B5B4-E851A3BE0D55}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="28.425" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="17.2833333333333" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7594,7 +6341,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7602,19 +6349,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7622,19 +6369,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7642,19 +6389,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="D4" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7662,16 +6409,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7679,16 +6426,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="F6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7696,81 +6443,96 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="F7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C9" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C10" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="D10" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E10">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02B963FD-B399-4A5F-A7EE-C698A9110DBE}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.425" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7795,45 +6557,57 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F843A941-2090-4EA2-92B0-02A8CDB751AA}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.425" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" customWidth="1"/>
-    <col min="6" max="6" width="8.425" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -7846,7 +6620,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -7855,13 +6629,13 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="J1" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -7869,13 +6643,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -7886,14 +6660,14 @@
       <c r="G2">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>325</v>
+      <c r="H2" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>299</v>
       </c>
       <c r="J2" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7901,13 +6675,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="C3" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="D3" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -7918,14 +6692,14 @@
       <c r="G3">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>326</v>
+      <c r="H3" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="J3" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7933,13 +6707,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="C4" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -7951,13 +6725,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>327</v>
+        <v>283</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>298</v>
       </c>
       <c r="J4" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7965,13 +6739,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>291</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="D5" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7982,14 +6756,14 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>331</v>
+      <c r="H5" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="J5" t="s">
-        <v>328</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7997,13 +6771,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>332</v>
+        <v>285</v>
       </c>
       <c r="C6" t="s">
-        <v>333</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -8014,14 +6788,14 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>331</v>
+      <c r="H6" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="J6" t="s">
-        <v>332</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8029,13 +6803,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>289</v>
       </c>
       <c r="C7" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -8047,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>330</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>331</v>
+        <v>284</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="J7" t="s">
-        <v>336</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8061,10 +6835,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -8076,13 +6850,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>330</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>338</v>
+        <v>284</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>316</v>
       </c>
       <c r="J8" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -8090,10 +6864,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -8105,13 +6879,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>330</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>340</v>
+        <v>284</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>317</v>
       </c>
       <c r="J9" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8119,10 +6893,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="D10" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -8134,47 +6908,47 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>330</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>342</v>
+        <v>284</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>319</v>
       </c>
       <c r="J10" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="11" spans="9:9">
-      <c r="I11" s="6"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="I11" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1AA25C0-E9A0-4DAC-9454-4255D17FAEDC}">
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8188,7 +6962,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -8197,54 +6971,57 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>344</v>
+        <v>297</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>304</v>
       </c>
       <c r="K1" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="L1" t="s">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="M1" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="N1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>307</v>
+      </c>
+      <c r="O1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>350</v>
+        <v>286</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>351</v>
+      <c r="H2" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -8262,33 +7039,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>350</v>
+        <v>287</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>351</v>
+        <v>303</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -8306,33 +7083,33 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>353</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>353</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>350</v>
+        <v>288</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>351</v>
+      <c r="H4" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>302</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -8350,9 +7127,132 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>100000</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="N5">
+        <v>7</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1176038-727D-41F6-85CD-7113C03BF2B8}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="6" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DF55B0-B4EA-4D8B-B63F-C4BA2DDECCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="10480" firstSheet="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -15,6 +21,7 @@
     <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
     <sheet name="DialogueEvents" sheetId="7" r:id="rId7"/>
     <sheet name="StreamEvents" sheetId="8" r:id="rId8"/>
+    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
@@ -28,8 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="367">
   <si>
     <t>ID</t>
   </si>
@@ -1099,172 +1104,67 @@
   </si>
   <si>
     <t>Stream3</t>
+  </si>
+  <si>
+    <t>VCardRarityCondition</t>
+  </si>
+  <si>
+    <t>SelectPhaseEnding</t>
+  </si>
+  <si>
+    <t>VRaisingPickPhaseEndingEffect</t>
+  </si>
+  <si>
+    <t>Ending1</t>
+  </si>
+  <si>
+    <t>Ending2</t>
+  </si>
+  <si>
+    <t>Ending3</t>
+  </si>
+  <si>
+    <t>VPhaseEndingAttributeCondition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASingingAbility </t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>VPhaseEndingEventCondition</t>
+  </si>
+  <si>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>#00B054</t>
+  </si>
+  <si>
+    <t>PhaseStart</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1313,188 +1213,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1520,265 +1240,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1786,72 +1261,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFFF"/>
-      <color rgb="00AB0580"/>
-      <color rgb="0000B050"/>
-      <color rgb="00FFB200"/>
-      <color rgb="004B58FF"/>
-      <color rgb="00FF2160"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFAB0580"/>
+      <color rgb="FF00B050"/>
+      <color rgb="FFFFB200"/>
+      <color rgb="FF4B58FF"/>
+      <color rgb="FFFF2160"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2109,43 +1543,43 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="12.75" customWidth="1"/>
-    <col min="3" max="3" width="38.2166666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.425" customWidth="1"/>
-    <col min="5" max="5" width="13.425" customWidth="1"/>
-    <col min="6" max="6" width="10.5666666666667" customWidth="1"/>
-    <col min="7" max="7" width="9.70833333333333" customWidth="1"/>
-    <col min="8" max="8" width="7.14166666666667" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="10.2833333333333" customWidth="1"/>
-    <col min="11" max="11" width="13.7083333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.70833333333333" customWidth="1"/>
-    <col min="13" max="13" width="9.70833333333333" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
-    <col min="15" max="15" width="17.7083333333333" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="12.2833333333333" customWidth="1"/>
-    <col min="18" max="18" width="17.1416666666667" customWidth="1"/>
-    <col min="21" max="21" width="17.7083333333333" customWidth="1"/>
-    <col min="22" max="22" width="10.7083333333333" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7083333333333" customWidth="1"/>
-    <col min="25" max="26" width="12.425" customWidth="1"/>
-    <col min="27" max="27" width="12.2833333333333" customWidth="1"/>
-    <col min="29" max="29" width="4.28333333333333" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" customWidth="1"/>
+    <col min="25" max="26" width="12.42578125" customWidth="1"/>
+    <col min="27" max="27" width="12.28515625" customWidth="1"/>
+    <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:31">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2167,10 +1601,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2182,46 +1616,46 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="7" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="9" t="s">
         <v>25</v>
       </c>
       <c r="AA1" t="s">
@@ -2237,7 +1671,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:31">
+    <row r="2" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2256,10 +1690,10 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="7">
         <v>4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="9">
         <v>3</v>
       </c>
       <c r="J2">
@@ -2268,22 +1702,21 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="7">
         <v>11</v>
       </c>
       <c r="N2">
         <v>7</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="9">
         <v>7</v>
       </c>
-      <c r="P2"/>
-      <c r="AC2" s="13"/>
+      <c r="AC2" s="10"/>
       <c r="AE2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:31">
+    <row r="3" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2302,10 +1735,10 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
         <v>0</v>
       </c>
       <c r="J3">
@@ -2314,22 +1747,21 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="7">
         <v>2</v>
       </c>
       <c r="N3">
         <v>4</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="9">
         <v>4</v>
       </c>
-      <c r="P3"/>
-      <c r="AC3" s="13"/>
+      <c r="AC3" s="10"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" customFormat="1" hidden="1" spans="1:31">
+    <row r="4" spans="1:31" hidden="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2348,10 +1780,10 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="7">
         <v>5</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="9">
         <v>5</v>
       </c>
       <c r="J4">
@@ -2360,22 +1792,21 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="7">
         <v>11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
-      <c r="O4" s="12">
+      <c r="O4" s="9">
         <v>15</v>
       </c>
-      <c r="P4"/>
-      <c r="AC4" s="13"/>
+      <c r="AC4" s="10"/>
       <c r="AE4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:31">
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2394,10 +1825,10 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="10">
-        <v>3</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="9">
         <v>3</v>
       </c>
       <c r="J5">
@@ -2406,31 +1837,30 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="7">
         <v>11</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
-      <c r="O5" s="12">
+      <c r="O5" s="9">
         <v>5</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="7">
         <v>2</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
-      <c r="R5" s="12">
-        <v>2</v>
-      </c>
-      <c r="S5"/>
-      <c r="AC5" s="13"/>
+      <c r="R5" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="10"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="1" hidden="1" spans="1:31">
+    <row r="6" spans="1:31" hidden="1">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2452,10 +1882,10 @@
       <c r="G6">
         <v>3</v>
       </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2464,15 +1894,15 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="13"/>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="10"/>
       <c r="AE6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:31">
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2491,10 +1921,10 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="7">
         <v>5</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="9">
         <v>4</v>
       </c>
       <c r="J7">
@@ -2503,34 +1933,33 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="7">
         <v>4</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="7">
         <v>21</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
-      <c r="R7" s="12">
-        <v>2</v>
-      </c>
-      <c r="S7" s="10">
+      <c r="R7" s="9">
+        <v>2</v>
+      </c>
+      <c r="S7" s="7">
         <v>14</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="U7" s="12">
-        <v>1</v>
-      </c>
-      <c r="V7"/>
-      <c r="AC7" s="13"/>
+      <c r="U7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="10"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="1" hidden="1" spans="1:31">
+    <row r="8" spans="1:31" hidden="1">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2552,10 +1981,10 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2564,40 +1993,39 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="7">
         <v>2</v>
       </c>
       <c r="N8">
         <v>7</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8" s="9">
         <v>7</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="7">
         <v>3</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8" s="12">
-        <v>1</v>
-      </c>
-      <c r="S8" s="10">
+      <c r="R8" s="9">
+        <v>1</v>
+      </c>
+      <c r="S8" s="7">
         <v>14</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8" s="12">
-        <v>1</v>
-      </c>
-      <c r="V8"/>
-      <c r="AC8" s="13"/>
+      <c r="U8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="10"/>
       <c r="AE8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" customFormat="1" hidden="1" spans="1:31">
+    <row r="9" spans="1:31" hidden="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2616,10 +2044,10 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="10">
-        <v>2</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="H9" s="7">
+        <v>2</v>
+      </c>
+      <c r="I9" s="9">
         <v>2</v>
       </c>
       <c r="J9">
@@ -2628,31 +2056,30 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="7">
         <v>6</v>
       </c>
       <c r="N9">
         <v>3</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="9">
         <v>4</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="7">
         <v>2</v>
       </c>
       <c r="Q9">
         <v>3</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="9">
         <v>4</v>
       </c>
-      <c r="S9"/>
-      <c r="AC9" s="13"/>
+      <c r="AC9" s="10"/>
       <c r="AE9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="1" hidden="1" spans="1:31">
+    <row r="10" spans="1:31" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2671,10 +2098,10 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" s="10">
-        <v>2</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="H10" s="7">
+        <v>2</v>
+      </c>
+      <c r="I10" s="9">
         <v>2</v>
       </c>
       <c r="J10">
@@ -2683,31 +2110,30 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="7">
         <v>7</v>
       </c>
       <c r="N10">
         <v>2</v>
       </c>
-      <c r="O10" s="12">
-        <v>3</v>
-      </c>
-      <c r="P10" s="10">
+      <c r="O10" s="9">
+        <v>3</v>
+      </c>
+      <c r="P10" s="7">
         <v>2</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
-      <c r="R10" s="12">
-        <v>3</v>
-      </c>
-      <c r="S10"/>
-      <c r="AC10" s="13"/>
+      <c r="R10" s="9">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="10"/>
       <c r="AE10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" customFormat="1" hidden="1" spans="1:31">
+    <row r="11" spans="1:31" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2726,10 +2152,10 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="10">
-        <v>2</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="H11" s="7">
+        <v>2</v>
+      </c>
+      <c r="I11" s="9">
         <v>2</v>
       </c>
       <c r="J11">
@@ -2738,31 +2164,30 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="7">
         <v>15</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
-      <c r="O11" s="12">
-        <v>3</v>
-      </c>
-      <c r="P11" s="10">
+      <c r="O11" s="9">
+        <v>3</v>
+      </c>
+      <c r="P11" s="7">
         <v>2</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="12">
-        <v>3</v>
-      </c>
-      <c r="S11"/>
-      <c r="AC11" s="13"/>
+      <c r="R11" s="9">
+        <v>3</v>
+      </c>
+      <c r="AC11" s="10"/>
       <c r="AE11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" customFormat="1" hidden="1" spans="1:31">
+    <row r="12" spans="1:31" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2781,10 +2206,10 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="7">
         <v>6</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="9">
         <v>6</v>
       </c>
       <c r="J12">
@@ -2793,26 +2218,25 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="7">
         <v>11</v>
       </c>
       <c r="N12">
         <v>9</v>
       </c>
-      <c r="O12" s="12">
+      <c r="O12" s="9">
         <v>13</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="7">
         <v>11</v>
       </c>
       <c r="Q12">
         <v>9</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="9">
         <v>13</v>
       </c>
-      <c r="S12"/>
-      <c r="AC12" s="13"/>
+      <c r="AC12" s="10"/>
       <c r="AD12" t="s">
         <v>61</v>
       </c>
@@ -2820,7 +2244,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:31">
+    <row r="13" spans="1:31">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2839,10 +2263,10 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <v>5</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="9">
         <v>5</v>
       </c>
       <c r="J13">
@@ -2851,32 +2275,30 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="7">
         <v>11</v>
       </c>
       <c r="N13">
         <v>11</v>
       </c>
-      <c r="O13" s="12">
+      <c r="O13" s="9">
         <v>15</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="7">
         <v>2</v>
       </c>
       <c r="Q13">
         <v>7</v>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="9">
         <v>9</v>
       </c>
-      <c r="S13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13"/>
+      <c r="AC13" s="10"/>
       <c r="AE13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" customFormat="1" hidden="1" spans="1:31">
+    <row r="14" spans="1:31" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2895,10 +2317,10 @@
       <c r="F14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="7">
         <v>5</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="9">
         <v>4</v>
       </c>
       <c r="J14">
@@ -2907,25 +2329,21 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="7">
         <v>6</v>
       </c>
       <c r="N14">
         <v>6</v>
       </c>
-      <c r="O14" s="12">
+      <c r="O14" s="9">
         <v>8</v>
       </c>
-      <c r="P14"/>
-      <c r="Q14"/>
-      <c r="R14"/>
-      <c r="S14"/>
-      <c r="AC14" s="13"/>
+      <c r="AC14" s="10"/>
       <c r="AE14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" customFormat="1" hidden="1" spans="1:31">
+    <row r="15" spans="1:31" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2944,10 +2362,10 @@
       <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="7">
         <v>4</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="9">
         <v>4</v>
       </c>
       <c r="J15">
@@ -2956,22 +2374,21 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="7">
         <v>18</v>
       </c>
       <c r="N15">
         <v>1.4</v>
       </c>
-      <c r="O15" s="12">
+      <c r="O15" s="9">
         <v>1.8</v>
       </c>
-      <c r="P15"/>
-      <c r="AC15" s="13"/>
+      <c r="AC15" s="10"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" customFormat="1" hidden="1" spans="1:31">
+    <row r="16" spans="1:31" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2990,10 +2407,10 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="7">
         <v>6</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="9">
         <v>5</v>
       </c>
       <c r="J16">
@@ -3002,31 +2419,30 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="7">
         <v>6</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
-      <c r="O16" s="12">
+      <c r="O16" s="9">
         <v>5</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="7">
         <v>18</v>
       </c>
       <c r="Q16">
         <v>0.8</v>
       </c>
-      <c r="R16" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="S16"/>
-      <c r="AC16" s="13"/>
+      <c r="R16" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AC16" s="10"/>
       <c r="AE16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:31">
+    <row r="17" spans="1:31">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3045,10 +2461,10 @@
       <c r="F17" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="10">
-        <v>3</v>
-      </c>
-      <c r="I17" s="12">
+      <c r="H17" s="7">
+        <v>3</v>
+      </c>
+      <c r="I17" s="9">
         <v>3</v>
       </c>
       <c r="J17">
@@ -3057,40 +2473,39 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="7">
         <v>19</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="O17" s="12">
-        <v>1</v>
-      </c>
-      <c r="P17" s="10">
+      <c r="O17" s="9">
+        <v>1</v>
+      </c>
+      <c r="P17" s="7">
         <v>2</v>
       </c>
       <c r="Q17">
         <v>4</v>
       </c>
-      <c r="R17" s="12">
+      <c r="R17" s="9">
         <v>6</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S17" s="7">
         <v>21</v>
       </c>
       <c r="T17">
         <v>2</v>
       </c>
-      <c r="U17" s="12">
-        <v>3</v>
-      </c>
-      <c r="V17"/>
-      <c r="AC17" s="14"/>
+      <c r="U17" s="9">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="11"/>
       <c r="AE17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" customFormat="1" hidden="1" spans="1:31">
+    <row r="18" spans="1:31" hidden="1">
       <c r="A18">
         <v>18</v>
       </c>
@@ -3109,10 +2524,10 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="7">
         <v>4</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="9">
         <v>3</v>
       </c>
       <c r="J18">
@@ -3121,28 +2536,21 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="7">
         <v>15</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
-      <c r="O18" s="12">
+      <c r="O18" s="9">
         <v>7</v>
       </c>
-      <c r="P18"/>
-      <c r="Q18"/>
-      <c r="R18"/>
-      <c r="S18"/>
-      <c r="T18"/>
-      <c r="U18"/>
-      <c r="V18"/>
-      <c r="AC18" s="13"/>
+      <c r="AC18" s="10"/>
       <c r="AE18" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" customFormat="1" hidden="1" spans="1:31">
+    <row r="19" spans="1:31" hidden="1">
       <c r="A19">
         <v>19</v>
       </c>
@@ -3161,10 +2569,10 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="7">
         <v>5</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="9">
         <v>4</v>
       </c>
       <c r="J19">
@@ -3173,31 +2581,30 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="7">
         <v>23</v>
       </c>
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19" s="12">
-        <v>1</v>
-      </c>
-      <c r="P19" s="10">
+      <c r="O19" s="9">
+        <v>1</v>
+      </c>
+      <c r="P19" s="7">
         <v>7</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
-      <c r="R19" s="12">
-        <v>2</v>
-      </c>
-      <c r="S19"/>
-      <c r="AC19" s="13"/>
+      <c r="R19" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC19" s="10"/>
       <c r="AE19" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" customFormat="1" hidden="1" spans="1:31">
+    <row r="20" spans="1:31" hidden="1">
       <c r="A20">
         <v>20</v>
       </c>
@@ -3216,10 +2623,10 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="7">
         <v>6</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="9">
         <v>6</v>
       </c>
       <c r="J20">
@@ -3231,22 +2638,21 @@
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="7">
         <v>11</v>
       </c>
       <c r="N20">
         <v>24</v>
       </c>
-      <c r="O20" s="12">
+      <c r="O20" s="9">
         <v>30</v>
       </c>
-      <c r="P20"/>
-      <c r="AC20" s="14"/>
+      <c r="AC20" s="11"/>
       <c r="AE20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" customFormat="1" hidden="1" spans="1:31">
+    <row r="21" spans="1:31" hidden="1">
       <c r="A21">
         <v>21</v>
       </c>
@@ -3265,10 +2671,10 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="7">
         <v>5</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="9">
         <v>4</v>
       </c>
       <c r="J21">
@@ -3277,40 +2683,39 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="7">
         <v>26</v>
       </c>
       <c r="N21">
         <v>2</v>
       </c>
-      <c r="O21" s="12">
-        <v>2</v>
-      </c>
-      <c r="P21" s="10">
+      <c r="O21" s="9">
+        <v>2</v>
+      </c>
+      <c r="P21" s="7">
         <v>11</v>
       </c>
       <c r="Q21">
         <v>30</v>
       </c>
-      <c r="R21" s="12">
+      <c r="R21" s="9">
         <v>42</v>
       </c>
-      <c r="S21" s="10">
+      <c r="S21" s="7">
         <v>2</v>
       </c>
       <c r="T21">
         <v>5</v>
       </c>
-      <c r="U21" s="12">
+      <c r="U21" s="9">
         <v>7</v>
       </c>
-      <c r="V21"/>
-      <c r="AC21" s="13"/>
+      <c r="AC21" s="10"/>
       <c r="AE21" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" customFormat="1" hidden="1" spans="1:31">
+    <row r="22" spans="1:31" hidden="1">
       <c r="A22">
         <v>22</v>
       </c>
@@ -3329,10 +2734,10 @@
       <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="7">
         <v>4</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="9">
         <v>4</v>
       </c>
       <c r="J22">
@@ -3341,31 +2746,30 @@
       <c r="K22">
         <v>1</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="7">
         <v>6</v>
       </c>
       <c r="N22">
         <v>2</v>
       </c>
-      <c r="O22" s="12">
+      <c r="O22" s="9">
         <v>4</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="7">
         <v>28</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
-      <c r="R22" s="12">
-        <v>1</v>
-      </c>
-      <c r="S22"/>
-      <c r="AC22" s="13"/>
+      <c r="R22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="10"/>
       <c r="AE22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" customFormat="1" hidden="1" spans="1:31">
+    <row r="23" spans="1:31" hidden="1">
       <c r="A23">
         <v>23</v>
       </c>
@@ -3384,10 +2788,10 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="10">
-        <v>1</v>
-      </c>
-      <c r="I23" s="12">
+      <c r="H23" s="7">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3396,34 +2800,30 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="7">
         <v>6</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
-      <c r="O23" s="12">
+      <c r="O23" s="9">
         <v>7</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="7">
         <v>2</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="R23" s="12">
-        <v>1</v>
-      </c>
-      <c r="S23"/>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23"/>
-      <c r="AC23" s="13"/>
+      <c r="R23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="10"/>
       <c r="AE23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" customFormat="1" hidden="1" spans="1:31">
+    <row r="24" spans="1:31" hidden="1">
       <c r="A24">
         <v>24</v>
       </c>
@@ -3442,10 +2842,10 @@
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="7">
         <v>4</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="9">
         <v>4</v>
       </c>
       <c r="J24">
@@ -3454,31 +2854,30 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="7">
         <v>15</v>
       </c>
       <c r="N24">
         <v>3</v>
       </c>
-      <c r="O24" s="12">
+      <c r="O24" s="9">
         <v>4</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="7">
         <v>11</v>
       </c>
       <c r="Q24">
         <v>8</v>
       </c>
-      <c r="R24" s="12">
+      <c r="R24" s="9">
         <v>11</v>
       </c>
-      <c r="S24"/>
-      <c r="AC24" s="13"/>
+      <c r="AC24" s="10"/>
       <c r="AE24" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="25" customFormat="1" hidden="1" spans="1:31">
+    <row r="25" spans="1:31" hidden="1">
       <c r="A25">
         <v>25</v>
       </c>
@@ -3497,10 +2896,10 @@
       <c r="F25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="10">
-        <v>3</v>
-      </c>
-      <c r="I25" s="12">
+      <c r="H25" s="7">
+        <v>3</v>
+      </c>
+      <c r="I25" s="9">
         <v>2</v>
       </c>
       <c r="J25">
@@ -3509,25 +2908,21 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="7">
         <v>7</v>
       </c>
       <c r="N25">
         <v>3</v>
       </c>
-      <c r="O25" s="12">
+      <c r="O25" s="9">
         <v>5</v>
       </c>
-      <c r="P25"/>
-      <c r="Q25"/>
-      <c r="R25"/>
-      <c r="S25"/>
-      <c r="AC25" s="13"/>
+      <c r="AC25" s="10"/>
       <c r="AE25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" customFormat="1" hidden="1" spans="1:31">
+    <row r="26" spans="1:31" hidden="1">
       <c r="A26">
         <v>26</v>
       </c>
@@ -3546,10 +2941,10 @@
       <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="10">
-        <v>3</v>
-      </c>
-      <c r="I26" s="12">
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
+      <c r="I26" s="9">
         <v>2</v>
       </c>
       <c r="J26">
@@ -3558,31 +2953,30 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="7">
         <v>7</v>
       </c>
       <c r="N26">
         <v>3</v>
       </c>
-      <c r="O26" s="12">
+      <c r="O26" s="9">
         <v>4</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="7">
         <v>2</v>
       </c>
       <c r="Q26">
         <v>4</v>
       </c>
-      <c r="R26" s="12">
+      <c r="R26" s="9">
         <v>6</v>
       </c>
-      <c r="S26"/>
-      <c r="AC26" s="13"/>
+      <c r="AC26" s="10"/>
       <c r="AE26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" customFormat="1" hidden="1" spans="1:31">
+    <row r="27" spans="1:31" hidden="1">
       <c r="A27">
         <v>27</v>
       </c>
@@ -3601,10 +2995,10 @@
       <c r="F27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="7">
         <v>8</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="9">
         <v>6</v>
       </c>
       <c r="J27">
@@ -3616,40 +3010,39 @@
       <c r="L27">
         <v>0</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="7">
         <v>11</v>
       </c>
       <c r="N27">
         <v>12</v>
       </c>
-      <c r="O27" s="12">
+      <c r="O27" s="9">
         <v>18</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="7">
         <v>56</v>
       </c>
       <c r="Q27">
         <v>24</v>
       </c>
-      <c r="R27" s="12">
+      <c r="R27" s="9">
         <v>30</v>
       </c>
-      <c r="S27" s="10">
+      <c r="S27" s="7">
         <v>57</v>
       </c>
       <c r="T27">
         <v>36</v>
       </c>
-      <c r="U27" s="12">
+      <c r="U27" s="9">
         <v>44</v>
       </c>
-      <c r="V27"/>
-      <c r="AC27" s="14"/>
+      <c r="AC27" s="11"/>
       <c r="AE27" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="28" customFormat="1" hidden="1" spans="1:31">
+    <row r="28" spans="1:31" hidden="1">
       <c r="A28">
         <v>28</v>
       </c>
@@ -3668,10 +3061,10 @@
       <c r="F28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="10">
-        <v>1</v>
-      </c>
-      <c r="I28" s="12">
+      <c r="H28" s="7">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9">
         <v>0</v>
       </c>
       <c r="J28">
@@ -3680,25 +3073,21 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="M28" s="10">
+      <c r="M28" s="7">
         <v>2</v>
       </c>
       <c r="N28">
         <v>6</v>
       </c>
-      <c r="O28" s="12">
+      <c r="O28" s="9">
         <v>8</v>
       </c>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="AC28" s="13"/>
+      <c r="AC28" s="10"/>
       <c r="AE28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:31">
+    <row r="29" spans="1:31">
       <c r="A29">
         <v>30</v>
       </c>
@@ -3717,10 +3106,10 @@
       <c r="F29" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="7">
         <v>5</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="9">
         <v>5</v>
       </c>
       <c r="J29">
@@ -3729,40 +3118,39 @@
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="M29" s="10">
+      <c r="M29" s="7">
         <v>32</v>
       </c>
       <c r="N29">
         <v>30</v>
       </c>
-      <c r="O29" s="12">
+      <c r="O29" s="9">
         <v>30</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="7">
         <v>2</v>
       </c>
       <c r="Q29">
         <v>3</v>
       </c>
-      <c r="R29" s="12">
+      <c r="R29" s="9">
         <v>5</v>
       </c>
-      <c r="S29" s="10">
+      <c r="S29" s="7">
         <v>21</v>
       </c>
       <c r="T29">
         <v>2</v>
       </c>
-      <c r="U29" s="12">
-        <v>3</v>
-      </c>
-      <c r="V29"/>
-      <c r="AC29" s="13"/>
+      <c r="U29" s="9">
+        <v>3</v>
+      </c>
+      <c r="AC29" s="10"/>
       <c r="AE29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="1:31">
+    <row r="30" spans="1:31">
       <c r="A30">
         <v>31</v>
       </c>
@@ -3781,10 +3169,10 @@
       <c r="F30" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>4</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="9">
         <v>4</v>
       </c>
       <c r="J30">
@@ -3793,31 +3181,30 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="7">
         <v>33</v>
       </c>
       <c r="N30">
         <v>50</v>
       </c>
-      <c r="O30" s="12">
+      <c r="O30" s="9">
         <v>70</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="7">
         <v>2</v>
       </c>
       <c r="Q30">
         <v>2</v>
       </c>
-      <c r="R30" s="12">
+      <c r="R30" s="9">
         <v>4</v>
       </c>
-      <c r="S30"/>
-      <c r="AC30" s="14"/>
+      <c r="AC30" s="11"/>
       <c r="AE30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:31">
+    <row r="31" spans="1:31">
       <c r="A31">
         <v>32</v>
       </c>
@@ -3836,10 +3223,10 @@
       <c r="F31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="7">
         <v>4</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="9">
         <v>3</v>
       </c>
       <c r="J31">
@@ -3848,34 +3235,30 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M31" s="7">
         <v>33</v>
       </c>
       <c r="N31">
         <v>20</v>
       </c>
-      <c r="O31" s="12">
+      <c r="O31" s="9">
         <v>30</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="7">
         <v>35</v>
       </c>
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="R31" s="12">
-        <v>1</v>
-      </c>
-      <c r="S31"/>
-      <c r="T31"/>
-      <c r="U31"/>
-      <c r="V31"/>
-      <c r="AC31" s="14"/>
+      <c r="R31" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="11"/>
       <c r="AE31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:31">
+    <row r="32" spans="1:31">
       <c r="A32">
         <v>33</v>
       </c>
@@ -3894,10 +3277,10 @@
       <c r="F32" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="7">
         <v>7</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="9">
         <v>6</v>
       </c>
       <c r="J32">
@@ -3910,7 +3293,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" customFormat="1" hidden="1" spans="1:31">
+    <row r="33" spans="1:31" hidden="1">
       <c r="A33">
         <v>34</v>
       </c>
@@ -3929,10 +3312,10 @@
       <c r="F33" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="7">
         <v>8</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="9">
         <v>7</v>
       </c>
       <c r="J33">
@@ -3941,24 +3324,20 @@
       <c r="K33">
         <v>1</v>
       </c>
-      <c r="M33" s="10">
+      <c r="M33" s="7">
         <v>11</v>
       </c>
       <c r="N33">
         <v>38</v>
       </c>
-      <c r="O33" s="12">
+      <c r="O33" s="9">
         <v>52</v>
       </c>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
       <c r="AE33" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" customFormat="1" hidden="1" spans="1:31">
+    <row r="34" spans="1:31" hidden="1">
       <c r="A34">
         <v>35</v>
       </c>
@@ -3977,10 +3356,10 @@
       <c r="F34" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="10">
-        <v>3</v>
-      </c>
-      <c r="I34" s="12">
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="I34" s="9">
         <v>3</v>
       </c>
       <c r="J34">
@@ -3992,24 +3371,20 @@
       <c r="L34">
         <v>0</v>
       </c>
-      <c r="M34" s="10">
+      <c r="M34" s="7">
         <v>15</v>
       </c>
       <c r="N34">
         <v>3</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="9">
         <v>4</v>
       </c>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
       <c r="AE34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" customFormat="1" hidden="1" spans="1:31">
+    <row r="35" spans="1:31" hidden="1">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4028,10 +3403,10 @@
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="10">
-        <v>3</v>
-      </c>
-      <c r="I35" s="12">
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+      <c r="I35" s="9">
         <v>3</v>
       </c>
       <c r="J35">
@@ -4040,25 +3415,24 @@
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="M35" s="10">
+      <c r="M35" s="7">
         <v>11</v>
       </c>
       <c r="N35">
         <v>18</v>
       </c>
-      <c r="O35" s="12">
+      <c r="O35" s="9">
         <v>22</v>
       </c>
-      <c r="P35"/>
       <c r="AE35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" customFormat="1" hidden="1" spans="1:31">
+    <row r="36" spans="1:31" hidden="1">
       <c r="A36">
         <v>37</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="8">
         <v>144</v>
       </c>
       <c r="C36" t="s">
@@ -4073,10 +3447,10 @@
       <c r="F36" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="10">
-        <v>3</v>
-      </c>
-      <c r="I36" s="12">
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+      <c r="I36" s="9">
         <v>3</v>
       </c>
       <c r="J36">
@@ -4085,30 +3459,29 @@
       <c r="K36">
         <v>0</v>
       </c>
-      <c r="M36" s="10">
+      <c r="M36" s="7">
         <v>15</v>
       </c>
       <c r="N36">
         <v>3</v>
       </c>
-      <c r="O36" s="12">
+      <c r="O36" s="9">
         <v>4</v>
       </c>
-      <c r="P36" s="10">
+      <c r="P36" s="7">
         <v>2</v>
       </c>
       <c r="Q36">
         <v>6</v>
       </c>
-      <c r="R36" s="12">
+      <c r="R36" s="9">
         <v>8</v>
       </c>
-      <c r="S36"/>
       <c r="AE36" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="37" customFormat="1" hidden="1" spans="1:31">
+    <row r="37" spans="1:31" hidden="1">
       <c r="A37">
         <v>38</v>
       </c>
@@ -4127,10 +3500,10 @@
       <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="10">
-        <v>3</v>
-      </c>
-      <c r="I37" s="12">
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="I37" s="9">
         <v>3</v>
       </c>
       <c r="J37">
@@ -4139,30 +3512,29 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="M37" s="10">
+      <c r="M37" s="7">
         <v>7</v>
       </c>
       <c r="N37">
         <v>3</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="9">
         <v>4</v>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="7">
         <v>2</v>
       </c>
       <c r="Q37">
         <v>6</v>
       </c>
-      <c r="R37" s="12">
+      <c r="R37" s="9">
         <v>8</v>
       </c>
-      <c r="S37"/>
       <c r="AE37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:31">
+    <row r="38" spans="1:31">
       <c r="A38">
         <v>39</v>
       </c>
@@ -4181,10 +3553,10 @@
       <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="10">
-        <v>1</v>
-      </c>
-      <c r="I38" s="12">
+      <c r="H38" s="7">
+        <v>1</v>
+      </c>
+      <c r="I38" s="9">
         <v>1</v>
       </c>
       <c r="J38">
@@ -4193,30 +3565,29 @@
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="M38" s="10">
+      <c r="M38" s="7">
         <v>21</v>
       </c>
       <c r="N38">
         <v>4</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="9">
         <v>5</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="7">
         <v>2</v>
       </c>
       <c r="Q38">
         <v>3</v>
       </c>
-      <c r="R38" s="12">
+      <c r="R38" s="9">
         <v>5</v>
       </c>
-      <c r="S38"/>
       <c r="AE38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:31">
+    <row r="39" spans="1:31">
       <c r="A39">
         <v>40</v>
       </c>
@@ -4235,10 +3606,10 @@
       <c r="F39" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="10">
-        <v>1</v>
-      </c>
-      <c r="I39" s="12">
+      <c r="H39" s="7">
+        <v>1</v>
+      </c>
+      <c r="I39" s="9">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4247,30 +3618,29 @@
       <c r="K39">
         <v>1</v>
       </c>
-      <c r="M39" s="10">
+      <c r="M39" s="7">
         <v>5</v>
       </c>
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39" s="12">
-        <v>2</v>
-      </c>
-      <c r="P39" s="10">
+      <c r="O39" s="9">
+        <v>2</v>
+      </c>
+      <c r="P39" s="7">
         <v>2</v>
       </c>
       <c r="Q39">
         <v>6</v>
       </c>
-      <c r="R39" s="12">
+      <c r="R39" s="9">
         <v>7</v>
       </c>
-      <c r="S39"/>
       <c r="AE39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" customFormat="1" hidden="1" spans="1:31">
+    <row r="40" spans="1:31" hidden="1">
       <c r="A40">
         <v>41</v>
       </c>
@@ -4289,10 +3659,10 @@
       <c r="F40" t="s">
         <v>34</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="7">
         <v>4</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="9">
         <v>3</v>
       </c>
       <c r="J40">
@@ -4301,30 +3671,29 @@
       <c r="K40">
         <v>1</v>
       </c>
-      <c r="M40" s="10">
+      <c r="M40" s="7">
         <v>7</v>
       </c>
       <c r="N40">
         <v>4</v>
       </c>
-      <c r="O40" s="12">
+      <c r="O40" s="9">
         <v>5</v>
       </c>
-      <c r="P40" s="10">
+      <c r="P40" s="7">
         <v>38</v>
       </c>
       <c r="Q40">
         <v>4</v>
       </c>
-      <c r="R40" s="12">
+      <c r="R40" s="9">
         <v>5</v>
       </c>
-      <c r="S40"/>
       <c r="AE40" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" customFormat="1" hidden="1" spans="1:31">
+    <row r="41" spans="1:31" hidden="1">
       <c r="A41">
         <v>42</v>
       </c>
@@ -4343,10 +3712,10 @@
       <c r="F41" t="s">
         <v>34</v>
       </c>
-      <c r="H41" s="10">
-        <v>2</v>
-      </c>
-      <c r="I41" s="12">
+      <c r="H41" s="7">
+        <v>2</v>
+      </c>
+      <c r="I41" s="9">
         <v>2</v>
       </c>
       <c r="J41">
@@ -4355,30 +3724,29 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="M41" s="10">
+      <c r="M41" s="7">
         <v>6</v>
       </c>
       <c r="N41">
         <v>3</v>
       </c>
-      <c r="O41" s="12">
-        <v>3</v>
-      </c>
-      <c r="P41" s="10">
+      <c r="O41" s="9">
+        <v>3</v>
+      </c>
+      <c r="P41" s="7">
         <v>39</v>
       </c>
       <c r="Q41">
         <v>2</v>
       </c>
-      <c r="R41" s="12">
-        <v>3</v>
-      </c>
-      <c r="S41"/>
+      <c r="R41" s="9">
+        <v>3</v>
+      </c>
       <c r="AE41" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" customFormat="1" hidden="1" spans="1:31">
+    <row r="42" spans="1:31" hidden="1">
       <c r="A42">
         <v>43</v>
       </c>
@@ -4397,10 +3765,10 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="7">
         <v>4</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="9">
         <v>3</v>
       </c>
       <c r="J42">
@@ -4409,30 +3777,29 @@
       <c r="K42">
         <v>1</v>
       </c>
-      <c r="M42" s="10">
+      <c r="M42" s="7">
         <v>7</v>
       </c>
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42" s="12">
-        <v>3</v>
-      </c>
-      <c r="P42" s="10">
+      <c r="O42" s="9">
+        <v>3</v>
+      </c>
+      <c r="P42" s="7">
         <v>41</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
-      <c r="R42" s="12">
-        <v>1</v>
-      </c>
-      <c r="S42"/>
+      <c r="R42" s="9">
+        <v>1</v>
+      </c>
       <c r="AE42" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" customFormat="1" hidden="1" spans="1:31">
+    <row r="43" spans="1:31" hidden="1">
       <c r="A43">
         <v>44</v>
       </c>
@@ -4451,10 +3818,10 @@
       <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="7">
         <v>7</v>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="9">
         <v>4</v>
       </c>
       <c r="J43">
@@ -4463,39 +3830,38 @@
       <c r="K43">
         <v>1</v>
       </c>
-      <c r="M43" s="10">
+      <c r="M43" s="7">
         <v>6</v>
       </c>
       <c r="N43">
         <v>5</v>
       </c>
-      <c r="O43" s="12">
+      <c r="O43" s="9">
         <v>5</v>
       </c>
-      <c r="P43" s="10">
+      <c r="P43" s="7">
         <v>14</v>
       </c>
       <c r="Q43">
         <v>1</v>
       </c>
-      <c r="R43" s="12">
-        <v>1</v>
-      </c>
-      <c r="S43" s="10">
+      <c r="R43" s="9">
+        <v>1</v>
+      </c>
+      <c r="S43" s="7">
         <v>18</v>
       </c>
       <c r="T43">
         <v>0.9</v>
       </c>
-      <c r="U43" s="12">
+      <c r="U43" s="9">
         <v>1.2</v>
       </c>
-      <c r="V43"/>
       <c r="AE43" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" customFormat="1" hidden="1" spans="1:31">
+    <row r="44" spans="1:31" hidden="1">
       <c r="A44">
         <v>45</v>
       </c>
@@ -4514,10 +3880,10 @@
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="7">
         <v>6</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I44" s="9">
         <v>4</v>
       </c>
       <c r="J44">
@@ -4526,30 +3892,29 @@
       <c r="K44">
         <v>1</v>
       </c>
-      <c r="M44" s="10">
+      <c r="M44" s="7">
         <v>15</v>
       </c>
       <c r="N44">
         <v>2</v>
       </c>
-      <c r="O44" s="12">
-        <v>2</v>
-      </c>
-      <c r="P44" s="10">
+      <c r="O44" s="9">
+        <v>2</v>
+      </c>
+      <c r="P44" s="7">
         <v>42</v>
       </c>
       <c r="Q44">
         <v>8</v>
       </c>
-      <c r="R44" s="12">
+      <c r="R44" s="9">
         <v>12</v>
       </c>
-      <c r="S44"/>
       <c r="AE44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" customFormat="1" hidden="1" spans="1:31">
+    <row r="45" spans="1:31" hidden="1">
       <c r="A45">
         <v>46</v>
       </c>
@@ -4568,10 +3933,10 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="7">
         <v>5</v>
       </c>
-      <c r="I45" s="12">
+      <c r="I45" s="9">
         <v>4</v>
       </c>
       <c r="J45">
@@ -4580,39 +3945,38 @@
       <c r="K45">
         <v>1</v>
       </c>
-      <c r="M45" s="10">
+      <c r="M45" s="7">
         <v>7</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
-      <c r="O45" s="12">
+      <c r="O45" s="9">
         <v>9</v>
       </c>
-      <c r="P45" s="10">
+      <c r="P45" s="7">
         <v>26</v>
       </c>
       <c r="Q45">
         <v>2</v>
       </c>
-      <c r="R45" s="12">
-        <v>2</v>
-      </c>
-      <c r="S45" s="10">
+      <c r="R45" s="9">
+        <v>2</v>
+      </c>
+      <c r="S45" s="7">
         <v>2</v>
       </c>
       <c r="T45">
         <v>7</v>
       </c>
-      <c r="U45" s="12">
+      <c r="U45" s="9">
         <v>8</v>
       </c>
-      <c r="V45"/>
       <c r="AE45" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:31">
+    <row r="46" spans="1:31">
       <c r="A46">
         <v>47</v>
       </c>
@@ -4631,10 +3995,10 @@
       <c r="F46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="7">
         <v>10</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="9">
         <v>6</v>
       </c>
       <c r="J46">
@@ -4643,39 +4007,38 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="M46" s="10">
+      <c r="M46" s="7">
         <v>32</v>
       </c>
       <c r="N46">
         <v>40</v>
       </c>
-      <c r="O46" s="12">
+      <c r="O46" s="9">
         <v>40</v>
       </c>
-      <c r="P46" s="10">
+      <c r="P46" s="7">
         <v>33</v>
       </c>
       <c r="Q46">
         <v>30</v>
       </c>
-      <c r="R46" s="12">
+      <c r="R46" s="9">
         <v>30</v>
       </c>
-      <c r="S46" s="10">
+      <c r="S46" s="7">
         <v>19</v>
       </c>
       <c r="T46">
         <v>1</v>
       </c>
-      <c r="U46" s="12">
-        <v>1</v>
-      </c>
-      <c r="V46"/>
+      <c r="U46" s="9">
+        <v>1</v>
+      </c>
       <c r="AE46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" customFormat="1" hidden="1" spans="1:31">
+    <row r="47" spans="1:31" hidden="1">
       <c r="A47">
         <v>48</v>
       </c>
@@ -4694,10 +4057,10 @@
       <c r="F47" t="s">
         <v>34</v>
       </c>
-      <c r="H47" s="10">
-        <v>2</v>
-      </c>
-      <c r="I47" s="12">
+      <c r="H47" s="7">
+        <v>2</v>
+      </c>
+      <c r="I47" s="9">
         <v>1</v>
       </c>
       <c r="J47">
@@ -4706,28 +4069,23 @@
       <c r="K47">
         <v>0</v>
       </c>
-      <c r="M47" s="10">
+      <c r="M47" s="7">
         <v>11</v>
       </c>
       <c r="N47">
         <v>10</v>
       </c>
-      <c r="O47" s="12">
+      <c r="O47" s="9">
         <v>14</v>
       </c>
-      <c r="P47"/>
-      <c r="Q47"/>
-      <c r="R47"/>
-      <c r="S47"/>
       <c r="AE47" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="48" customFormat="1" hidden="1" spans="1:31">
+    <row r="48" spans="1:31" hidden="1">
       <c r="A48">
         <v>49</v>
       </c>
-      <c r="B48"/>
       <c r="C48" t="s">
         <v>132</v>
       </c>
@@ -4740,10 +4098,10 @@
       <c r="F48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="7">
         <v>4</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="9">
         <v>3</v>
       </c>
       <c r="J48">
@@ -4752,33 +4110,29 @@
       <c r="K48">
         <v>0</v>
       </c>
-      <c r="M48" s="10">
+      <c r="M48" s="7">
         <v>11</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
-      <c r="O48" s="12">
+      <c r="O48" s="9">
         <v>11</v>
       </c>
-      <c r="P48" s="10">
+      <c r="P48" s="7">
         <v>6</v>
       </c>
       <c r="Q48">
         <v>3</v>
       </c>
-      <c r="R48" s="12">
-        <v>3</v>
-      </c>
-      <c r="S48"/>
-      <c r="T48"/>
-      <c r="U48"/>
-      <c r="V48"/>
+      <c r="R48" s="9">
+        <v>3</v>
+      </c>
       <c r="AE48" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" customFormat="1" hidden="1" spans="1:31">
+    <row r="49" spans="1:31" hidden="1">
       <c r="A49">
         <v>50</v>
       </c>
@@ -4797,10 +4151,10 @@
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="7">
         <v>4</v>
       </c>
-      <c r="I49" s="12">
+      <c r="I49" s="9">
         <v>3</v>
       </c>
       <c r="J49">
@@ -4809,33 +4163,29 @@
       <c r="K49">
         <v>0</v>
       </c>
-      <c r="M49" s="10">
+      <c r="M49" s="7">
         <v>11</v>
       </c>
       <c r="N49">
         <v>7</v>
       </c>
-      <c r="O49" s="12">
+      <c r="O49" s="9">
         <v>11</v>
       </c>
-      <c r="P49" s="10">
+      <c r="P49" s="7">
         <v>45</v>
       </c>
       <c r="Q49">
         <v>2</v>
       </c>
-      <c r="R49" s="12">
-        <v>3</v>
-      </c>
-      <c r="S49"/>
-      <c r="T49"/>
-      <c r="U49"/>
-      <c r="V49"/>
+      <c r="R49" s="9">
+        <v>3</v>
+      </c>
       <c r="AE49" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50" customFormat="1" hidden="1" spans="1:31">
+    <row r="50" spans="1:31" hidden="1">
       <c r="A50">
         <v>51</v>
       </c>
@@ -4854,10 +4204,10 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="7">
         <v>5</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="9">
         <v>4</v>
       </c>
       <c r="J50">
@@ -4866,30 +4216,29 @@
       <c r="K50">
         <v>1</v>
       </c>
-      <c r="M50" s="10">
+      <c r="M50" s="7">
         <v>6</v>
       </c>
       <c r="N50">
         <v>5</v>
       </c>
-      <c r="O50" s="12">
+      <c r="O50" s="9">
         <v>7</v>
       </c>
-      <c r="P50" s="10">
+      <c r="P50" s="7">
         <v>18</v>
       </c>
       <c r="Q50">
-        <v>1.1</v>
-      </c>
-      <c r="R50" s="12">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R50" s="9">
         <v>1.7</v>
       </c>
-      <c r="S50"/>
       <c r="AE50" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" customFormat="1" hidden="1" spans="1:31">
+    <row r="51" spans="1:31" hidden="1">
       <c r="A51">
         <v>52</v>
       </c>
@@ -4908,10 +4257,10 @@
       <c r="F51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="7">
         <v>9</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="9">
         <v>6</v>
       </c>
       <c r="J51">
@@ -4920,30 +4269,29 @@
       <c r="K51">
         <v>1</v>
       </c>
-      <c r="M51" s="10">
+      <c r="M51" s="7">
         <v>6</v>
       </c>
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51" s="12">
-        <v>3</v>
-      </c>
-      <c r="P51" s="10">
+      <c r="O51" s="9">
+        <v>3</v>
+      </c>
+      <c r="P51" s="7">
         <v>49</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
-      <c r="R51" s="12">
-        <v>1</v>
-      </c>
-      <c r="S51"/>
+      <c r="R51" s="9">
+        <v>1</v>
+      </c>
       <c r="AE51" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:31">
+    <row r="52" spans="1:31">
       <c r="A52">
         <v>53</v>
       </c>
@@ -4962,10 +4310,10 @@
       <c r="F52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" s="10">
-        <v>1</v>
-      </c>
-      <c r="I52" s="12">
+      <c r="H52" s="7">
+        <v>1</v>
+      </c>
+      <c r="I52" s="9">
         <v>0</v>
       </c>
       <c r="J52">
@@ -4974,30 +4322,29 @@
       <c r="K52">
         <v>1</v>
       </c>
-      <c r="M52" s="10">
+      <c r="M52" s="7">
         <v>9</v>
       </c>
       <c r="N52">
         <v>2</v>
       </c>
-      <c r="O52" s="12">
-        <v>2</v>
-      </c>
-      <c r="P52" s="10">
+      <c r="O52" s="9">
+        <v>2</v>
+      </c>
+      <c r="P52" s="7">
         <v>21</v>
       </c>
       <c r="Q52">
         <v>2</v>
       </c>
-      <c r="R52" s="12">
-        <v>2</v>
-      </c>
-      <c r="S52"/>
+      <c r="R52" s="9">
+        <v>2</v>
+      </c>
       <c r="AE52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" customFormat="1" hidden="1" spans="1:31">
+    <row r="53" spans="1:31" hidden="1">
       <c r="A53">
         <v>54</v>
       </c>
@@ -5016,10 +4363,10 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="7">
         <v>5</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="9">
         <v>5</v>
       </c>
       <c r="J53">
@@ -5031,30 +4378,29 @@
       <c r="L53">
         <v>6</v>
       </c>
-      <c r="M53" s="10">
+      <c r="M53" s="7">
         <v>50</v>
       </c>
       <c r="N53">
         <v>3</v>
       </c>
-      <c r="O53" s="12">
+      <c r="O53" s="9">
         <v>4</v>
       </c>
-      <c r="P53" s="10">
+      <c r="P53" s="7">
         <v>51</v>
       </c>
       <c r="Q53">
         <v>-0.5</v>
       </c>
-      <c r="R53" s="12">
+      <c r="R53" s="9">
         <v>-0.5</v>
       </c>
-      <c r="S53"/>
       <c r="AE53" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" customFormat="1" hidden="1" spans="1:31">
+    <row r="54" spans="1:31" hidden="1">
       <c r="A54">
         <v>55</v>
       </c>
@@ -5076,10 +4422,10 @@
       <c r="G54">
         <v>14</v>
       </c>
-      <c r="H54" s="10">
-        <v>2</v>
-      </c>
-      <c r="I54" s="12">
+      <c r="H54" s="7">
+        <v>2</v>
+      </c>
+      <c r="I54" s="9">
         <v>1</v>
       </c>
       <c r="J54">
@@ -5088,39 +4434,38 @@
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="M54" s="10">
+      <c r="M54" s="7">
         <v>15</v>
       </c>
       <c r="N54">
         <v>3</v>
       </c>
-      <c r="O54" s="12">
+      <c r="O54" s="9">
         <v>4</v>
       </c>
-      <c r="P54" s="10">
+      <c r="P54" s="7">
         <v>14</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
-      <c r="R54" s="12">
-        <v>1</v>
-      </c>
-      <c r="S54" s="10">
+      <c r="R54" s="9">
+        <v>1</v>
+      </c>
+      <c r="S54" s="7">
         <v>52</v>
       </c>
       <c r="T54">
         <v>3</v>
       </c>
-      <c r="U54" s="12">
+      <c r="U54" s="9">
         <v>5</v>
       </c>
-      <c r="V54"/>
       <c r="AE54" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="55" customFormat="1" hidden="1" spans="1:31">
+    <row r="55" spans="1:31" hidden="1">
       <c r="A55">
         <v>56</v>
       </c>
@@ -5139,10 +4484,10 @@
       <c r="F55" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="7">
         <v>4</v>
       </c>
-      <c r="I55" s="12">
+      <c r="I55" s="9">
         <v>3</v>
       </c>
       <c r="J55">
@@ -5160,22 +4505,21 @@
       <c r="O55">
         <v>3</v>
       </c>
-      <c r="P55" s="10">
+      <c r="P55" s="7">
         <v>60</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
-      <c r="R55" s="12">
-        <v>1</v>
-      </c>
-      <c r="S55"/>
-      <c r="AA55" s="12"/>
+      <c r="R55" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="9"/>
       <c r="AE55" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="56" customFormat="1" hidden="1" spans="3:31">
+    <row r="56" spans="1:31" hidden="1">
       <c r="C56" t="s">
         <v>147</v>
       </c>
@@ -5188,10 +4532,10 @@
       <c r="F56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" s="10">
-        <v>3</v>
-      </c>
-      <c r="I56" s="12">
+      <c r="H56" s="7">
+        <v>3</v>
+      </c>
+      <c r="I56" s="9">
         <v>2</v>
       </c>
       <c r="J56">
@@ -5200,7 +4544,6 @@
       <c r="K56">
         <v>0</v>
       </c>
-      <c r="L56"/>
       <c r="M56">
         <v>15</v>
       </c>
@@ -5210,22 +4553,21 @@
       <c r="O56">
         <v>2</v>
       </c>
-      <c r="P56" s="10">
+      <c r="P56" s="7">
         <v>45</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
-      <c r="R56" s="12">
-        <v>2</v>
-      </c>
-      <c r="S56"/>
-      <c r="AA56" s="12"/>
+      <c r="R56" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA56" s="9"/>
       <c r="AE56" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" customFormat="1" hidden="1" spans="2:31">
+    <row r="57" spans="1:31" hidden="1">
       <c r="B57" t="s">
         <v>148</v>
       </c>
@@ -5244,10 +4586,10 @@
       <c r="G57">
         <v>3</v>
       </c>
-      <c r="H57" s="10">
-        <v>2</v>
-      </c>
-      <c r="I57" s="12">
+      <c r="H57" s="7">
+        <v>2</v>
+      </c>
+      <c r="I57" s="9">
         <v>1</v>
       </c>
       <c r="J57">
@@ -5265,30 +4607,30 @@
       <c r="O57">
         <v>4</v>
       </c>
-      <c r="P57" s="10">
+      <c r="P57" s="7">
         <v>11</v>
       </c>
       <c r="Q57">
         <v>12</v>
       </c>
-      <c r="R57" s="12">
+      <c r="R57" s="9">
         <v>18</v>
       </c>
-      <c r="S57" s="10">
+      <c r="S57" s="7">
         <v>14</v>
       </c>
       <c r="T57">
         <v>1</v>
       </c>
-      <c r="U57" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="12"/>
+      <c r="U57" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="9"/>
       <c r="AE57" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="58" customFormat="1" hidden="1" spans="2:31">
+    <row r="58" spans="1:31" hidden="1">
       <c r="B58" t="s">
         <v>150</v>
       </c>
@@ -5304,10 +4646,10 @@
       <c r="F58" t="s">
         <v>34</v>
       </c>
-      <c r="H58" s="10">
-        <v>3</v>
-      </c>
-      <c r="I58" s="12">
+      <c r="H58" s="7">
+        <v>3</v>
+      </c>
+      <c r="I58" s="9">
         <v>3</v>
       </c>
       <c r="J58">
@@ -5316,29 +4658,29 @@
       <c r="K58">
         <v>1</v>
       </c>
-      <c r="M58" s="10">
+      <c r="M58" s="7">
         <v>45</v>
       </c>
       <c r="N58">
         <v>2</v>
       </c>
-      <c r="O58" s="12">
-        <v>3</v>
-      </c>
-      <c r="P58" s="10">
+      <c r="O58" s="9">
+        <v>3</v>
+      </c>
+      <c r="P58" s="7">
         <v>2</v>
       </c>
       <c r="Q58">
         <v>2</v>
       </c>
-      <c r="R58" s="12">
+      <c r="R58" s="9">
         <v>3</v>
       </c>
       <c r="AE58" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="59" customFormat="1" hidden="1" spans="2:31">
+    <row r="59" spans="1:31" hidden="1">
       <c r="B59" t="s">
         <v>152</v>
       </c>
@@ -5354,10 +4696,10 @@
       <c r="F59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="10">
-        <v>3</v>
-      </c>
-      <c r="I59" s="12">
+      <c r="H59" s="7">
+        <v>3</v>
+      </c>
+      <c r="I59" s="9">
         <v>3</v>
       </c>
       <c r="J59">
@@ -5370,7 +4712,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" customFormat="1" hidden="1" spans="2:31">
+    <row r="60" spans="1:31" hidden="1">
       <c r="B60" t="s">
         <v>154</v>
       </c>
@@ -5389,10 +4731,10 @@
       <c r="G60">
         <v>3</v>
       </c>
-      <c r="H60" s="10">
-        <v>2</v>
-      </c>
-      <c r="I60" s="12">
+      <c r="H60" s="7">
+        <v>2</v>
+      </c>
+      <c r="I60" s="9">
         <v>1</v>
       </c>
       <c r="J60">
@@ -5401,63 +4743,60 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="M60" s="10">
+      <c r="M60" s="7">
         <v>2</v>
       </c>
       <c r="N60">
         <v>5</v>
       </c>
-      <c r="O60" s="12">
+      <c r="O60" s="9">
         <v>6</v>
       </c>
-      <c r="P60" s="10">
+      <c r="P60" s="7">
         <v>2</v>
       </c>
       <c r="Q60">
         <v>5</v>
       </c>
-      <c r="R60" s="12">
+      <c r="R60" s="9">
         <v>6</v>
       </c>
       <c r="AE60" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="61" hidden="1"/>
-    <row r="62" hidden="1"/>
+    <row r="61" spans="1:31" hidden="1"/>
+    <row r="62" spans="1:31" hidden="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE62" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:AE62" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="30">
       <filters>
         <filter val="F"/>
       </filters>
     </filterColumn>
-    <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J62"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I62"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="19.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="18.8583333333333" customWidth="1"/>
-    <col min="7" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.1416666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5473,7 +4812,7 @@
       <c r="E1" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>157</v>
       </c>
       <c r="G1" t="s">
@@ -5486,7 +4825,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5502,9 +4841,8 @@
       <c r="I2">
         <v>-1</v>
       </c>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" customFormat="1" spans="1:9">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5527,7 +4865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:9">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5547,7 +4885,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5567,7 +4905,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:9">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5584,7 +4922,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:9">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5604,7 +4942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:9">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5624,7 +4962,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:9">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5644,7 +4982,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:9">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5664,7 +5002,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:9">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5681,7 +5019,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:9">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5701,7 +5039,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:9">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5721,7 +5059,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:9">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5744,7 +5082,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:9">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5764,7 +5102,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:9">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5784,7 +5122,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:9">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5804,7 +5142,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:9">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5824,7 +5162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5844,7 +5182,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:9">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5864,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:9">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5884,7 +5222,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:9">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5904,7 +5242,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:9">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5924,7 +5262,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:9">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5947,7 +5285,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:9">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5967,7 +5305,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:9">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5990,7 +5328,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:9">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>25</v>
       </c>
@@ -6010,7 +5348,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:9">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>26</v>
       </c>
@@ -6030,7 +5368,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:9">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>27</v>
       </c>
@@ -6056,7 +5394,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="1:9">
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>28</v>
       </c>
@@ -6076,7 +5414,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:9">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>29</v>
       </c>
@@ -6099,7 +5437,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:9">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>30</v>
       </c>
@@ -6122,7 +5460,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:9">
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>31</v>
       </c>
@@ -6145,7 +5483,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:9">
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>32</v>
       </c>
@@ -6165,7 +5503,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:9">
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>33</v>
       </c>
@@ -6185,7 +5523,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:9">
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>34</v>
       </c>
@@ -6211,7 +5549,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" customFormat="1" spans="1:9">
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>35</v>
       </c>
@@ -6231,7 +5569,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:9">
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>36</v>
       </c>
@@ -6251,7 +5589,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:9">
+    <row r="39" spans="1:9">
       <c r="A39">
         <v>37</v>
       </c>
@@ -6274,7 +5612,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:9">
+    <row r="40" spans="1:9">
       <c r="A40">
         <v>38</v>
       </c>
@@ -6294,7 +5632,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" customFormat="1" spans="1:9">
+    <row r="41" spans="1:9">
       <c r="A41">
         <v>39</v>
       </c>
@@ -6317,7 +5655,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:9">
+    <row r="42" spans="1:9">
       <c r="A42">
         <v>40</v>
       </c>
@@ -6343,7 +5681,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="43" customFormat="1" spans="1:9">
+    <row r="43" spans="1:9">
       <c r="A43">
         <v>41</v>
       </c>
@@ -6363,7 +5701,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="1:9">
+    <row r="44" spans="1:9">
       <c r="A44">
         <v>42</v>
       </c>
@@ -6383,7 +5721,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:9">
+    <row r="45" spans="1:9">
       <c r="A45">
         <v>43</v>
       </c>
@@ -6406,7 +5744,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:9">
+    <row r="46" spans="1:9">
       <c r="A46">
         <v>44</v>
       </c>
@@ -6426,7 +5764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="1:9">
+    <row r="47" spans="1:9">
       <c r="A47">
         <v>45</v>
       </c>
@@ -6446,7 +5784,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" customFormat="1" spans="1:9">
+    <row r="48" spans="1:9">
       <c r="A48">
         <v>46</v>
       </c>
@@ -6469,7 +5807,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" customFormat="1" spans="1:9">
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>47</v>
       </c>
@@ -6489,7 +5827,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:9">
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>48</v>
       </c>
@@ -6512,7 +5850,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="51" customFormat="1" spans="1:9">
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>49</v>
       </c>
@@ -6532,7 +5870,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:9">
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>50</v>
       </c>
@@ -6552,7 +5890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" customFormat="1" spans="1:9">
+    <row r="53" spans="1:9">
       <c r="A53">
         <v>51</v>
       </c>
@@ -6572,7 +5910,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:9">
+    <row r="54" spans="1:9">
       <c r="A54">
         <v>52</v>
       </c>
@@ -6595,7 +5933,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:9">
+    <row r="55" spans="1:9">
       <c r="A55">
         <v>53</v>
       </c>
@@ -6618,7 +5956,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="56" customFormat="1" spans="1:9">
+    <row r="56" spans="1:9">
       <c r="A56">
         <v>54</v>
       </c>
@@ -6641,7 +5979,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" customFormat="1" spans="1:9">
+    <row r="57" spans="1:9">
       <c r="A57">
         <v>55</v>
       </c>
@@ -6664,7 +6002,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="58" customFormat="1" spans="1:9">
+    <row r="58" spans="1:9">
       <c r="A58">
         <v>56</v>
       </c>
@@ -6687,7 +6025,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="59" customFormat="1" spans="1:9">
+    <row r="59" spans="1:9">
       <c r="A59">
         <v>57</v>
       </c>
@@ -6710,7 +6048,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="60" customFormat="1" spans="1:9">
+    <row r="60" spans="1:9">
       <c r="A60">
         <v>58</v>
       </c>
@@ -6733,7 +6071,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="61" customFormat="1" spans="1:9">
+    <row r="61" spans="1:9">
       <c r="A61">
         <v>59</v>
       </c>
@@ -6756,7 +6094,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="62" customFormat="1" spans="1:9">
+    <row r="62" spans="1:9">
       <c r="A62">
         <v>60</v>
       </c>
@@ -6778,30 +6116,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.425" customWidth="1"/>
-    <col min="2" max="2" width="27.425" customWidth="1"/>
-    <col min="3" max="3" width="14.425" customWidth="1"/>
-    <col min="4" max="5" width="16.1416666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.425" customWidth="1"/>
-    <col min="7" max="7" width="14.425" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:15">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6814,7 +6150,7 @@
       <c r="D1" t="s">
         <v>258</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>259</v>
       </c>
       <c r="F1" t="s">
@@ -6848,7 +6184,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6877,7 +6213,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:7">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6900,7 +6236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:5">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -6917,7 +6253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:11">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>3</v>
       </c>
@@ -6952,7 +6288,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:7">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
@@ -6975,7 +6311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:7">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
@@ -6998,7 +6334,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:7">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7021,7 +6357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:7">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7044,7 +6380,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:7">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7067,7 +6403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:9">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>9</v>
       </c>
@@ -7096,7 +6432,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:9">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>10</v>
       </c>
@@ -7125,7 +6461,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:7">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>11</v>
       </c>
@@ -7148,7 +6484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:7">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>12</v>
       </c>
@@ -7171,7 +6507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:7">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>13</v>
       </c>
@@ -7194,7 +6530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:7">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7217,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>15</v>
       </c>
@@ -7236,11 +6572,11 @@
       <c r="F17">
         <v>46</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>16</v>
       </c>
@@ -7263,7 +6599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>17</v>
       </c>
@@ -7280,7 +6616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>18</v>
       </c>
@@ -7297,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>19</v>
       </c>
@@ -7314,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:7">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>20</v>
       </c>
@@ -7339,27 +6675,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85833333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.7083333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="15.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.1416666666667" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1416666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7382,7 +6716,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
@@ -7402,7 +6736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="13" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="12.95" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7419,7 +6753,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="13" customHeight="1" spans="1:6">
+    <row r="4" spans="1:7" ht="12.95" customHeight="1">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7436,7 +6770,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7456,7 +6790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7476,7 +6810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7496,7 +6830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7516,7 +6850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7536,7 +6870,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7558,23 +6892,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.425" customWidth="1"/>
-    <col min="3" max="3" width="29.425" customWidth="1"/>
-    <col min="4" max="4" width="28.425" customWidth="1"/>
-    <col min="5" max="5" width="15.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="17.2833333333333" customWidth="1"/>
-    <col min="7" max="7" width="15.7083333333333" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7708,7 +7040,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -7722,7 +7054,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -7736,7 +7068,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -7753,24 +7085,36 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D11" t="s">
+        <v>356</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="17.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="19.425" customWidth="1"/>
-    <col min="5" max="5" width="19.7083333333333" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7807,33 +7151,45 @@
         <v>38</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.425" customWidth="1"/>
-    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.1416666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.1416666666667" customWidth="1"/>
-    <col min="5" max="5" width="8.14166666666667" customWidth="1"/>
-    <col min="6" max="6" width="8.425" customWidth="1"/>
-    <col min="7" max="7" width="6.85833333333333" customWidth="1"/>
-    <col min="8" max="8" width="10.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="15.5666666666667" customWidth="1"/>
-    <col min="10" max="10" width="16.8583333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -7886,10 +7242,10 @@
       <c r="G2">
         <v>90</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>325</v>
       </c>
       <c r="J2" t="s">
@@ -7918,10 +7274,10 @@
       <c r="G3">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>324</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>326</v>
       </c>
       <c r="J3" t="s">
@@ -7953,7 +7309,7 @@
       <c r="H4" t="s">
         <v>324</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>327</v>
       </c>
       <c r="J4" t="s">
@@ -7982,10 +7338,10 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>330</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>331</v>
       </c>
       <c r="J5" t="s">
@@ -8014,10 +7370,10 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" t="s">
         <v>330</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>331</v>
       </c>
       <c r="J6" t="s">
@@ -8049,7 +7405,7 @@
       <c r="H7" t="s">
         <v>330</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>331</v>
       </c>
       <c r="J7" t="s">
@@ -8078,7 +7434,7 @@
       <c r="H8" t="s">
         <v>330</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>338</v>
       </c>
       <c r="J8" t="s">
@@ -8107,7 +7463,7 @@
       <c r="H9" t="s">
         <v>330</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>340</v>
       </c>
       <c r="J9" t="s">
@@ -8136,45 +7492,71 @@
       <c r="H10" t="s">
         <v>330</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>342</v>
       </c>
       <c r="J10" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="11" spans="9:9">
-      <c r="I11" s="6"/>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>366</v>
+      </c>
+      <c r="D11" t="s">
+        <v>330</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>330</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="J11" t="s">
+        <v>366</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.425" customWidth="1"/>
-    <col min="2" max="2" width="21.8583333333333" customWidth="1"/>
-    <col min="3" max="3" width="22.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="11.5666666666667" customWidth="1"/>
-    <col min="5" max="6" width="11.425" customWidth="1"/>
-    <col min="7" max="7" width="6.70833333333333" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="15.7083333333333" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="15.8583333333333" customWidth="1"/>
-    <col min="13" max="13" width="13.1416666666667" customWidth="1"/>
-    <col min="14" max="14" width="10.425" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8202,7 +7584,7 @@
       <c r="I1" t="s">
         <v>322</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>344</v>
       </c>
       <c r="K1" t="s">
@@ -8217,8 +7599,11 @@
       <c r="N1" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="8" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8228,22 +7613,22 @@
       <c r="C2" t="s">
         <v>349</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>350</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>34</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>350</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>351</v>
       </c>
       <c r="J2">
@@ -8261,8 +7646,9 @@
       <c r="N2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" s="12"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8272,13 +7658,13 @@
       <c r="C3" t="s">
         <v>352</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>350</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>34</v>
       </c>
       <c r="G3">
@@ -8287,7 +7673,7 @@
       <c r="H3" t="s">
         <v>350</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>351</v>
       </c>
       <c r="J3">
@@ -8305,8 +7691,9 @@
       <c r="N3">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>2</v>
       </c>
@@ -8316,22 +7703,22 @@
       <c r="C4" t="s">
         <v>353</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>350</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>34</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>350</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>351</v>
       </c>
       <c r="J4">
@@ -8349,10 +7736,248 @@
       <c r="N4">
         <v>7</v>
       </c>
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>10000</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+      <c r="N5">
+        <v>7</v>
+      </c>
+      <c r="O5" s="12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>350</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
+        <v>10000</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>7</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>10000</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+      <c r="N7">
+        <v>7</v>
+      </c>
+      <c r="O7" s="12">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DF55B0-B4EA-4D8B-B63F-C4BA2DDECCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4C3E14-6D64-4D5E-8F03-AF9EE73B099B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="RaisingEffects" sheetId="5" r:id="rId5"/>
     <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
     <sheet name="DialogueEvents" sheetId="7" r:id="rId7"/>
-    <sheet name="StreamEvents" sheetId="8" r:id="rId8"/>
-    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId9"/>
+    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId8"/>
+    <sheet name="StreamEvents" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="372">
   <si>
     <t>ID</t>
   </si>
@@ -1127,22 +1127,37 @@
     <t>VPhaseEndingAttributeCondition</t>
   </si>
   <si>
-    <t xml:space="preserve">CASingingAbility </t>
-  </si>
-  <si>
     <t>Conditions</t>
   </si>
   <si>
     <t>VPhaseEndingEventCondition</t>
   </si>
   <si>
-    <t>1,3</t>
-  </si>
-  <si>
     <t>#00B054</t>
   </si>
   <si>
     <t>PhaseStart</t>
+  </si>
+  <si>
+    <t>0, 2</t>
+  </si>
+  <si>
+    <t>Ending4</t>
+  </si>
+  <si>
+    <t>Ending5</t>
+  </si>
+  <si>
+    <t>Ending6</t>
+  </si>
+  <si>
+    <t>#00B055</t>
+  </si>
+  <si>
+    <t>PhaseStart2</t>
+  </si>
+  <si>
+    <t>AddRandomRare</t>
   </si>
 </sst>
 </file>
@@ -6898,7 +6913,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -7099,9 +7114,26 @@
         <v>356</v>
       </c>
     </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D12" t="s">
+        <v>317</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7173,7 +7205,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" customWidth="1"/>
@@ -7504,7 +7536,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D11" t="s">
         <v>330</v>
@@ -7522,10 +7554,39 @@
         <v>330</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J11" t="s">
-        <v>366</v>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>330</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="J12" t="s">
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -7536,8 +7597,106 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -7600,7 +7759,7 @@
         <v>348</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -7829,7 +7988,7 @@
         <v>7</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -7876,108 +8035,152 @@
         <v>7</v>
       </c>
       <c r="O7" s="12">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C8" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" t="s">
+        <v>350</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>350</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>30</v>
+      </c>
+      <c r="L8">
+        <v>10000</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+      <c r="N8">
+        <v>7</v>
+      </c>
+      <c r="O8" s="12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>350</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>30</v>
+      </c>
+      <c r="L9">
+        <v>10000</v>
+      </c>
+      <c r="M9">
+        <v>6</v>
+      </c>
+      <c r="N9">
+        <v>7</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>350</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>30</v>
+      </c>
+      <c r="L10">
+        <v>10000</v>
+      </c>
+      <c r="M10">
+        <v>6</v>
+      </c>
+      <c r="N10">
+        <v>7</v>
+      </c>
+      <c r="O10" s="12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>363</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4C3E14-6D64-4D5E-8F03-AF9EE73B099B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B9A809-96B9-452A-BEF9-59ADE7EAA7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="374">
   <si>
     <t>ID</t>
   </si>
@@ -1158,6 +1158,12 @@
   </si>
   <si>
     <t>AddRandomRare</t>
+  </si>
+  <si>
+    <t>Replace</t>
+  </si>
+  <si>
+    <t>VRaisingReplaceCardEffect</t>
   </si>
 </sst>
 </file>
@@ -6913,7 +6919,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -7128,6 +7134,23 @@
         <v>317</v>
       </c>
       <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D13" t="s">
+        <v>373</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B9A809-96B9-452A-BEF9-59ADE7EAA7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AFFF1E-4006-4AFB-BE36-9E277CD849F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="379">
   <si>
     <t>ID</t>
   </si>
@@ -1164,6 +1164,21 @@
   </si>
   <si>
     <t>VRaisingReplaceCardEffect</t>
+  </si>
+  <si>
+    <t>Select3</t>
+  </si>
+  <si>
+    <t>VRaisingAddSelectedFrom3Effect</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>VCardPoolCondition</t>
+  </si>
+  <si>
+    <t>0,1,2</t>
   </si>
 </sst>
 </file>
@@ -6919,7 +6934,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -7154,6 +7169,23 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C14" t="s">
+        <v>372</v>
+      </c>
+      <c r="D14" t="s">
+        <v>375</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7162,13 +7194,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7218,6 +7250,20 @@
       </c>
       <c r="E3" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AFFF1E-4006-4AFB-BE36-9E277CD849F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896509AF-F5C6-4E31-9F13-A26265473CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,14 @@
     <sheet name="Conditions" sheetId="4" r:id="rId4"/>
     <sheet name="RaisingEffects" sheetId="5" r:id="rId5"/>
     <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
-    <sheet name="DialogueEvents" sheetId="7" r:id="rId7"/>
-    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId8"/>
-    <sheet name="StreamEvents" sheetId="8" r:id="rId9"/>
+    <sheet name="StreamEvents" sheetId="8" r:id="rId7"/>
+    <sheet name="DialogueEvents" sheetId="7" r:id="rId8"/>
+    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId9"/>
+    <sheet name="Relics" sheetId="11" r:id="rId10"/>
+    <sheet name="RaisingRelicConditions" sheetId="13" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="390">
   <si>
     <t>ID</t>
   </si>
@@ -164,9 +166,6 @@
     <t>闪耀</t>
   </si>
   <si>
-    <t>参数+15</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -176,12 +175,6 @@
     <t>参数+5，神采+4</t>
   </si>
   <si>
-    <t>网络波动</t>
-  </si>
-  <si>
-    <t>下一张使用的牌会使用两次</t>
-  </si>
-  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -356,21 +349,12 @@
     <t>爆！</t>
   </si>
   <si>
-    <t>参数+38</t>
-  </si>
-  <si>
     <t>越想越气</t>
   </si>
   <si>
     <t>红温+2，有红温的状态下，红温+2，红温大于30层时，红温+4</t>
   </si>
   <si>
-    <t>欢呼</t>
-  </si>
-  <si>
-    <t>参数+18</t>
-  </si>
-  <si>
     <t>红温+3，神采+6</t>
   </si>
   <si>
@@ -485,27 +469,12 @@
     <t>红温+1，以后每当使用A卡的时候，红温+1</t>
   </si>
   <si>
-    <t>红温+2，幽默+1</t>
-  </si>
-  <si>
     <t>自洽</t>
   </si>
   <si>
     <t>幽默+3，参数+12，卡牌使用次数+1</t>
   </si>
   <si>
-    <t>早上好！</t>
-  </si>
-  <si>
-    <t>开局加入手牌，幽默+2，神采+2</t>
-  </si>
-  <si>
-    <t>拜拜！！！</t>
-  </si>
-  <si>
-    <t>最后一回合加入手牌，</t>
-  </si>
-  <si>
     <t>封禁</t>
   </si>
   <si>
@@ -1179,6 +1148,72 @@
   </si>
   <si>
     <t>0,1,2</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>ConditionType</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>VBattleRelicConfiguration</t>
+  </si>
+  <si>
+    <t>OnTurnBegin</t>
+  </si>
+  <si>
+    <t>VCardOperationRelicCondition</t>
+  </si>
+  <si>
+    <t>Equal</t>
+  </si>
+  <si>
+    <t>参数+15，红温大于10层时，参数+9</t>
+  </si>
+  <si>
+    <t>kale</t>
+  </si>
+  <si>
+    <t>下一张使用的牌会使用两次，抽一张卡,神采+2</t>
+  </si>
+  <si>
+    <t>参数+38，红温大于30层时，卡牌使用次数+1</t>
+  </si>
+  <si>
+    <t>为我欢呼</t>
+  </si>
+  <si>
+    <t>幽默+1，以后每当使用M卡时，幽默+1</t>
+  </si>
+  <si>
+    <t>节目效果</t>
+  </si>
+  <si>
+    <t>获得神采120%的参数</t>
+  </si>
+  <si>
+    <t>LLBC</t>
+  </si>
+  <si>
+    <t>神采+7，获得神采90%的参数</t>
+  </si>
+  <si>
+    <t>大爆特爆</t>
+  </si>
+  <si>
+    <t>消耗所有神采，获得消耗神采300%的参数</t>
+  </si>
+  <si>
+    <t>冷笑话</t>
+  </si>
+  <si>
+    <t>获得神采100%的参数，下一回合抽一张卡牌</t>
   </si>
 </sst>
 </file>
@@ -1586,32 +1621,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AE62"/>
+  <dimension ref="A1:AE61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="9" customWidth="1"/>
     <col min="8" max="8" width="7.140625" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14" style="9" customWidth="1"/>
     <col min="10" max="10" width="10.28515625" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="13" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="9" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
     <col min="14" max="14" width="12.140625" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" customWidth="1"/>
+    <col min="15" max="15" width="17.7109375" style="9" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
     <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" customWidth="1"/>
-    <col min="21" max="21" width="17.7109375" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" style="9" customWidth="1"/>
+    <col min="21" max="21" width="17.7109375" style="9" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" customWidth="1"/>
-    <col min="25" max="26" width="12.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" style="9" customWidth="1"/>
+    <col min="25" max="25" width="12.42578125" customWidth="1"/>
+    <col min="26" max="26" width="12.42578125" style="9" customWidth="1"/>
     <col min="27" max="27" width="12.28515625" customWidth="1"/>
+    <col min="28" max="28" width="9" style="9"/>
     <col min="29" max="29" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1634,10 +1672,10 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
@@ -1649,7 +1687,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="7" t="s">
@@ -1697,7 +1735,7 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="AC1" t="s">
@@ -1726,6 +1764,7 @@
       <c r="F2" t="s">
         <v>34</v>
       </c>
+      <c r="G2"/>
       <c r="H2" s="7">
         <v>4</v>
       </c>
@@ -1738,6 +1777,7 @@
       <c r="K2">
         <v>0</v>
       </c>
+      <c r="L2"/>
       <c r="M2" s="7">
         <v>11</v>
       </c>
@@ -1747,6 +1787,11 @@
       <c r="O2" s="9">
         <v>7</v>
       </c>
+      <c r="R2"/>
+      <c r="U2"/>
+      <c r="X2"/>
+      <c r="Z2"/>
+      <c r="AB2"/>
       <c r="AC2" s="10"/>
       <c r="AE2" t="s">
         <v>35</v>
@@ -1771,6 +1816,7 @@
       <c r="F3" t="s">
         <v>34</v>
       </c>
+      <c r="G3"/>
       <c r="H3" s="7">
         <v>0</v>
       </c>
@@ -1783,6 +1829,7 @@
       <c r="K3">
         <v>0</v>
       </c>
+      <c r="L3"/>
       <c r="M3" s="7">
         <v>2</v>
       </c>
@@ -1792,12 +1839,17 @@
       <c r="O3" s="9">
         <v>4</v>
       </c>
+      <c r="R3"/>
+      <c r="U3"/>
+      <c r="X3"/>
+      <c r="Z3"/>
+      <c r="AB3"/>
       <c r="AC3" s="10"/>
       <c r="AE3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:31" hidden="1">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1805,7 +1857,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -1816,11 +1868,11 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4">
         <v>5</v>
       </c>
       <c r="I4" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1835,11 +1887,20 @@
         <v>15</v>
       </c>
       <c r="O4" s="9">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="P4">
+        <v>56</v>
+      </c>
+      <c r="Q4">
+        <v>9</v>
+      </c>
+      <c r="R4" s="9">
+        <v>12</v>
       </c>
       <c r="AC4" s="10"/>
       <c r="AE4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -1847,10 +1908,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -1861,6 +1922,7 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
+      <c r="G5"/>
       <c r="H5" s="7">
         <v>3</v>
       </c>
@@ -1873,6 +1935,7 @@
       <c r="K5">
         <v>0</v>
       </c>
+      <c r="L5"/>
       <c r="M5" s="7">
         <v>11</v>
       </c>
@@ -1891,34 +1954,38 @@
       <c r="R5" s="9">
         <v>2</v>
       </c>
+      <c r="U5"/>
+      <c r="X5"/>
+      <c r="Z5"/>
+      <c r="AB5"/>
       <c r="AC5" s="10"/>
       <c r="AE5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:31" hidden="1">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>377</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>378</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6" s="7">
+        <v>44</v>
+      </c>
+      <c r="G6" s="9">
+        <v>3</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" s="9">
@@ -1932,10 +1999,28 @@
       </c>
       <c r="M6" s="7">
         <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6" s="9">
+        <v>7</v>
+      </c>
+      <c r="S6">
+        <v>9</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="9">
+        <v>1</v>
       </c>
       <c r="AC6" s="10"/>
       <c r="AE6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -1943,13 +2028,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1957,6 +2042,7 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
+      <c r="G7"/>
       <c r="H7" s="7">
         <v>5</v>
       </c>
@@ -1969,9 +2055,11 @@
       <c r="K7">
         <v>1</v>
       </c>
+      <c r="L7"/>
       <c r="M7" s="7">
         <v>4</v>
       </c>
+      <c r="O7"/>
       <c r="P7" s="7">
         <v>21</v>
       </c>
@@ -1990,29 +2078,32 @@
       <c r="U7" s="9">
         <v>1</v>
       </c>
+      <c r="X7"/>
+      <c r="Z7"/>
+      <c r="AB7"/>
       <c r="AC7" s="10"/>
       <c r="AE7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:31" hidden="1">
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2029,6 +2120,7 @@
       <c r="K8">
         <v>1</v>
       </c>
+      <c r="L8"/>
       <c r="M8" s="7">
         <v>2</v>
       </c>
@@ -2056,20 +2148,23 @@
       <c r="U8" s="9">
         <v>1</v>
       </c>
+      <c r="X8"/>
+      <c r="Z8"/>
+      <c r="AB8"/>
       <c r="AC8" s="10"/>
       <c r="AE8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2080,6 +2175,7 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
+      <c r="G9"/>
       <c r="H9" s="7">
         <v>2</v>
       </c>
@@ -2092,6 +2188,7 @@
       <c r="K9">
         <v>0</v>
       </c>
+      <c r="L9"/>
       <c r="M9" s="7">
         <v>6</v>
       </c>
@@ -2110,20 +2207,24 @@
       <c r="R9" s="9">
         <v>4</v>
       </c>
+      <c r="U9"/>
+      <c r="X9"/>
+      <c r="Z9"/>
+      <c r="AB9"/>
       <c r="AC9" s="10"/>
       <c r="AE9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:31" hidden="1">
+    <row r="10" spans="1:31">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -2134,6 +2235,7 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
+      <c r="G10"/>
       <c r="H10" s="7">
         <v>2</v>
       </c>
@@ -2146,6 +2248,7 @@
       <c r="K10">
         <v>0</v>
       </c>
+      <c r="L10"/>
       <c r="M10" s="7">
         <v>7</v>
       </c>
@@ -2164,20 +2267,24 @@
       <c r="R10" s="9">
         <v>3</v>
       </c>
+      <c r="U10"/>
+      <c r="X10"/>
+      <c r="Z10"/>
+      <c r="AB10"/>
       <c r="AC10" s="10"/>
       <c r="AE10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2188,7 +2295,7 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" s="9">
@@ -2220,18 +2327,18 @@
       </c>
       <c r="AC11" s="10"/>
       <c r="AE11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -2242,6 +2349,7 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
+      <c r="G12"/>
       <c r="H12" s="7">
         <v>6</v>
       </c>
@@ -2254,6 +2362,7 @@
       <c r="K12">
         <v>0</v>
       </c>
+      <c r="L12"/>
       <c r="M12" s="7">
         <v>11</v>
       </c>
@@ -2272,12 +2381,16 @@
       <c r="R12" s="9">
         <v>13</v>
       </c>
+      <c r="U12"/>
+      <c r="X12"/>
+      <c r="Z12"/>
+      <c r="AB12"/>
       <c r="AC12" s="10"/>
       <c r="AD12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AE12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -2285,13 +2398,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -2299,6 +2412,7 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
+      <c r="G13"/>
       <c r="H13" s="7">
         <v>5</v>
       </c>
@@ -2311,6 +2425,7 @@
       <c r="K13">
         <v>0</v>
       </c>
+      <c r="L13"/>
       <c r="M13" s="7">
         <v>11</v>
       </c>
@@ -2329,20 +2444,24 @@
       <c r="R13" s="9">
         <v>9</v>
       </c>
+      <c r="U13"/>
+      <c r="X13"/>
+      <c r="Z13"/>
+      <c r="AB13"/>
       <c r="AC13" s="10"/>
       <c r="AE13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:31" hidden="1">
+    <row r="14" spans="1:31">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -2353,6 +2472,7 @@
       <c r="F14" t="s">
         <v>34</v>
       </c>
+      <c r="G14"/>
       <c r="H14" s="7">
         <v>5</v>
       </c>
@@ -2365,6 +2485,7 @@
       <c r="K14">
         <v>0</v>
       </c>
+      <c r="L14"/>
       <c r="M14" s="7">
         <v>6</v>
       </c>
@@ -2374,23 +2495,28 @@
       <c r="O14" s="9">
         <v>8</v>
       </c>
+      <c r="R14"/>
+      <c r="U14"/>
+      <c r="X14"/>
+      <c r="Z14"/>
+      <c r="AB14"/>
       <c r="AC14" s="10"/>
       <c r="AE14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:31" hidden="1">
+    <row r="15" spans="1:31">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
@@ -2398,6 +2524,7 @@
       <c r="F15" t="s">
         <v>34</v>
       </c>
+      <c r="G15"/>
       <c r="H15" s="7">
         <v>4</v>
       </c>
@@ -2410,6 +2537,7 @@
       <c r="K15">
         <v>0</v>
       </c>
+      <c r="L15"/>
       <c r="M15" s="7">
         <v>18</v>
       </c>
@@ -2419,23 +2547,28 @@
       <c r="O15" s="9">
         <v>1.8</v>
       </c>
+      <c r="R15"/>
+      <c r="U15"/>
+      <c r="X15"/>
+      <c r="Z15"/>
+      <c r="AB15"/>
       <c r="AC15" s="10"/>
       <c r="AE15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:31" hidden="1">
+    <row r="16" spans="1:31">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
@@ -2443,6 +2576,7 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
+      <c r="G16"/>
       <c r="H16" s="7">
         <v>6</v>
       </c>
@@ -2455,6 +2589,7 @@
       <c r="K16">
         <v>0</v>
       </c>
+      <c r="L16"/>
       <c r="M16" s="7">
         <v>6</v>
       </c>
@@ -2473,6 +2608,10 @@
       <c r="R16" s="9">
         <v>1.1000000000000001</v>
       </c>
+      <c r="U16"/>
+      <c r="X16"/>
+      <c r="Z16"/>
+      <c r="AB16"/>
       <c r="AC16" s="10"/>
       <c r="AE16" t="s">
         <v>33</v>
@@ -2483,13 +2622,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
         <v>38</v>
@@ -2497,6 +2636,7 @@
       <c r="F17" t="s">
         <v>34</v>
       </c>
+      <c r="G17"/>
       <c r="H17" s="7">
         <v>3</v>
       </c>
@@ -2509,6 +2649,7 @@
       <c r="K17">
         <v>1</v>
       </c>
+      <c r="L17"/>
       <c r="M17" s="7">
         <v>19</v>
       </c>
@@ -2536,23 +2677,26 @@
       <c r="U17" s="9">
         <v>3</v>
       </c>
+      <c r="X17"/>
+      <c r="Z17"/>
+      <c r="AB17"/>
       <c r="AC17" s="11"/>
       <c r="AE17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:31" hidden="1">
+    <row r="18" spans="1:31">
       <c r="A18">
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
@@ -2560,7 +2704,7 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18">
         <v>4</v>
       </c>
       <c r="I18" s="9">
@@ -2581,23 +2725,29 @@
       <c r="O18" s="9">
         <v>7</v>
       </c>
+      <c r="Y18">
+        <v>61</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>1.5</v>
+      </c>
       <c r="AC18" s="10"/>
       <c r="AE18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31">
       <c r="A19">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -2605,6 +2755,7 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
+      <c r="G19"/>
       <c r="H19" s="7">
         <v>5</v>
       </c>
@@ -2617,6 +2768,7 @@
       <c r="K19">
         <v>1</v>
       </c>
+      <c r="L19"/>
       <c r="M19" s="7">
         <v>23</v>
       </c>
@@ -2635,20 +2787,24 @@
       <c r="R19" s="9">
         <v>2</v>
       </c>
+      <c r="U19"/>
+      <c r="X19"/>
+      <c r="Z19"/>
+      <c r="AB19"/>
       <c r="AC19" s="10"/>
       <c r="AE19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31">
       <c r="A20">
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -2659,7 +2815,7 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20">
         <v>6</v>
       </c>
       <c r="I20" s="9">
@@ -2671,7 +2827,7 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="9">
         <v>0</v>
       </c>
       <c r="M20" s="7">
@@ -2683,23 +2839,29 @@
       <c r="O20" s="9">
         <v>30</v>
       </c>
+      <c r="Y20">
+        <v>62</v>
+      </c>
+      <c r="Z20" s="9">
+        <v>7</v>
+      </c>
       <c r="AC20" s="11"/>
       <c r="AE20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
         <v>33</v>
@@ -2707,7 +2869,7 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21">
         <v>5</v>
       </c>
       <c r="I21" s="9">
@@ -2737,7 +2899,7 @@
       <c r="R21" s="9">
         <v>42</v>
       </c>
-      <c r="S21" s="7">
+      <c r="S21">
         <v>2</v>
       </c>
       <c r="T21">
@@ -2748,21 +2910,21 @@
       </c>
       <c r="AC21" s="10"/>
       <c r="AE21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31">
       <c r="A22">
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s">
         <v>38</v>
@@ -2770,6 +2932,7 @@
       <c r="F22" t="s">
         <v>34</v>
       </c>
+      <c r="G22"/>
       <c r="H22" s="7">
         <v>4</v>
       </c>
@@ -2782,6 +2945,7 @@
       <c r="K22">
         <v>1</v>
       </c>
+      <c r="L22"/>
       <c r="M22" s="7">
         <v>6</v>
       </c>
@@ -2800,23 +2964,27 @@
       <c r="R22" s="9">
         <v>1</v>
       </c>
+      <c r="U22"/>
+      <c r="X22"/>
+      <c r="Z22"/>
+      <c r="AB22"/>
       <c r="AC22" s="10"/>
       <c r="AE22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:31" hidden="1">
+    <row r="23" spans="1:31">
       <c r="A23">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
         <v>38</v>
@@ -2824,6 +2992,7 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
+      <c r="G23"/>
       <c r="H23" s="7">
         <v>1</v>
       </c>
@@ -2836,6 +3005,7 @@
       <c r="K23">
         <v>0</v>
       </c>
+      <c r="L23"/>
       <c r="M23" s="7">
         <v>6</v>
       </c>
@@ -2854,20 +3024,24 @@
       <c r="R23" s="9">
         <v>1</v>
       </c>
+      <c r="U23"/>
+      <c r="X23"/>
+      <c r="Z23"/>
+      <c r="AB23"/>
       <c r="AC23" s="10"/>
       <c r="AE23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:31" hidden="1">
+    <row r="24" spans="1:31">
       <c r="A24">
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -2878,7 +3052,7 @@
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24">
         <v>4</v>
       </c>
       <c r="I24" s="9">
@@ -2908,20 +3082,26 @@
       <c r="R24" s="9">
         <v>11</v>
       </c>
+      <c r="Y24">
+        <v>63</v>
+      </c>
+      <c r="Z24" s="9">
+        <v>3</v>
+      </c>
       <c r="AC24" s="10"/>
       <c r="AE24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31">
       <c r="A25">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
         <v>32</v>
@@ -2932,6 +3112,7 @@
       <c r="F25" t="s">
         <v>34</v>
       </c>
+      <c r="G25"/>
       <c r="H25" s="7">
         <v>3</v>
       </c>
@@ -2944,6 +3125,7 @@
       <c r="K25">
         <v>0</v>
       </c>
+      <c r="L25"/>
       <c r="M25" s="7">
         <v>7</v>
       </c>
@@ -2953,20 +3135,25 @@
       <c r="O25" s="9">
         <v>5</v>
       </c>
+      <c r="R25"/>
+      <c r="U25"/>
+      <c r="X25"/>
+      <c r="Z25"/>
+      <c r="AB25"/>
       <c r="AC25" s="10"/>
       <c r="AE25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31">
       <c r="A26">
         <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
@@ -2977,6 +3164,7 @@
       <c r="F26" t="s">
         <v>34</v>
       </c>
+      <c r="G26"/>
       <c r="H26" s="7">
         <v>3</v>
       </c>
@@ -2989,6 +3177,7 @@
       <c r="K26">
         <v>0</v>
       </c>
+      <c r="L26"/>
       <c r="M26" s="7">
         <v>7</v>
       </c>
@@ -3007,23 +3196,27 @@
       <c r="R26" s="9">
         <v>6</v>
       </c>
+      <c r="U26"/>
+      <c r="X26"/>
+      <c r="Z26"/>
+      <c r="AB26"/>
       <c r="AC26" s="10"/>
       <c r="AE26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31">
       <c r="A27">
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
@@ -3031,7 +3224,7 @@
       <c r="F27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27">
         <v>8</v>
       </c>
       <c r="I27" s="9">
@@ -3043,7 +3236,7 @@
       <c r="K27">
         <v>1</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="9">
         <v>0</v>
       </c>
       <c r="M27" s="7">
@@ -3064,7 +3257,7 @@
       <c r="R27" s="9">
         <v>30</v>
       </c>
-      <c r="S27" s="7">
+      <c r="S27">
         <v>57</v>
       </c>
       <c r="T27">
@@ -3075,18 +3268,18 @@
       </c>
       <c r="AC27" s="11"/>
       <c r="AE27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31">
       <c r="A28">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -3097,7 +3290,7 @@
       <c r="F28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28">
         <v>1</v>
       </c>
       <c r="I28" s="9">
@@ -3118,9 +3311,15 @@
       <c r="O28" s="9">
         <v>8</v>
       </c>
+      <c r="Y28">
+        <v>21</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>12</v>
+      </c>
       <c r="AC28" s="10"/>
       <c r="AE28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:31">
@@ -3128,13 +3327,13 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
@@ -3142,6 +3341,7 @@
       <c r="F29" t="s">
         <v>34</v>
       </c>
+      <c r="G29"/>
       <c r="H29" s="7">
         <v>5</v>
       </c>
@@ -3154,6 +3354,7 @@
       <c r="K29">
         <v>1</v>
       </c>
+      <c r="L29"/>
       <c r="M29" s="7">
         <v>32</v>
       </c>
@@ -3181,6 +3382,9 @@
       <c r="U29" s="9">
         <v>3</v>
       </c>
+      <c r="X29"/>
+      <c r="Z29"/>
+      <c r="AB29"/>
       <c r="AC29" s="10"/>
       <c r="AE29" t="s">
         <v>35</v>
@@ -3191,13 +3395,13 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
@@ -3205,6 +3409,7 @@
       <c r="F30" t="s">
         <v>34</v>
       </c>
+      <c r="G30"/>
       <c r="H30" s="7">
         <v>4</v>
       </c>
@@ -3217,6 +3422,7 @@
       <c r="K30">
         <v>1</v>
       </c>
+      <c r="L30"/>
       <c r="M30" s="7">
         <v>33</v>
       </c>
@@ -3235,6 +3441,10 @@
       <c r="R30" s="9">
         <v>4</v>
       </c>
+      <c r="U30"/>
+      <c r="X30"/>
+      <c r="Z30"/>
+      <c r="AB30"/>
       <c r="AC30" s="11"/>
       <c r="AE30" t="s">
         <v>35</v>
@@ -3245,13 +3455,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>
@@ -3259,6 +3469,7 @@
       <c r="F31" t="s">
         <v>34</v>
       </c>
+      <c r="G31"/>
       <c r="H31" s="7">
         <v>4</v>
       </c>
@@ -3271,6 +3482,7 @@
       <c r="K31">
         <v>1</v>
       </c>
+      <c r="L31"/>
       <c r="M31" s="7">
         <v>33</v>
       </c>
@@ -3289,6 +3501,10 @@
       <c r="R31" s="9">
         <v>1</v>
       </c>
+      <c r="U31"/>
+      <c r="X31"/>
+      <c r="Z31"/>
+      <c r="AB31"/>
       <c r="AC31" s="11"/>
       <c r="AE31" t="s">
         <v>35</v>
@@ -3299,13 +3515,13 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
         <v>38</v>
@@ -3313,6 +3529,7 @@
       <c r="F32" t="s">
         <v>34</v>
       </c>
+      <c r="G32"/>
       <c r="H32" s="7">
         <v>7</v>
       </c>
@@ -3325,22 +3542,29 @@
       <c r="K32">
         <v>1</v>
       </c>
+      <c r="L32"/>
+      <c r="O32"/>
+      <c r="R32"/>
+      <c r="U32"/>
+      <c r="X32"/>
+      <c r="Z32"/>
+      <c r="AB32"/>
       <c r="AE32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:31" hidden="1">
+    <row r="33" spans="1:31">
       <c r="A33">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>379</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
         <v>33</v>
@@ -3348,7 +3572,7 @@
       <c r="F33" t="s">
         <v>34</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33">
         <v>8</v>
       </c>
       <c r="I33" s="9">
@@ -3369,22 +3593,28 @@
       <c r="O33" s="9">
         <v>52</v>
       </c>
+      <c r="Y33">
+        <v>64</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>1</v>
+      </c>
       <c r="AE33" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31">
       <c r="A34">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
@@ -3392,7 +3622,7 @@
       <c r="F34" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34">
         <v>3</v>
       </c>
       <c r="I34" s="9">
@@ -3404,7 +3634,7 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="9">
         <v>0</v>
       </c>
       <c r="M34" s="7">
@@ -3417,21 +3647,21 @@
         <v>4</v>
       </c>
       <c r="AE34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31">
       <c r="A35">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>380</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>381</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E35" t="s">
         <v>33</v>
@@ -3439,7 +3669,7 @@
       <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35">
         <v>3</v>
       </c>
       <c r="I35" s="9">
@@ -3461,10 +3691,10 @@
         <v>22</v>
       </c>
       <c r="AE35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31">
       <c r="A36">
         <v>37</v>
       </c>
@@ -3472,10 +3702,10 @@
         <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E36" t="s">
         <v>38</v>
@@ -3483,7 +3713,7 @@
       <c r="F36" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36">
         <v>3</v>
       </c>
       <c r="I36" s="9">
@@ -3514,21 +3744,21 @@
         <v>8</v>
       </c>
       <c r="AE36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31">
       <c r="A37">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
         <v>38</v>
@@ -3536,6 +3766,7 @@
       <c r="F37" t="s">
         <v>34</v>
       </c>
+      <c r="G37"/>
       <c r="H37" s="7">
         <v>3</v>
       </c>
@@ -3548,6 +3779,7 @@
       <c r="K37">
         <v>0</v>
       </c>
+      <c r="L37"/>
       <c r="M37" s="7">
         <v>7</v>
       </c>
@@ -3566,8 +3798,12 @@
       <c r="R37" s="9">
         <v>8</v>
       </c>
+      <c r="U37"/>
+      <c r="X37"/>
+      <c r="Z37"/>
+      <c r="AB37"/>
       <c r="AE37" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:31">
@@ -3575,13 +3811,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
         <v>38</v>
@@ -3589,6 +3825,7 @@
       <c r="F38" t="s">
         <v>34</v>
       </c>
+      <c r="G38"/>
       <c r="H38" s="7">
         <v>1</v>
       </c>
@@ -3601,6 +3838,7 @@
       <c r="K38">
         <v>1</v>
       </c>
+      <c r="L38"/>
       <c r="M38" s="7">
         <v>21</v>
       </c>
@@ -3619,6 +3857,10 @@
       <c r="R38" s="9">
         <v>5</v>
       </c>
+      <c r="U38"/>
+      <c r="X38"/>
+      <c r="Z38"/>
+      <c r="AB38"/>
       <c r="AE38" t="s">
         <v>35</v>
       </c>
@@ -3628,13 +3870,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -3642,6 +3884,7 @@
       <c r="F39" t="s">
         <v>34</v>
       </c>
+      <c r="G39"/>
       <c r="H39" s="7">
         <v>1</v>
       </c>
@@ -3654,6 +3897,7 @@
       <c r="K39">
         <v>1</v>
       </c>
+      <c r="L39"/>
       <c r="M39" s="7">
         <v>5</v>
       </c>
@@ -3672,22 +3916,26 @@
       <c r="R39" s="9">
         <v>7</v>
       </c>
+      <c r="U39"/>
+      <c r="X39"/>
+      <c r="Z39"/>
+      <c r="AB39"/>
       <c r="AE39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:31" hidden="1">
+    <row r="40" spans="1:31">
       <c r="A40">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -3695,6 +3943,7 @@
       <c r="F40" t="s">
         <v>34</v>
       </c>
+      <c r="G40"/>
       <c r="H40" s="7">
         <v>4</v>
       </c>
@@ -3707,6 +3956,7 @@
       <c r="K40">
         <v>1</v>
       </c>
+      <c r="L40"/>
       <c r="M40" s="7">
         <v>7</v>
       </c>
@@ -3725,19 +3975,23 @@
       <c r="R40" s="9">
         <v>5</v>
       </c>
+      <c r="U40"/>
+      <c r="X40"/>
+      <c r="Z40"/>
+      <c r="AB40"/>
       <c r="AE40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31">
       <c r="A41">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
         <v>32</v>
@@ -3748,6 +4002,7 @@
       <c r="F41" t="s">
         <v>34</v>
       </c>
+      <c r="G41"/>
       <c r="H41" s="7">
         <v>2</v>
       </c>
@@ -3760,6 +4015,7 @@
       <c r="K41">
         <v>0</v>
       </c>
+      <c r="L41"/>
       <c r="M41" s="7">
         <v>6</v>
       </c>
@@ -3778,22 +4034,26 @@
       <c r="R41" s="9">
         <v>3</v>
       </c>
+      <c r="U41"/>
+      <c r="X41"/>
+      <c r="Z41"/>
+      <c r="AB41"/>
       <c r="AE41" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:31" hidden="1">
+    <row r="42" spans="1:31">
       <c r="A42">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
@@ -3801,6 +4061,7 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
+      <c r="G42"/>
       <c r="H42" s="7">
         <v>4</v>
       </c>
@@ -3813,6 +4074,7 @@
       <c r="K42">
         <v>1</v>
       </c>
+      <c r="L42"/>
       <c r="M42" s="7">
         <v>7</v>
       </c>
@@ -3831,22 +4093,26 @@
       <c r="R42" s="9">
         <v>1</v>
       </c>
+      <c r="U42"/>
+      <c r="X42"/>
+      <c r="Z42"/>
+      <c r="AB42"/>
       <c r="AE42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31">
       <c r="A43">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
         <v>33</v>
@@ -3854,6 +4120,7 @@
       <c r="F43" t="s">
         <v>34</v>
       </c>
+      <c r="G43"/>
       <c r="H43" s="7">
         <v>7</v>
       </c>
@@ -3866,6 +4133,7 @@
       <c r="K43">
         <v>1</v>
       </c>
+      <c r="L43"/>
       <c r="M43" s="7">
         <v>6</v>
       </c>
@@ -3893,22 +4161,25 @@
       <c r="U43" s="9">
         <v>1.2</v>
       </c>
+      <c r="X43"/>
+      <c r="Z43"/>
+      <c r="AB43"/>
       <c r="AE43" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:31" hidden="1">
+    <row r="44" spans="1:31">
       <c r="A44">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E44" t="s">
         <v>33</v>
@@ -3916,7 +4187,7 @@
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44">
         <v>6</v>
       </c>
       <c r="I44" s="9">
@@ -3947,21 +4218,21 @@
         <v>12</v>
       </c>
       <c r="AE44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31">
       <c r="A45">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E45" t="s">
         <v>38</v>
@@ -3969,6 +4240,7 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
+      <c r="G45"/>
       <c r="H45" s="7">
         <v>5</v>
       </c>
@@ -3981,6 +4253,7 @@
       <c r="K45">
         <v>1</v>
       </c>
+      <c r="L45"/>
       <c r="M45" s="7">
         <v>7</v>
       </c>
@@ -4008,8 +4281,11 @@
       <c r="U45" s="9">
         <v>8</v>
       </c>
+      <c r="X45"/>
+      <c r="Z45"/>
+      <c r="AB45"/>
       <c r="AE45" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:31">
@@ -4017,13 +4293,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E46" t="s">
         <v>38</v>
@@ -4031,6 +4307,7 @@
       <c r="F46" t="s">
         <v>34</v>
       </c>
+      <c r="G46"/>
       <c r="H46" s="7">
         <v>10</v>
       </c>
@@ -4043,6 +4320,7 @@
       <c r="K46">
         <v>1</v>
       </c>
+      <c r="L46"/>
       <c r="M46" s="7">
         <v>32</v>
       </c>
@@ -4070,19 +4348,22 @@
       <c r="U46" s="9">
         <v>1</v>
       </c>
+      <c r="X46"/>
+      <c r="Z46"/>
+      <c r="AB46"/>
       <c r="AE46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:31" hidden="1">
+    <row r="47" spans="1:31">
       <c r="A47">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D47" t="s">
         <v>32</v>
@@ -4093,6 +4374,7 @@
       <c r="F47" t="s">
         <v>34</v>
       </c>
+      <c r="G47"/>
       <c r="H47" s="7">
         <v>2</v>
       </c>
@@ -4105,6 +4387,7 @@
       <c r="K47">
         <v>0</v>
       </c>
+      <c r="L47"/>
       <c r="M47" s="7">
         <v>11</v>
       </c>
@@ -4114,16 +4397,24 @@
       <c r="O47" s="9">
         <v>14</v>
       </c>
+      <c r="R47"/>
+      <c r="U47"/>
+      <c r="X47"/>
+      <c r="Z47"/>
+      <c r="AB47"/>
       <c r="AE47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" hidden="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31">
       <c r="A48">
         <v>49</v>
       </c>
+      <c r="B48">
+        <v>123</v>
+      </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D48" t="s">
         <v>32</v>
@@ -4134,6 +4425,7 @@
       <c r="F48" t="s">
         <v>34</v>
       </c>
+      <c r="G48"/>
       <c r="H48" s="7">
         <v>4</v>
       </c>
@@ -4146,6 +4438,7 @@
       <c r="K48">
         <v>0</v>
       </c>
+      <c r="L48"/>
       <c r="M48" s="7">
         <v>11</v>
       </c>
@@ -4164,19 +4457,23 @@
       <c r="R48" s="9">
         <v>3</v>
       </c>
+      <c r="U48"/>
+      <c r="X48"/>
+      <c r="Z48"/>
+      <c r="AB48"/>
       <c r="AE48" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:31" hidden="1">
+    <row r="49" spans="1:31">
       <c r="A49">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
         <v>32</v>
@@ -4187,7 +4484,7 @@
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49">
         <v>4</v>
       </c>
       <c r="I49" s="9">
@@ -4218,21 +4515,21 @@
         <v>3</v>
       </c>
       <c r="AE49" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31">
       <c r="A50">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E50" t="s">
         <v>33</v>
@@ -4240,6 +4537,7 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
+      <c r="G50"/>
       <c r="H50" s="7">
         <v>5</v>
       </c>
@@ -4252,6 +4550,7 @@
       <c r="K50">
         <v>1</v>
       </c>
+      <c r="L50"/>
       <c r="M50" s="7">
         <v>6</v>
       </c>
@@ -4270,22 +4569,26 @@
       <c r="R50" s="9">
         <v>1.7</v>
       </c>
+      <c r="U50"/>
+      <c r="X50"/>
+      <c r="Z50"/>
+      <c r="AB50"/>
       <c r="AE50" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:31" hidden="1">
+    <row r="51" spans="1:31">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
         <v>38</v>
@@ -4293,6 +4596,7 @@
       <c r="F51" t="s">
         <v>34</v>
       </c>
+      <c r="G51"/>
       <c r="H51" s="7">
         <v>9</v>
       </c>
@@ -4305,6 +4609,7 @@
       <c r="K51">
         <v>1</v>
       </c>
+      <c r="L51"/>
       <c r="M51" s="7">
         <v>6</v>
       </c>
@@ -4323,6 +4628,10 @@
       <c r="R51" s="9">
         <v>1</v>
       </c>
+      <c r="U51"/>
+      <c r="X51"/>
+      <c r="Z51"/>
+      <c r="AB51"/>
       <c r="AE51" t="s">
         <v>33</v>
       </c>
@@ -4332,13 +4641,13 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E52" t="s">
         <v>38</v>
@@ -4346,6 +4655,7 @@
       <c r="F52" t="s">
         <v>34</v>
       </c>
+      <c r="G52"/>
       <c r="H52" s="7">
         <v>1</v>
       </c>
@@ -4358,6 +4668,7 @@
       <c r="K52">
         <v>1</v>
       </c>
+      <c r="L52"/>
       <c r="M52" s="7">
         <v>9</v>
       </c>
@@ -4376,22 +4687,26 @@
       <c r="R52" s="9">
         <v>2</v>
       </c>
+      <c r="U52"/>
+      <c r="X52"/>
+      <c r="Z52"/>
+      <c r="AB52"/>
       <c r="AE52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:31" hidden="1">
+    <row r="53" spans="1:31">
       <c r="A53">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C53" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E53" t="s">
         <v>33</v>
@@ -4399,7 +4714,7 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H53">
         <v>5</v>
       </c>
       <c r="I53" s="9">
@@ -4411,10 +4726,10 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="9">
         <v>6</v>
       </c>
-      <c r="M53" s="7">
+      <c r="M53">
         <v>50</v>
       </c>
       <c r="N53">
@@ -4423,7 +4738,7 @@
       <c r="O53" s="9">
         <v>4</v>
       </c>
-      <c r="P53" s="7">
+      <c r="P53">
         <v>51</v>
       </c>
       <c r="Q53">
@@ -4433,32 +4748,32 @@
         <v>-0.5</v>
       </c>
       <c r="AE53" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31">
       <c r="A54">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E54" t="s">
         <v>38</v>
       </c>
       <c r="F54" t="s">
-        <v>47</v>
-      </c>
-      <c r="G54">
+        <v>44</v>
+      </c>
+      <c r="G54" s="9">
         <v>14</v>
       </c>
-      <c r="H54" s="7">
+      <c r="H54">
         <v>2</v>
       </c>
       <c r="I54" s="9">
@@ -4470,7 +4785,7 @@
       <c r="K54">
         <v>1</v>
       </c>
-      <c r="M54" s="7">
+      <c r="M54">
         <v>15</v>
       </c>
       <c r="N54">
@@ -4479,7 +4794,7 @@
       <c r="O54" s="9">
         <v>4</v>
       </c>
-      <c r="P54" s="7">
+      <c r="P54">
         <v>14</v>
       </c>
       <c r="Q54">
@@ -4488,7 +4803,7 @@
       <c r="R54" s="9">
         <v>1</v>
       </c>
-      <c r="S54" s="7">
+      <c r="S54">
         <v>52</v>
       </c>
       <c r="T54">
@@ -4498,21 +4813,21 @@
         <v>5</v>
       </c>
       <c r="AE54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31">
       <c r="A55">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E55" t="s">
         <v>38</v>
@@ -4520,7 +4835,7 @@
       <c r="F55" t="s">
         <v>34</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55">
         <v>4</v>
       </c>
       <c r="I55" s="9">
@@ -4538,10 +4853,10 @@
       <c r="N55">
         <v>1</v>
       </c>
-      <c r="O55">
-        <v>3</v>
-      </c>
-      <c r="P55" s="7">
+      <c r="O55" s="9">
+        <v>3</v>
+      </c>
+      <c r="P55">
         <v>60</v>
       </c>
       <c r="Q55">
@@ -4552,179 +4867,178 @@
       </c>
       <c r="AA55" s="9"/>
       <c r="AE55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31">
+      <c r="A56">
+        <v>57</v>
+      </c>
+      <c r="B56" t="s">
+        <v>141</v>
+      </c>
       <c r="C56" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
-        <v>34</v>
-      </c>
-      <c r="H56" s="7">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="G56" s="9">
+        <v>3</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
       </c>
       <c r="I56" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="N56">
-        <v>2</v>
-      </c>
-      <c r="O56">
-        <v>2</v>
-      </c>
-      <c r="P56" s="7">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="O56" s="9">
+        <v>4</v>
+      </c>
+      <c r="P56">
+        <v>11</v>
       </c>
       <c r="Q56">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R56" s="9">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="S56">
+        <v>14</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+      <c r="U56" s="9">
+        <v>1</v>
       </c>
       <c r="AA56" s="9"/>
       <c r="AE56" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31">
+      <c r="A57">
+        <v>58</v>
+      </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E57" t="s">
         <v>33</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
-      </c>
-      <c r="G57">
-        <v>3</v>
-      </c>
-      <c r="H57" s="7">
+        <v>44</v>
+      </c>
+      <c r="G57" s="9">
+        <v>3</v>
+      </c>
+      <c r="H57">
         <v>2</v>
       </c>
       <c r="I57" s="9">
         <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57">
         <v>1</v>
       </c>
       <c r="M57">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="N57">
-        <v>3</v>
-      </c>
-      <c r="O57">
-        <v>4</v>
-      </c>
-      <c r="P57" s="7">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="O57" s="9">
+        <v>6</v>
+      </c>
+      <c r="P57">
+        <v>2</v>
       </c>
       <c r="Q57">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R57" s="9">
-        <v>18</v>
-      </c>
-      <c r="S57" s="7">
-        <v>14</v>
-      </c>
-      <c r="T57">
-        <v>1</v>
-      </c>
-      <c r="U57" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="9"/>
+        <v>6</v>
+      </c>
       <c r="AE57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31">
+      <c r="A58">
+        <v>59</v>
+      </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>382</v>
       </c>
       <c r="C58" t="s">
-        <v>151</v>
+        <v>383</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
         <v>34</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58">
         <v>3</v>
       </c>
       <c r="I58" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58">
-        <v>1</v>
-      </c>
-      <c r="M58" s="7">
-        <v>45</v>
-      </c>
-      <c r="N58">
-        <v>2</v>
-      </c>
-      <c r="O58" s="9">
-        <v>3</v>
-      </c>
-      <c r="P58" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q58">
-        <v>2</v>
-      </c>
-      <c r="R58" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31">
+      <c r="A59">
+        <v>60</v>
+      </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>384</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>385</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E59" t="s">
         <v>33</v>
@@ -4732,8 +5046,8 @@
       <c r="F59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" s="7">
-        <v>3</v>
+      <c r="H59">
+        <v>4</v>
       </c>
       <c r="I59" s="9">
         <v>3</v>
@@ -4742,36 +5056,45 @@
         <v>1</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59">
+        <v>7</v>
+      </c>
+      <c r="O59" s="9">
+        <v>9</v>
       </c>
       <c r="AE59" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" hidden="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31">
+      <c r="A60">
+        <v>61</v>
+      </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>386</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>387</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E60" t="s">
         <v>33</v>
       </c>
       <c r="F60" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60">
-        <v>3</v>
-      </c>
-      <c r="H60" s="7">
+        <v>34</v>
+      </c>
+      <c r="H60">
         <v>2</v>
       </c>
       <c r="I60" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -4779,40 +5102,222 @@
       <c r="K60">
         <v>1</v>
       </c>
-      <c r="M60" s="7">
-        <v>2</v>
-      </c>
-      <c r="N60">
-        <v>5</v>
-      </c>
-      <c r="O60" s="9">
-        <v>6</v>
-      </c>
-      <c r="P60" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q60">
-        <v>5</v>
-      </c>
-      <c r="R60" s="9">
-        <v>6</v>
-      </c>
       <c r="AE60" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31" hidden="1"/>
-    <row r="62" spans="1:31" hidden="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31">
+      <c r="A61">
+        <v>62</v>
+      </c>
+      <c r="B61" t="s">
+        <v>388</v>
+      </c>
+      <c r="C61" t="s">
+        <v>389</v>
+      </c>
+      <c r="D61" t="s">
+        <v>61</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="s">
+        <v>44</v>
+      </c>
+      <c r="G61" s="9">
+        <v>14</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+      <c r="I61" s="9">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE62" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:AE61" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="30">
       <filters>
+        <filter val="C"/>
         <filter val="F"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFA4640-CFCE-465A-87A0-93766D6720A8}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9A170A-FBD6-48B2-AAE0-2B7F0755C3F2}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4846,19 +5351,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G1" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="H1" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="I1" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4866,13 +5371,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I2">
         <v>-1</v>
@@ -4883,19 +5388,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F3" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4906,16 +5411,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -4926,16 +5431,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -4946,13 +5451,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -4963,16 +5468,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -4983,13 +5488,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5003,13 +5508,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5023,13 +5528,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5043,13 +5548,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -5060,16 +5565,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -5080,16 +5585,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -5100,19 +5605,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -5123,16 +5628,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C15" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -5143,16 +5648,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -5163,13 +5668,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -5183,16 +5688,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5203,13 +5708,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -5223,13 +5728,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5243,16 +5748,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -5263,16 +5768,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -5283,13 +5788,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -5303,19 +5808,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -5326,13 +5831,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -5346,16 +5851,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5369,16 +5874,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E27" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -5389,13 +5894,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5409,19 +5914,19 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -5435,13 +5940,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C30" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -5455,19 +5960,19 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C31" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D31" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -5478,19 +5983,19 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="D32" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -5501,19 +6006,19 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -5524,16 +6029,16 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -5544,16 +6049,16 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -5564,19 +6069,19 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F36" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -5590,13 +6095,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E37">
         <v>11</v>
@@ -5610,16 +6115,16 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C38" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -5630,13 +6135,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -5653,16 +6158,16 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E40" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -5673,13 +6178,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5696,19 +6201,19 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5722,13 +6227,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C43" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E43">
         <v>12</v>
@@ -5742,13 +6247,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E44">
         <v>13</v>
@@ -5762,19 +6267,19 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F45" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -5785,16 +6290,16 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E46" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -5805,13 +6310,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E47">
         <v>14</v>
@@ -5825,19 +6330,19 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D48" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -5848,13 +6353,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C49" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D49" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -5868,19 +6373,19 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D50" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I50">
         <v>-1</v>
@@ -5891,13 +6396,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C51" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D51" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E51">
         <v>16</v>
@@ -5911,13 +6416,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -5931,13 +6436,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="D53" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -5951,13 +6456,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C54" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D54" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -5974,16 +6479,16 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C55" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D55" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -5997,16 +6502,16 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D56" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E56" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G56">
         <v>7</v>
@@ -6020,16 +6525,16 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C57" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D57" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E57" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G57">
         <v>8</v>
@@ -6043,16 +6548,16 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G58">
         <v>6</v>
@@ -6066,16 +6571,16 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G59">
         <v>7</v>
@@ -6089,16 +6594,16 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C60" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E60" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G60">
         <v>8</v>
@@ -6112,19 +6617,19 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="D61" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E61">
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="I61">
         <v>-1</v>
@@ -6135,13 +6640,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C62" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D62" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -6152,7 +6657,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6181,13 +6686,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D1" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="F1" t="s">
         <v>12</v>
@@ -6214,10 +6719,10 @@
         <v>22</v>
       </c>
       <c r="N1" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="O1" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -6225,10 +6730,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -6254,10 +6759,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -6277,10 +6782,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6294,10 +6799,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -6329,10 +6834,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C6" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6352,10 +6857,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C7" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -6375,10 +6880,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6398,10 +6903,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -6421,10 +6926,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6444,10 +6949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6473,10 +6978,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6502,10 +7007,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6525,10 +7030,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6548,10 +7053,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6571,10 +7076,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -6594,10 +7099,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6617,10 +7122,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C18" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6640,10 +7145,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -6657,10 +7162,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -6674,10 +7179,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6691,10 +7196,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6740,16 +7245,16 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E1" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="F1" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="G1" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -6757,13 +7262,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -6777,13 +7282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D3" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -6794,13 +7299,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
         <v>33</v>
@@ -6811,13 +7316,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -6831,13 +7336,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D6" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6851,13 +7356,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D7" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6871,13 +7376,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D8" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -6891,13 +7396,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -6911,13 +7416,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -6962,7 +7467,7 @@
         <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -6970,19 +7475,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6990,19 +7495,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D3" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -7010,19 +7515,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D4" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7030,16 +7535,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D5" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7047,16 +7552,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C6" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D6" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="F6" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7064,16 +7569,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D7" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="F7" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7081,13 +7586,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="C8" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7095,13 +7600,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="C9" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="D9" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7109,13 +7614,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C10" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D10" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7126,13 +7631,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="C11" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="D11" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7140,13 +7645,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C12" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -7157,13 +7662,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C13" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D13" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -7174,13 +7679,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C14" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -7226,13 +7731,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -7243,13 +7748,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7257,13 +7762,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="E4" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -7273,497 +7778,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2">
-        <v>90</v>
-      </c>
-      <c r="H2" t="s">
-        <v>324</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="J2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D3" t="s">
-        <v>324</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="J3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D4" t="s">
-        <v>324</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4">
-        <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>324</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="J4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C5" t="s">
-        <v>329</v>
-      </c>
-      <c r="D5" t="s">
-        <v>330</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>330</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="J5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>332</v>
-      </c>
-      <c r="C6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>330</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="J6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>330</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="J7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>337</v>
-      </c>
-      <c r="D8" t="s">
-        <v>330</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>330</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="J8" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>339</v>
-      </c>
-      <c r="D9" t="s">
-        <v>330</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>330</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="J9" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>341</v>
-      </c>
-      <c r="D10" t="s">
-        <v>330</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>330</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="J10" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D11" t="s">
-        <v>330</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>330</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="J11" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>370</v>
-      </c>
-      <c r="D12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>330</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="J12" t="s">
-        <v>370</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>362</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -7798,7 +7812,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -7807,28 +7821,28 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="J1" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="K1" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="L1" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="M1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="N1" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -7836,13 +7850,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D2" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7854,10 +7868,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -7881,13 +7895,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -7899,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J3">
         <v>5</v>
@@ -7926,13 +7940,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C4" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -7944,10 +7958,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -7971,13 +7985,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D5" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -7989,10 +8003,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -8018,13 +8032,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D6" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -8036,10 +8050,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -8057,7 +8071,7 @@
         <v>7</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -8065,13 +8079,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -8083,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -8112,13 +8126,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C8" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -8130,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J8">
         <v>10</v>
@@ -8159,13 +8173,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -8177,10 +8191,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J9">
         <v>10</v>
@@ -8198,7 +8212,7 @@
         <v>7</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -8206,13 +8220,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -8224,10 +8238,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -8252,4 +8266,495 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2">
+        <v>90</v>
+      </c>
+      <c r="H2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>313</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="J4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>319</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>319</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="J8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>319</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>319</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="J10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>319</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>319</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/StreamingAssets/Configurations/NewCards.xlsx
+++ b/Assets/StreamingAssets/Configurations/NewCards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\VTuberSim\Assets\StreamingAssets\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{896509AF-F5C6-4E31-9F13-A26265473CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9618729-529B-4113-9140-C2D3C826719B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
     <sheet name="CardConditions" sheetId="6" r:id="rId6"/>
     <sheet name="StreamEvents" sheetId="8" r:id="rId7"/>
     <sheet name="DialogueEvents" sheetId="7" r:id="rId8"/>
-    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId9"/>
-    <sheet name="Relics" sheetId="11" r:id="rId10"/>
-    <sheet name="RaisingRelicConditions" sheetId="13" r:id="rId11"/>
+    <sheet name="RaisingRelicConditions" sheetId="13" r:id="rId9"/>
+    <sheet name="PhaseEndingConditions" sheetId="10" r:id="rId10"/>
+    <sheet name="Relics" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Cards!$A$1:$AE$61</definedName>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="394">
   <si>
     <t>ID</t>
   </si>
@@ -1162,12 +1162,6 @@
     <t>Layer</t>
   </si>
   <si>
-    <t>VBattleRelicConfiguration</t>
-  </si>
-  <si>
-    <t>OnTurnBegin</t>
-  </si>
-  <si>
     <t>VCardOperationRelicCondition</t>
   </si>
   <si>
@@ -1214,6 +1208,24 @@
   </si>
   <si>
     <t>获得神采100%的参数，下一回合抽一张卡牌</t>
+  </si>
+  <si>
+    <t>AddRelic0</t>
+  </si>
+  <si>
+    <t>VRaisingAddRelicEffect</t>
+  </si>
+  <si>
+    <t>VBattleRelic</t>
+  </si>
+  <si>
+    <t>MyRelic</t>
+  </si>
+  <si>
+    <t>VCardTypeUsedCountCondition</t>
+  </si>
+  <si>
+    <t>OnCardUsed</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1638,7 @@
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" customWidth="1"/>
@@ -1857,7 +1869,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -1968,10 +1980,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D6" t="s">
         <v>43</v>
@@ -3561,7 +3573,7 @@
         <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D33" t="s">
         <v>43</v>
@@ -3634,9 +3646,6 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="L34" s="9">
-        <v>0</v>
-      </c>
       <c r="M34" s="7">
         <v>15</v>
       </c>
@@ -3655,10 +3664,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C35" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D35" t="s">
         <v>61</v>
@@ -4997,10 +5006,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C58" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D58" t="s">
         <v>32</v>
@@ -5032,10 +5041,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C59" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D59" t="s">
         <v>61</v>
@@ -5076,10 +5085,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C60" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D60" t="s">
         <v>43</v>
@@ -5111,10 +5120,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C61" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D61" t="s">
         <v>61</v>
@@ -5156,6 +5165,104 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFA4640-CFCE-465A-87A0-93766D6720A8}">
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5164,7 +5271,7 @@
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
@@ -5234,85 +5341,32 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>391</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9A170A-FBD6-48B2-AAE0-2B7F0755C3F2}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>368</v>
-      </c>
-      <c r="F1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
+        <v>393</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7222,12 +7276,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
@@ -7431,15 +7485,35 @@
         <v>50</v>
       </c>
     </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>12313</v>
+      </c>
+      <c r="C11" t="s">
+        <v>392</v>
+      </c>
+      <c r="D11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.42578125" customWidth="1"/>
@@ -7691,7 +7765,25 @@
         <v>2</v>
       </c>
     </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C15" t="s">
+        <v>388</v>
+      </c>
+      <c r="D15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -8662,19 +8754,19 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6620075D-DE02-4F16-B523-AE1F397F6AC8}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F9A170A-FBD6-48B2-AAE0-2B7F0755C3F2}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8688,73 +8780,40 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>268</v>
+        <v>368</v>
       </c>
       <c r="F1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>369</v>
+      </c>
+      <c r="G1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>319</v>
+        <v>373</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>